--- a/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
@@ -13572,19 +13572,19 @@
         <v>45777</v>
       </c>
       <c r="C4" s="22">
-        <f>[9]Apr!$M$1-C17</f>
+        <f>[9]Jul!$M$1-C17</f>
         <v>0</v>
       </c>
       <c r="D4" s="22">
-        <f>[9]Apr!$N$1-D17</f>
+        <f>[9]Jul!$N$1-D17</f>
         <v>0</v>
       </c>
       <c r="E4" s="22">
-        <f>[9]Apr!$O$1-E17</f>
+        <f>[9]Jul!$O$1-E17</f>
         <v>0</v>
       </c>
       <c r="F4" s="22">
-        <f>[9]Apr!$P$1+[9]Apr!$Q$1-F17</f>
+        <f>[9]Jul!$P$1+[9]Jul!$Q$1-F17</f>
         <v>0</v>
       </c>
       <c r="G4" s="22">
@@ -13592,11 +13592,11 @@
         <v>0</v>
       </c>
       <c r="H4" s="22">
-        <f>[9]Apr!$T$1-H17</f>
+        <f>[9]Jul!$T$1-H17</f>
         <v>0</v>
       </c>
       <c r="I4" s="22">
-        <f>[9]Apr!$G$1</f>
+        <f>[9]Jul!$G$1</f>
         <v>0</v>
       </c>
       <c r="J4" s="13"/>
@@ -13612,19 +13612,19 @@
         <v>45808</v>
       </c>
       <c r="C5" s="22">
-        <f>[9]May!$M$1-C18</f>
+        <f>[9]Aug!$M$1-C18</f>
         <v>0</v>
       </c>
       <c r="D5" s="22">
-        <f>[9]May!$N$1-D18</f>
+        <f>[9]Aug!$N$1-D18</f>
         <v>0</v>
       </c>
       <c r="E5" s="22">
-        <f>[9]May!$O$1-E18</f>
+        <f>[9]Aug!$O$1-E18</f>
         <v>0</v>
       </c>
       <c r="F5" s="22">
-        <f>[9]May!$P$1+[9]May!$Q$1-F18</f>
+        <f>[9]Aug!$P$1+[9]Aug!$Q$1-F18</f>
         <v>0</v>
       </c>
       <c r="G5" s="22">
@@ -13632,11 +13632,11 @@
         <v>0</v>
       </c>
       <c r="H5" s="22">
-        <f>[9]May!$T$1-H18</f>
+        <f>[9]Aug!$T$1-H18</f>
         <v>0</v>
       </c>
       <c r="I5" s="22">
-        <f>[9]May!$G$1</f>
+        <f>[9]Aug!$G$1</f>
         <v>0</v>
       </c>
       <c r="J5" s="13"/>
@@ -13650,19 +13650,19 @@
         <v>45838</v>
       </c>
       <c r="C6" s="22">
-        <f>[9]Jun!$M$1-C19</f>
+        <f>[9]Sep!$M$1-C19</f>
         <v>0</v>
       </c>
       <c r="D6" s="22">
-        <f>[9]Jun!$N$1-D19</f>
+        <f>[9]Sep!$N$1-D19</f>
         <v>0</v>
       </c>
       <c r="E6" s="22">
-        <f>[9]Jun!$O$1-E19</f>
+        <f>[9]Sep!$O$1-E19</f>
         <v>0</v>
       </c>
       <c r="F6" s="22">
-        <f>[9]Jun!$P$1+[9]Jun!$Q$1-F19</f>
+        <f>[9]Sep!$P$1+[9]Sep!$Q$1-F19</f>
         <v>0</v>
       </c>
       <c r="G6" s="22">
@@ -13670,11 +13670,11 @@
         <v>0</v>
       </c>
       <c r="H6" s="22">
-        <f>[9]Jun!$T$1-H19</f>
+        <f>[9]Sep!$T$1-H19</f>
         <v>0</v>
       </c>
       <c r="I6" s="22">
-        <f>[9]Jun!$G$1</f>
+        <f>[9]Sep!$G$1</f>
         <v>0</v>
       </c>
       <c r="J6" s="13"/>
@@ -13688,19 +13688,19 @@
         <v>45869</v>
       </c>
       <c r="C7" s="22">
-        <f>[9]Jul!$M$1-C20</f>
+        <f>[9]Oct!$M$1-C20</f>
         <v>0</v>
       </c>
       <c r="D7" s="22">
-        <f>[9]Jul!$N$1-D20</f>
+        <f>[9]Oct!$N$1-D20</f>
         <v>0</v>
       </c>
       <c r="E7" s="22">
-        <f>[9]Jul!$O$1-E20</f>
+        <f>[9]Oct!$O$1-E20</f>
         <v>0</v>
       </c>
       <c r="F7" s="22">
-        <f>[9]Jul!$P$1+[9]Jul!$Q$1-F20</f>
+        <f>[9]Oct!$P$1+[9]Oct!$Q$1-F20</f>
         <v>0</v>
       </c>
       <c r="G7" s="22">
@@ -13708,11 +13708,11 @@
         <v>0</v>
       </c>
       <c r="H7" s="22">
-        <f>[9]Jul!$T$1-H20</f>
+        <f>[9]Oct!$T$1-H20</f>
         <v>0</v>
       </c>
       <c r="I7" s="22">
-        <f>[9]Jul!$G$1</f>
+        <f>[9]Oct!$G$1</f>
         <v>0</v>
       </c>
       <c r="J7" s="13"/>
@@ -13726,19 +13726,19 @@
         <v>45900</v>
       </c>
       <c r="C8" s="22">
-        <f>[9]Aug!$M$1-C21</f>
+        <f>[9]Nov!$M$1-C21</f>
         <v>0</v>
       </c>
       <c r="D8" s="22">
-        <f>[9]Aug!$N$1-D21</f>
+        <f>[9]Nov!$N$1-D21</f>
         <v>0</v>
       </c>
       <c r="E8" s="22">
-        <f>[9]Aug!$O$1-E21</f>
+        <f>[9]Nov!$O$1-E21</f>
         <v>0</v>
       </c>
       <c r="F8" s="22">
-        <f>[9]Aug!$P$1+[9]Aug!$Q$1-F21</f>
+        <f>[9]Nov!$P$1+[9]Nov!$Q$1-F21</f>
         <v>0</v>
       </c>
       <c r="G8" s="22">
@@ -13746,11 +13746,11 @@
         <v>0</v>
       </c>
       <c r="H8" s="22">
-        <f>[9]Aug!$T$1-H21</f>
+        <f>[9]Nov!$T$1-H21</f>
         <v>0</v>
       </c>
       <c r="I8" s="22">
-        <f>[9]Aug!$G$1</f>
+        <f>[9]Nov!$G$1</f>
         <v>0</v>
       </c>
       <c r="J8" s="13"/>
@@ -13766,19 +13766,19 @@
         <v>45930</v>
       </c>
       <c r="C9" s="22">
-        <f>[9]Sep!$M$1-C22</f>
+        <f>[9]Dec!$M$1-C22</f>
         <v>0</v>
       </c>
       <c r="D9" s="22">
-        <f>[9]Sep!$N$1-D22</f>
+        <f>[9]Dec!$N$1-D22</f>
         <v>0</v>
       </c>
       <c r="E9" s="22">
-        <f>[9]Sep!$O$1-E22</f>
+        <f>[9]Dec!$O$1-E22</f>
         <v>0</v>
       </c>
       <c r="F9" s="22">
-        <f>[9]Sep!$P$1+[9]Sep!$Q$1-F22</f>
+        <f>[9]Dec!$P$1+[9]Dec!$Q$1-F22</f>
         <v>0</v>
       </c>
       <c r="G9" s="22">
@@ -13786,11 +13786,11 @@
         <v>0</v>
       </c>
       <c r="H9" s="22">
-        <f>[9]Sep!$T$1-H22</f>
+        <f>[9]Dec!$T$1-H22</f>
         <v>0</v>
       </c>
       <c r="I9" s="22">
-        <f>[9]Sep!$G$1</f>
+        <f>[9]Dec!$G$1</f>
         <v>0</v>
       </c>
       <c r="J9" s="13"/>
@@ -13804,19 +13804,19 @@
         <v>45961</v>
       </c>
       <c r="C10" s="22">
-        <f>[9]Oct!$M$1-C23</f>
+        <f>[9]Jan!$M$1-C23</f>
         <v>0</v>
       </c>
       <c r="D10" s="22">
-        <f>[9]Oct!$N$1-D23</f>
+        <f>[9]Jan!$N$1-D23</f>
         <v>0</v>
       </c>
       <c r="E10" s="22">
-        <f>[9]Oct!$O$1-E23</f>
+        <f>[9]Jan!$O$1-E23</f>
         <v>0</v>
       </c>
       <c r="F10" s="22">
-        <f>[9]Oct!$P$1+[9]Oct!$Q$1-F23</f>
+        <f>[9]Jan!$P$1+[9]Jan!$Q$1-F23</f>
         <v>0</v>
       </c>
       <c r="G10" s="22">
@@ -13824,11 +13824,11 @@
         <v>0</v>
       </c>
       <c r="H10" s="22">
-        <f>[9]Oct!$T$1-H23</f>
+        <f>[9]Jan!$T$1-H23</f>
         <v>0</v>
       </c>
       <c r="I10" s="22">
-        <f>[9]Oct!$G$1</f>
+        <f>[9]Jan!$G$1</f>
         <v>0</v>
       </c>
       <c r="J10" s="13"/>
@@ -13842,19 +13842,19 @@
         <v>45991</v>
       </c>
       <c r="C11" s="22">
-        <f>[9]Nov!$M$1-C24</f>
+        <f>[9]Feb!$M$1-C24</f>
         <v>0</v>
       </c>
       <c r="D11" s="22">
-        <f>[9]Nov!$N$1-D24</f>
+        <f>[9]Feb!$N$1-D24</f>
         <v>0</v>
       </c>
       <c r="E11" s="22">
-        <f>[9]Nov!$O$1-E24</f>
+        <f>[9]Feb!$O$1-E24</f>
         <v>0</v>
       </c>
       <c r="F11" s="22">
-        <f>[9]Nov!$P$1+[9]Nov!$Q$1-F24</f>
+        <f>[9]Feb!$P$1+[9]Feb!$Q$1-F24</f>
         <v>0</v>
       </c>
       <c r="G11" s="22">
@@ -13862,11 +13862,11 @@
         <v>0</v>
       </c>
       <c r="H11" s="22">
-        <f>[9]Nov!$T$1-H24</f>
+        <f>[9]Feb!$T$1-H24</f>
         <v>0</v>
       </c>
       <c r="I11" s="22">
-        <f>[9]Nov!$G$1</f>
+        <f>[9]Feb!$G$1</f>
         <v>0</v>
       </c>
       <c r="J11" s="13"/>
@@ -13880,19 +13880,19 @@
         <v>46022</v>
       </c>
       <c r="C12" s="22">
-        <f>[9]Dec!$M$1-C25</f>
+        <f>[9]Mar!$M$1-C25</f>
         <v>0</v>
       </c>
       <c r="D12" s="22">
-        <f>[9]Dec!$N$1-D25</f>
+        <f>[9]Mar!$N$1-D25</f>
         <v>0</v>
       </c>
       <c r="E12" s="22">
-        <f>[9]Dec!$O$1-E25</f>
+        <f>[9]Mar!$O$1-E25</f>
         <v>0</v>
       </c>
       <c r="F12" s="22">
-        <f>[9]Dec!$P$1+[9]Dec!$Q$1-F25</f>
+        <f>[9]Mar!$P$1+[9]Mar!$Q$1-F25</f>
         <v>0</v>
       </c>
       <c r="G12" s="22">
@@ -13900,11 +13900,11 @@
         <v>0</v>
       </c>
       <c r="H12" s="22">
-        <f>[9]Dec!$T$1-H25</f>
+        <f>[9]Mar!$T$1-H25</f>
         <v>0</v>
       </c>
       <c r="I12" s="22">
-        <f>[9]Dec!$G$1</f>
+        <f>[9]Mar!$G$1</f>
         <v>0</v>
       </c>
       <c r="J12" s="13"/>
@@ -13920,19 +13920,19 @@
         <v>46053</v>
       </c>
       <c r="C13" s="22">
-        <f>[9]Jan!$M$1-C26</f>
+        <f>[9]Apr!$M$1-C26</f>
         <v>0</v>
       </c>
       <c r="D13" s="22">
-        <f>[9]Jan!$N$1-D26</f>
+        <f>[9]Apr!$N$1-D26</f>
         <v>0</v>
       </c>
       <c r="E13" s="22">
-        <f>[9]Jan!$O$1-E26</f>
+        <f>[9]Apr!$O$1-E26</f>
         <v>0</v>
       </c>
       <c r="F13" s="22">
-        <f>[9]Jan!$P$1+[9]Jan!$Q$1-F26</f>
+        <f>[9]Apr!$P$1+[9]Apr!$Q$1-F26</f>
         <v>0</v>
       </c>
       <c r="G13" s="22">
@@ -13940,11 +13940,11 @@
         <v>0</v>
       </c>
       <c r="H13" s="22">
-        <f>[9]Jan!$T$1-H26</f>
+        <f>[9]Apr!$T$1-H26</f>
         <v>0</v>
       </c>
       <c r="I13" s="22">
-        <f>[9]Jan!$G$1</f>
+        <f>[9]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="J13" s="13"/>
@@ -13958,19 +13958,19 @@
         <v>46081</v>
       </c>
       <c r="C14" s="22">
-        <f>[9]Feb!$M$1-C27</f>
+        <f>[9]May!$M$1-C27</f>
         <v>0</v>
       </c>
       <c r="D14" s="22">
-        <f>[9]Feb!$N$1-D27</f>
+        <f>[9]May!$N$1-D27</f>
         <v>0</v>
       </c>
       <c r="E14" s="22">
-        <f>[9]Feb!$O$1-E27</f>
+        <f>[9]May!$O$1-E27</f>
         <v>0</v>
       </c>
       <c r="F14" s="22">
-        <f>[9]Feb!$P$1+[9]Feb!$Q$1-F27</f>
+        <f>[9]May!$P$1+[9]May!$Q$1-F27</f>
         <v>0</v>
       </c>
       <c r="G14" s="22">
@@ -13978,11 +13978,11 @@
         <v>0</v>
       </c>
       <c r="H14" s="22">
-        <f>[9]Feb!$T$1-H27</f>
+        <f>[9]May!$T$1-H27</f>
         <v>0</v>
       </c>
       <c r="I14" s="22">
-        <f>[9]Feb!$G$1</f>
+        <f>[9]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="J14" s="13"/>
@@ -13996,19 +13996,19 @@
         <v>46112</v>
       </c>
       <c r="C15" s="22">
-        <f>[9]Mar!$M$1-C28</f>
+        <f>[9]Jun!$M$1-C28</f>
         <v>0</v>
       </c>
       <c r="D15" s="22">
-        <f>[9]Mar!$N$1-D28</f>
+        <f>[9]Jun!$N$1-D28</f>
         <v>0</v>
       </c>
       <c r="E15" s="22">
-        <f>[9]Mar!$O$1-E28</f>
+        <f>[9]Jun!$O$1-E28</f>
         <v>0</v>
       </c>
       <c r="F15" s="22">
-        <f>[9]Mar!$P$1+[9]Mar!$Q$1-F28</f>
+        <f>[9]Jun!$P$1+[9]Jun!$Q$1-F28</f>
         <v>0</v>
       </c>
       <c r="G15" s="22">
@@ -14016,11 +14016,11 @@
         <v>0</v>
       </c>
       <c r="H15" s="22">
-        <f>[9]Mar!$T$1-H28</f>
+        <f>[9]Jun!$T$1-H28</f>
         <v>0</v>
       </c>
       <c r="I15" s="22">
-        <f>[9]Mar!$G$1</f>
+        <f>[9]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="J15" s="13"/>
@@ -14050,19 +14050,19 @@
         <v>45777</v>
       </c>
       <c r="C17" s="22">
-        <f>[9]Apr!$M$2</f>
+        <f>[9]Jul!$M$2</f>
         <v>0</v>
       </c>
       <c r="D17" s="22">
-        <f>[9]Apr!$N$2</f>
+        <f>[9]Jul!$N$2</f>
         <v>0</v>
       </c>
       <c r="E17" s="22">
-        <f>[9]Apr!$O$2</f>
+        <f>[9]Jul!$O$2</f>
         <v>0</v>
       </c>
       <c r="F17" s="22">
-        <f>[9]Apr!$P$2+[9]Apr!$Q$2</f>
+        <f>[9]Jul!$P$2+[9]Jul!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G17" s="22">
@@ -14070,7 +14070,7 @@
         <v>0</v>
       </c>
       <c r="H17" s="22">
-        <f>[9]Apr!$T$2</f>
+        <f>[9]Jul!$T$2</f>
         <v>0</v>
       </c>
       <c r="J17" s="13"/>
@@ -14086,19 +14086,19 @@
         <v>45808</v>
       </c>
       <c r="C18" s="22">
-        <f>[9]May!$M$2</f>
+        <f>[9]Aug!$M$2</f>
         <v>0</v>
       </c>
       <c r="D18" s="22">
-        <f>[9]May!$N$2</f>
+        <f>[9]Aug!$N$2</f>
         <v>0</v>
       </c>
       <c r="E18" s="22">
-        <f>[9]May!$O$2</f>
+        <f>[9]Aug!$O$2</f>
         <v>0</v>
       </c>
       <c r="F18" s="22">
-        <f>[9]May!$P$2+[9]May!$Q$2</f>
+        <f>[9]Aug!$P$2+[9]Aug!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G18" s="22">
@@ -14106,7 +14106,7 @@
         <v>0</v>
       </c>
       <c r="H18" s="22">
-        <f>[9]May!$T$2</f>
+        <f>[9]Aug!$T$2</f>
         <v>0</v>
       </c>
       <c r="J18" s="13"/>
@@ -14120,19 +14120,19 @@
         <v>45838</v>
       </c>
       <c r="C19" s="22">
-        <f>[9]Jun!$M$2</f>
+        <f>[9]Sep!$M$2</f>
         <v>0</v>
       </c>
       <c r="D19" s="22">
-        <f>[9]Jun!$N$2</f>
+        <f>[9]Sep!$N$2</f>
         <v>0</v>
       </c>
       <c r="E19" s="22">
-        <f>[9]Jun!$O$2</f>
+        <f>[9]Sep!$O$2</f>
         <v>0</v>
       </c>
       <c r="F19" s="22">
-        <f>[9]Jun!$P$2+[9]Jun!$Q$2</f>
+        <f>[9]Sep!$P$2+[9]Sep!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G19" s="22">
@@ -14140,7 +14140,7 @@
         <v>0</v>
       </c>
       <c r="H19" s="22">
-        <f>[9]Jun!$T$2</f>
+        <f>[9]Sep!$T$2</f>
         <v>0</v>
       </c>
       <c r="J19" s="13"/>
@@ -14154,19 +14154,19 @@
         <v>45869</v>
       </c>
       <c r="C20" s="22">
-        <f>[9]Jul!$M$2</f>
+        <f>[9]Oct!$M$2</f>
         <v>0</v>
       </c>
       <c r="D20" s="22">
-        <f>[9]Jul!$N$2</f>
+        <f>[9]Oct!$N$2</f>
         <v>0</v>
       </c>
       <c r="E20" s="22">
-        <f>[9]Jul!$O$2</f>
+        <f>[9]Oct!$O$2</f>
         <v>0</v>
       </c>
       <c r="F20" s="22">
-        <f>[9]Jul!$P$2+[9]Jul!$Q$2</f>
+        <f>[9]Oct!$P$2+[9]Oct!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G20" s="22">
@@ -14174,7 +14174,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="22">
-        <f>[9]Jul!$T$2</f>
+        <f>[9]Oct!$T$2</f>
         <v>0</v>
       </c>
       <c r="J20" s="13"/>
@@ -14188,19 +14188,19 @@
         <v>45900</v>
       </c>
       <c r="C21" s="22">
-        <f>[9]Aug!$M$2</f>
+        <f>[9]Nov!$M$2</f>
         <v>0</v>
       </c>
       <c r="D21" s="22">
-        <f>[9]Aug!$N$2</f>
+        <f>[9]Nov!$N$2</f>
         <v>0</v>
       </c>
       <c r="E21" s="22">
-        <f>[9]Aug!$O$2</f>
+        <f>[9]Nov!$O$2</f>
         <v>0</v>
       </c>
       <c r="F21" s="22">
-        <f>[9]Aug!$P$2+[9]Aug!$Q$2</f>
+        <f>[9]Nov!$P$2+[9]Nov!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G21" s="22">
@@ -14208,7 +14208,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="22">
-        <f>[9]Aug!$T$2</f>
+        <f>[9]Nov!$T$2</f>
         <v>0</v>
       </c>
       <c r="J21" s="13"/>
@@ -14222,19 +14222,19 @@
         <v>45930</v>
       </c>
       <c r="C22" s="22">
-        <f>[9]Sep!$M$2</f>
+        <f>[9]Dec!$M$2</f>
         <v>0</v>
       </c>
       <c r="D22" s="22">
-        <f>[9]Sep!$N$2</f>
+        <f>[9]Dec!$N$2</f>
         <v>0</v>
       </c>
       <c r="E22" s="22">
-        <f>[9]Sep!$O$2</f>
+        <f>[9]Dec!$O$2</f>
         <v>0</v>
       </c>
       <c r="F22" s="22">
-        <f>[9]Sep!$P$2+[9]Sep!$Q$2</f>
+        <f>[9]Dec!$P$2+[9]Dec!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G22" s="22">
@@ -14242,7 +14242,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="22">
-        <f>[9]Sep!$T$2</f>
+        <f>[9]Dec!$T$2</f>
         <v>0</v>
       </c>
       <c r="J22" s="13"/>
@@ -14256,19 +14256,19 @@
         <v>45961</v>
       </c>
       <c r="C23" s="22">
-        <f>[9]Oct!$M$2</f>
+        <f>[9]Jan!$M$2</f>
         <v>0</v>
       </c>
       <c r="D23" s="22">
-        <f>[9]Oct!$N$2</f>
+        <f>[9]Jan!$N$2</f>
         <v>0</v>
       </c>
       <c r="E23" s="22">
-        <f>[9]Oct!$O$2</f>
+        <f>[9]Jan!$O$2</f>
         <v>0</v>
       </c>
       <c r="F23" s="22">
-        <f>[9]Oct!$P$2+[9]Oct!$Q$2</f>
+        <f>[9]Jan!$P$2+[9]Jan!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G23" s="22">
@@ -14276,7 +14276,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="22">
-        <f>[9]Oct!$T$2</f>
+        <f>[9]Jan!$T$2</f>
         <v>0</v>
       </c>
       <c r="J23" s="13"/>
@@ -14290,19 +14290,19 @@
         <v>45991</v>
       </c>
       <c r="C24" s="22">
-        <f>[9]Nov!$M$2</f>
+        <f>[9]Feb!$M$2</f>
         <v>0</v>
       </c>
       <c r="D24" s="22">
-        <f>[9]Nov!$N$2</f>
+        <f>[9]Feb!$N$2</f>
         <v>0</v>
       </c>
       <c r="E24" s="22">
-        <f>[9]Nov!$O$2</f>
+        <f>[9]Feb!$O$2</f>
         <v>0</v>
       </c>
       <c r="F24" s="22">
-        <f>[9]Nov!$P$2+[9]Nov!$Q$2</f>
+        <f>[9]Feb!$P$2+[9]Feb!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G24" s="22">
@@ -14310,7 +14310,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="22">
-        <f>[9]Nov!$T$2</f>
+        <f>[9]Feb!$T$2</f>
         <v>0</v>
       </c>
       <c r="J24" s="13"/>
@@ -14324,19 +14324,19 @@
         <v>46022</v>
       </c>
       <c r="C25" s="22">
-        <f>[9]Dec!$M$2</f>
+        <f>[9]Mar!$M$2</f>
         <v>0</v>
       </c>
       <c r="D25" s="22">
-        <f>[9]Dec!$N$2</f>
+        <f>[9]Mar!$N$2</f>
         <v>0</v>
       </c>
       <c r="E25" s="22">
-        <f>[9]Dec!$O$2</f>
+        <f>[9]Mar!$O$2</f>
         <v>0</v>
       </c>
       <c r="F25" s="22">
-        <f>[9]Dec!$P$2+[9]Dec!$Q$2</f>
+        <f>[9]Mar!$P$2+[9]Mar!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G25" s="22">
@@ -14344,7 +14344,7 @@
         <v>0</v>
       </c>
       <c r="H25" s="22">
-        <f>[9]Dec!$T$2</f>
+        <f>[9]Mar!$T$2</f>
         <v>0</v>
       </c>
       <c r="J25" s="13"/>
@@ -14358,19 +14358,19 @@
         <v>46053</v>
       </c>
       <c r="C26" s="22">
-        <f>[9]Jan!$M$2</f>
+        <f>[9]Apr!$M$2</f>
         <v>0</v>
       </c>
       <c r="D26" s="22">
-        <f>[9]Jan!$N$2</f>
+        <f>[9]Apr!$N$2</f>
         <v>0</v>
       </c>
       <c r="E26" s="22">
-        <f>[9]Jan!$O$2</f>
+        <f>[9]Apr!$O$2</f>
         <v>0</v>
       </c>
       <c r="F26" s="22">
-        <f>[9]Jan!$P$2+[9]Jan!$Q$2</f>
+        <f>[9]Apr!$P$2+[9]Apr!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G26" s="22">
@@ -14378,7 +14378,7 @@
         <v>0</v>
       </c>
       <c r="H26" s="22">
-        <f>[9]Jan!$T$2</f>
+        <f>[9]Apr!$T$2</f>
         <v>0</v>
       </c>
       <c r="J26" s="13"/>
@@ -14392,19 +14392,19 @@
         <v>46081</v>
       </c>
       <c r="C27" s="22">
-        <f>[9]Feb!$M$2</f>
+        <f>[9]May!$M$2</f>
         <v>0</v>
       </c>
       <c r="D27" s="22">
-        <f>[9]Feb!$N$2</f>
+        <f>[9]May!$N$2</f>
         <v>0</v>
       </c>
       <c r="E27" s="22">
-        <f>[9]Feb!$O$2</f>
+        <f>[9]May!$O$2</f>
         <v>0</v>
       </c>
       <c r="F27" s="22">
-        <f>[9]Feb!$P$2+[9]Feb!$Q$2</f>
+        <f>[9]May!$P$2+[9]May!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G27" s="22">
@@ -14412,7 +14412,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="22">
-        <f>[9]Feb!$T$2</f>
+        <f>[9]May!$T$2</f>
         <v>0</v>
       </c>
       <c r="J27" s="13"/>
@@ -14426,19 +14426,19 @@
         <v>46112</v>
       </c>
       <c r="C28" s="22">
-        <f>[9]Mar!$M$2</f>
+        <f>[9]Jun!$M$2</f>
         <v>0</v>
       </c>
       <c r="D28" s="22">
-        <f>[9]Mar!$N$2</f>
+        <f>[9]Jun!$N$2</f>
         <v>0</v>
       </c>
       <c r="E28" s="22">
-        <f>[9]Mar!$O$2</f>
+        <f>[9]Jun!$O$2</f>
         <v>0</v>
       </c>
       <c r="F28" s="22">
-        <f>[9]Mar!$P$2+[9]Mar!$Q$2</f>
+        <f>[9]Jun!$P$2+[9]Jun!$Q$2</f>
         <v>0</v>
       </c>
       <c r="G28" s="22">
@@ -14446,7 +14446,7 @@
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <f>[9]Mar!$T$2</f>
+        <f>[9]Jun!$T$2</f>
         <v>0</v>
       </c>
       <c r="J28" s="13"/>
@@ -14851,7 +14851,7 @@
       </c>
       <c r="E8" s="97"/>
       <c r="F8" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Apr!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Jul!O$1)</f>
         <v>0</v>
       </c>
       <c r="G8" s="97"/>
@@ -14861,7 +14861,7 @@
       </c>
       <c r="I8" s="97"/>
       <c r="J8" s="97">
-        <f>[3]Apr!$O$1</f>
+        <f>[3]Jul!$O$1</f>
         <v>0</v>
       </c>
       <c r="K8" s="97"/>
@@ -14876,7 +14876,7 @@
       </c>
       <c r="O8" s="97"/>
       <c r="P8" s="97">
-        <f>[3]Apr!$P$1</f>
+        <f>[3]Jul!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q8" s="97"/>
@@ -14891,7 +14891,7 @@
       </c>
       <c r="U8" s="97"/>
       <c r="V8" s="97">
-        <f>[3]Apr!$Q$1</f>
+        <f>[3]Jul!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W8" s="97"/>
@@ -14965,7 +14965,7 @@
       </c>
       <c r="E10" s="97"/>
       <c r="F10" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]May!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Aug!O$1)</f>
         <v>0</v>
       </c>
       <c r="G10" s="97"/>
@@ -14975,7 +14975,7 @@
       </c>
       <c r="I10" s="97"/>
       <c r="J10" s="97">
-        <f>[3]May!$O$1</f>
+        <f>[3]Aug!$O$1</f>
         <v>0</v>
       </c>
       <c r="K10" s="97"/>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="O10" s="97"/>
       <c r="P10" s="97">
-        <f>[3]May!$P$1</f>
+        <f>[3]Aug!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q10" s="97"/>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="U10" s="97"/>
       <c r="V10" s="97">
-        <f>[3]May!$Q$1</f>
+        <f>[3]Aug!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W10" s="97"/>
@@ -15081,7 +15081,7 @@
       </c>
       <c r="E12" s="97"/>
       <c r="F12" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Jun!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Sep!O$1)</f>
         <v>0</v>
       </c>
       <c r="G12" s="97"/>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="I12" s="97"/>
       <c r="J12" s="97">
-        <f>[3]Jun!$O$1</f>
+        <f>[3]Sep!$O$1</f>
         <v>0</v>
       </c>
       <c r="K12" s="97"/>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="O12" s="97"/>
       <c r="P12" s="97">
-        <f>[3]Jun!$P$1</f>
+        <f>[3]Sep!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q12" s="97"/>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="U12" s="97"/>
       <c r="V12" s="97">
-        <f>[3]Jun!$Q$1</f>
+        <f>[3]Sep!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W12" s="97"/>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="E14" s="97"/>
       <c r="F14" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Jul!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Oct!O$1)</f>
         <v>0</v>
       </c>
       <c r="G14" s="97"/>
@@ -15205,7 +15205,7 @@
       </c>
       <c r="I14" s="97"/>
       <c r="J14" s="97">
-        <f>[3]Jul!$O$1</f>
+        <f>[3]Oct!$O$1</f>
         <v>0</v>
       </c>
       <c r="K14" s="97"/>
@@ -15220,7 +15220,7 @@
       </c>
       <c r="O14" s="97"/>
       <c r="P14" s="97">
-        <f>[3]Jul!$P$1</f>
+        <f>[3]Oct!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q14" s="97"/>
@@ -15235,7 +15235,7 @@
       </c>
       <c r="U14" s="97"/>
       <c r="V14" s="97">
-        <f>[3]Jul!$Q$1</f>
+        <f>[3]Oct!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W14" s="97"/>
@@ -15311,7 +15311,7 @@
       </c>
       <c r="E16" s="97"/>
       <c r="F16" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Aug!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Nov!O$1)</f>
         <v>0</v>
       </c>
       <c r="G16" s="97"/>
@@ -15321,7 +15321,7 @@
       </c>
       <c r="I16" s="97"/>
       <c r="J16" s="97">
-        <f>[3]Aug!$O$1</f>
+        <f>[3]Nov!$O$1</f>
         <v>0</v>
       </c>
       <c r="K16" s="97"/>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="O16" s="97"/>
       <c r="P16" s="97">
-        <f>[3]Aug!$P$1</f>
+        <f>[3]Nov!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q16" s="97"/>
@@ -15351,7 +15351,7 @@
       </c>
       <c r="U16" s="97"/>
       <c r="V16" s="97">
-        <f>[3]Aug!$Q$1</f>
+        <f>[3]Nov!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W16" s="97"/>
@@ -15425,7 +15425,7 @@
       </c>
       <c r="E18" s="97"/>
       <c r="F18" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Sep!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Dec!O$1)</f>
         <v>0</v>
       </c>
       <c r="G18" s="97"/>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="I18" s="97"/>
       <c r="J18" s="97">
-        <f>[3]Sep!$O$1</f>
+        <f>[3]Dec!$O$1</f>
         <v>0</v>
       </c>
       <c r="K18" s="97"/>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="O18" s="97"/>
       <c r="P18" s="97">
-        <f>[3]Sep!$P$1</f>
+        <f>[3]Dec!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q18" s="97"/>
@@ -15465,7 +15465,7 @@
       </c>
       <c r="U18" s="97"/>
       <c r="V18" s="97">
-        <f>[3]Sep!$Q$1</f>
+        <f>[3]Dec!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W18" s="97"/>
@@ -15541,7 +15541,7 @@
       </c>
       <c r="E20" s="97"/>
       <c r="F20" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Oct!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Jan!O$1)</f>
         <v>0</v>
       </c>
       <c r="G20" s="97"/>
@@ -15551,7 +15551,7 @@
       </c>
       <c r="I20" s="97"/>
       <c r="J20" s="97">
-        <f>[3]Oct!$O$1</f>
+        <f>[3]Jan!$O$1</f>
         <v>0</v>
       </c>
       <c r="K20" s="97"/>
@@ -15566,7 +15566,7 @@
       </c>
       <c r="O20" s="97"/>
       <c r="P20" s="97">
-        <f>[3]Oct!$P$1</f>
+        <f>[3]Jan!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q20" s="97"/>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="U20" s="97"/>
       <c r="V20" s="97">
-        <f>[3]Oct!$Q$1</f>
+        <f>[3]Jan!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W20" s="97"/>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="E22" s="97"/>
       <c r="F22" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Nov!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Feb!O$1)</f>
         <v>0</v>
       </c>
       <c r="G22" s="97"/>
@@ -15665,7 +15665,7 @@
       </c>
       <c r="I22" s="97"/>
       <c r="J22" s="97">
-        <f>[3]Nov!$O$1</f>
+        <f>[3]Feb!$O$1</f>
         <v>0</v>
       </c>
       <c r="K22" s="97"/>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="O22" s="97"/>
       <c r="P22" s="97">
-        <f>[3]Nov!$P$1</f>
+        <f>[3]Feb!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q22" s="97"/>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="U22" s="97"/>
       <c r="V22" s="97">
-        <f>[3]Nov!$Q$1</f>
+        <f>[3]Feb!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W22" s="97"/>
@@ -15771,7 +15771,7 @@
       </c>
       <c r="E24" s="97"/>
       <c r="F24" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Dec!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Mar!O$1)</f>
         <v>0</v>
       </c>
       <c r="G24" s="97"/>
@@ -15781,7 +15781,7 @@
       </c>
       <c r="I24" s="97"/>
       <c r="J24" s="97">
-        <f>[3]Dec!$O$1</f>
+        <f>[3]Mar!$O$1</f>
         <v>0</v>
       </c>
       <c r="K24" s="97"/>
@@ -15796,7 +15796,7 @@
       </c>
       <c r="O24" s="97"/>
       <c r="P24" s="97">
-        <f>[3]Dec!$P$1</f>
+        <f>[3]Mar!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q24" s="97"/>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="U24" s="97"/>
       <c r="V24" s="97">
-        <f>[3]Dec!$Q$1</f>
+        <f>[3]Mar!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W24" s="97"/>
@@ -15885,7 +15885,7 @@
       </c>
       <c r="E26" s="97"/>
       <c r="F26" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Jan!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Apr!O$1)</f>
         <v>0</v>
       </c>
       <c r="G26" s="97"/>
@@ -15895,7 +15895,7 @@
       </c>
       <c r="I26" s="97"/>
       <c r="J26" s="97">
-        <f>[3]Jan!$O$1</f>
+        <f>[3]Apr!$O$1</f>
         <v>0</v>
       </c>
       <c r="K26" s="97"/>
@@ -15910,7 +15910,7 @@
       </c>
       <c r="O26" s="97"/>
       <c r="P26" s="97">
-        <f>[3]Jan!$P$1</f>
+        <f>[3]Apr!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q26" s="97"/>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="U26" s="97"/>
       <c r="V26" s="97">
-        <f>[3]Jan!$Q$1</f>
+        <f>[3]Apr!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W26" s="97"/>
@@ -15999,7 +15999,7 @@
       </c>
       <c r="E28" s="97"/>
       <c r="F28" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Feb!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]May!O$1)</f>
         <v>0</v>
       </c>
       <c r="G28" s="97"/>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="I28" s="97"/>
       <c r="J28" s="97">
-        <f>[3]Feb!$O$1</f>
+        <f>[3]May!$O$1</f>
         <v>0</v>
       </c>
       <c r="K28" s="97"/>
@@ -16024,7 +16024,7 @@
       </c>
       <c r="O28" s="97"/>
       <c r="P28" s="97">
-        <f>[3]Feb!$P$1</f>
+        <f>[3]May!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q28" s="97"/>
@@ -16039,7 +16039,7 @@
       </c>
       <c r="U28" s="97"/>
       <c r="V28" s="97">
-        <f>[3]Feb!$Q$1</f>
+        <f>[3]May!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W28" s="97"/>
@@ -16115,7 +16115,7 @@
       </c>
       <c r="E30" s="97"/>
       <c r="F30" s="97">
-        <f>IF((H$4+N$4+T$4)=0,0,[2]Mar!O$1)</f>
+        <f>IF((H$4+N$4+T$4)=0,0,[2]Jun!O$1)</f>
         <v>0</v>
       </c>
       <c r="G30" s="97"/>
@@ -16125,7 +16125,7 @@
       </c>
       <c r="I30" s="97"/>
       <c r="J30" s="97">
-        <f>[3]Mar!$O$1</f>
+        <f>[3]Jun!$O$1</f>
         <v>0</v>
       </c>
       <c r="K30" s="97"/>
@@ -16140,7 +16140,7 @@
       </c>
       <c r="O30" s="97"/>
       <c r="P30" s="97">
-        <f>[3]Mar!$P$1</f>
+        <f>[3]Jun!$P$1</f>
         <v>0</v>
       </c>
       <c r="Q30" s="97"/>
@@ -16155,7 +16155,7 @@
       </c>
       <c r="U30" s="97"/>
       <c r="V30" s="97">
-        <f>[3]Mar!$Q$1</f>
+        <f>[3]Jun!$Q$1</f>
         <v>0</v>
       </c>
       <c r="W30" s="97"/>
@@ -20414,7 +20414,7 @@
       <c r="E16" s="21"/>
       <c r="F16" s="22"/>
       <c r="G16" s="22">
-        <f>[2]Apr!$AI$1</f>
+        <f>[2]Jul!$AI$1</f>
         <v>0</v>
       </c>
       <c r="H16" s="22"/>
@@ -20430,7 +20430,7 @@
       <c r="P16" s="21"/>
       <c r="Q16" s="22"/>
       <c r="R16" s="22">
-        <f>[2]May!$AI$1</f>
+        <f>[2]Aug!$AI$1</f>
         <v>0</v>
       </c>
       <c r="S16" s="22"/>
@@ -20447,7 +20447,7 @@
       <c r="AA16" s="21"/>
       <c r="AB16" s="22"/>
       <c r="AC16" s="22">
-        <f>[2]Jun!$AI$1</f>
+        <f>[2]Sep!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AD16" s="22"/>
@@ -20464,7 +20464,7 @@
       <c r="AL16" s="21"/>
       <c r="AM16" s="22"/>
       <c r="AN16" s="22">
-        <f>[2]Jul!$AI$1</f>
+        <f>[2]Oct!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AO16" s="22"/>
@@ -20481,7 +20481,7 @@
       <c r="AW16" s="21"/>
       <c r="AX16" s="22"/>
       <c r="AY16" s="22">
-        <f>[2]Aug!$AI$1</f>
+        <f>[2]Nov!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AZ16" s="22"/>
@@ -20498,7 +20498,7 @@
       <c r="BH16" s="21"/>
       <c r="BI16" s="22"/>
       <c r="BJ16" s="22">
-        <f>[2]Sep!$AI$1</f>
+        <f>[2]Dec!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BK16" s="22"/>
@@ -20515,7 +20515,7 @@
       <c r="BS16" s="21"/>
       <c r="BT16" s="22"/>
       <c r="BU16" s="22">
-        <f>[2]Oct!$AI$1</f>
+        <f>[2]Jan!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BV16" s="22"/>
@@ -20532,7 +20532,7 @@
       <c r="CD16" s="21"/>
       <c r="CE16" s="22"/>
       <c r="CF16" s="22">
-        <f>[2]Nov!$AI$1</f>
+        <f>[2]Feb!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CG16" s="22"/>
@@ -20549,7 +20549,7 @@
       <c r="CO16" s="21"/>
       <c r="CP16" s="22"/>
       <c r="CQ16" s="22">
-        <f>[2]Dec!$AI$1</f>
+        <f>[2]Mar!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CR16" s="22"/>
@@ -20566,7 +20566,7 @@
       <c r="CZ16" s="21"/>
       <c r="DA16" s="22"/>
       <c r="DB16" s="22">
-        <f>[2]Jan!$AI$1</f>
+        <f>[2]Apr!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DC16" s="22"/>
@@ -20583,7 +20583,7 @@
       <c r="DK16" s="21"/>
       <c r="DL16" s="22"/>
       <c r="DM16" s="22">
-        <f>[2]Feb!$AI$1</f>
+        <f>[2]May!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DN16" s="22"/>
@@ -20600,7 +20600,7 @@
       <c r="DV16" s="21"/>
       <c r="DW16" s="22"/>
       <c r="DX16" s="22">
-        <f>[2]Mar!$AI$1</f>
+        <f>[2]Jun!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DY16" s="22"/>
@@ -20637,7 +20637,7 @@
       <c r="D17" s="22"/>
       <c r="E17" s="21"/>
       <c r="F17" s="22">
-        <f>-[3]Apr!$U$1</f>
+        <f>-[3]Jul!$U$1</f>
         <v>0</v>
       </c>
       <c r="G17" s="22"/>
@@ -20657,7 +20657,7 @@
       </c>
       <c r="P17" s="21"/>
       <c r="Q17" s="22">
-        <f>-[3]May!$U$1</f>
+        <f>-[3]Aug!$U$1</f>
         <v>0</v>
       </c>
       <c r="R17" s="22"/>
@@ -20677,7 +20677,7 @@
       </c>
       <c r="AA17" s="21"/>
       <c r="AB17" s="22">
-        <f>-[3]Jun!$U$1</f>
+        <f>-[3]Sep!$U$1</f>
         <v>0</v>
       </c>
       <c r="AC17" s="22"/>
@@ -20697,7 +20697,7 @@
       </c>
       <c r="AL17" s="21"/>
       <c r="AM17" s="22">
-        <f>-[3]Jul!$U$1</f>
+        <f>-[3]Oct!$U$1</f>
         <v>0</v>
       </c>
       <c r="AN17" s="22"/>
@@ -20717,7 +20717,7 @@
       </c>
       <c r="AW17" s="21"/>
       <c r="AX17" s="22">
-        <f>-[3]Aug!$U$1</f>
+        <f>-[3]Nov!$U$1</f>
         <v>0</v>
       </c>
       <c r="AY17" s="22"/>
@@ -20737,7 +20737,7 @@
       </c>
       <c r="BH17" s="21"/>
       <c r="BI17" s="22">
-        <f>-[3]Sep!$U$1</f>
+        <f>-[3]Dec!$U$1</f>
         <v>0</v>
       </c>
       <c r="BJ17" s="22"/>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="BS17" s="21"/>
       <c r="BT17" s="22">
-        <f>-[3]Oct!$U$1</f>
+        <f>-[3]Jan!$U$1</f>
         <v>0</v>
       </c>
       <c r="BU17" s="22"/>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="CD17" s="21"/>
       <c r="CE17" s="22">
-        <f>-[3]Nov!$U$1</f>
+        <f>-[3]Feb!$U$1</f>
         <v>0</v>
       </c>
       <c r="CF17" s="22"/>
@@ -20797,7 +20797,7 @@
       </c>
       <c r="CO17" s="21"/>
       <c r="CP17" s="22">
-        <f>-[3]Dec!$U$1</f>
+        <f>-[3]Mar!$U$1</f>
         <v>0</v>
       </c>
       <c r="CQ17" s="22"/>
@@ -20817,7 +20817,7 @@
       </c>
       <c r="CZ17" s="21"/>
       <c r="DA17" s="22">
-        <f>-[3]Jan!$U$1</f>
+        <f>-[3]Apr!$U$1</f>
         <v>0</v>
       </c>
       <c r="DB17" s="22"/>
@@ -20837,7 +20837,7 @@
       </c>
       <c r="DK17" s="21"/>
       <c r="DL17" s="22">
-        <f>-[3]Feb!$U$1</f>
+        <f>-[3]May!$U$1</f>
         <v>0</v>
       </c>
       <c r="DM17" s="22"/>
@@ -20857,7 +20857,7 @@
       </c>
       <c r="DV17" s="21"/>
       <c r="DW17" s="22">
-        <f>-[3]Mar!$U$1</f>
+        <f>-[3]Jun!$U$1</f>
         <v>0</v>
       </c>
       <c r="DX17" s="22"/>
@@ -21268,24 +21268,24 @@
       </c>
       <c r="E20" s="21"/>
       <c r="F20" s="22">
-        <f>[3]Apr!$F$1-[3]Apr!$V$1</f>
+        <f>[3]Jul!$F$1-[3]Jul!$V$1</f>
         <v>0</v>
       </c>
       <c r="G20" s="22"/>
       <c r="H20" s="22">
-        <f>-[4]Apr!$J$1</f>
+        <f>-[4]Jul!$J$1</f>
         <v>0</v>
       </c>
       <c r="I20" s="22">
-        <f>-[5]Apr!$J$1</f>
+        <f>-[5]Jul!$J$1</f>
         <v>0</v>
       </c>
       <c r="J20" s="22">
-        <f>-[6]Apr!$J$1</f>
+        <f>-[6]Jul!$J$1</f>
         <v>0</v>
       </c>
       <c r="K20" s="22">
-        <f>-[7]Apr!$J$1</f>
+        <f>-[7]Jul!$J$1</f>
         <v>0</v>
       </c>
       <c r="L20" s="22"/>
@@ -21296,24 +21296,24 @@
       </c>
       <c r="P20" s="21"/>
       <c r="Q20" s="22">
-        <f>[3]May!$F$1-[3]May!$V$1</f>
+        <f>[3]Aug!$F$1-[3]Aug!$V$1</f>
         <v>0</v>
       </c>
       <c r="R20" s="22"/>
       <c r="S20" s="22">
-        <f>-[4]May!$J$1</f>
+        <f>-[4]Aug!$J$1</f>
         <v>0</v>
       </c>
       <c r="T20" s="22">
-        <f>-[5]May!$J$1</f>
+        <f>-[5]Aug!$J$1</f>
         <v>0</v>
       </c>
       <c r="U20" s="22">
-        <f>-[6]May!$J$1</f>
+        <f>-[6]Aug!$J$1</f>
         <v>0</v>
       </c>
       <c r="V20" s="22">
-        <f>-[7]May!$J$1</f>
+        <f>-[7]Aug!$J$1</f>
         <v>0</v>
       </c>
       <c r="W20" s="22"/>
@@ -21327,24 +21327,24 @@
       </c>
       <c r="AA20" s="21"/>
       <c r="AB20" s="22">
-        <f>[3]Jun!$F$1-[3]Jun!$V$1</f>
+        <f>[3]Sep!$F$1-[3]Sep!$V$1</f>
         <v>0</v>
       </c>
       <c r="AC20" s="22"/>
       <c r="AD20" s="22">
-        <f>-[4]Jun!$J$1</f>
+        <f>-[4]Sep!$J$1</f>
         <v>0</v>
       </c>
       <c r="AE20" s="22">
-        <f>-[5]Jun!$J$1</f>
+        <f>-[5]Sep!$J$1</f>
         <v>0</v>
       </c>
       <c r="AF20" s="22">
-        <f>-[6]Jun!$J$1</f>
+        <f>-[6]Sep!$J$1</f>
         <v>0</v>
       </c>
       <c r="AG20" s="22">
-        <f>-[7]Jun!$J$1</f>
+        <f>-[7]Sep!$J$1</f>
         <v>0</v>
       </c>
       <c r="AH20" s="22"/>
@@ -21356,24 +21356,24 @@
       </c>
       <c r="AL20" s="21"/>
       <c r="AM20" s="22">
-        <f>[3]Jul!$F$1-[3]Jul!$V$1</f>
+        <f>[3]Oct!$F$1-[3]Oct!$V$1</f>
         <v>0</v>
       </c>
       <c r="AN20" s="22"/>
       <c r="AO20" s="22">
-        <f>-[4]Jul!$J$1</f>
+        <f>-[4]Oct!$J$1</f>
         <v>0</v>
       </c>
       <c r="AP20" s="22">
-        <f>-[5]Jul!$J$1</f>
+        <f>-[5]Oct!$J$1</f>
         <v>0</v>
       </c>
       <c r="AQ20" s="22">
-        <f>-[6]Jul!$J$1</f>
+        <f>-[6]Oct!$J$1</f>
         <v>0</v>
       </c>
       <c r="AR20" s="22">
-        <f>-[7]Jul!$J$1</f>
+        <f>-[7]Oct!$J$1</f>
         <v>0</v>
       </c>
       <c r="AS20" s="22"/>
@@ -21385,24 +21385,24 @@
       </c>
       <c r="AW20" s="21"/>
       <c r="AX20" s="22">
-        <f>[3]Aug!$F$1-[3]Aug!$V$1</f>
+        <f>[3]Nov!$F$1-[3]Nov!$V$1</f>
         <v>0</v>
       </c>
       <c r="AY20" s="22"/>
       <c r="AZ20" s="22">
-        <f>-[4]Aug!$J$1</f>
+        <f>-[4]Nov!$J$1</f>
         <v>0</v>
       </c>
       <c r="BA20" s="22">
-        <f>-[5]Aug!$J$1</f>
+        <f>-[5]Nov!$J$1</f>
         <v>0</v>
       </c>
       <c r="BB20" s="22">
-        <f>-[6]Aug!$J$1</f>
+        <f>-[6]Nov!$J$1</f>
         <v>0</v>
       </c>
       <c r="BC20" s="22">
-        <f>-[7]Aug!$J$1</f>
+        <f>-[7]Nov!$J$1</f>
         <v>0</v>
       </c>
       <c r="BD20" s="22"/>
@@ -21414,24 +21414,24 @@
       </c>
       <c r="BH20" s="21"/>
       <c r="BI20" s="22">
-        <f>[3]Sep!$F$1-[3]Sep!$V$1</f>
+        <f>[3]Dec!$F$1-[3]Dec!$V$1</f>
         <v>0</v>
       </c>
       <c r="BJ20" s="22"/>
       <c r="BK20" s="22">
-        <f>-[4]Sep!$J$1</f>
+        <f>-[4]Dec!$J$1</f>
         <v>0</v>
       </c>
       <c r="BL20" s="22">
-        <f>-[5]Sep!$J$1</f>
+        <f>-[5]Dec!$J$1</f>
         <v>0</v>
       </c>
       <c r="BM20" s="22">
-        <f>-[6]Sep!$J$1</f>
+        <f>-[6]Dec!$J$1</f>
         <v>0</v>
       </c>
       <c r="BN20" s="22">
-        <f>-[7]Sep!$J$1</f>
+        <f>-[7]Dec!$J$1</f>
         <v>0</v>
       </c>
       <c r="BO20" s="22"/>
@@ -21443,24 +21443,24 @@
       </c>
       <c r="BS20" s="21"/>
       <c r="BT20" s="22">
-        <f>[3]Oct!$F$1-[3]Oct!$V$1</f>
+        <f>[3]Jan!$F$1-[3]Jan!$V$1</f>
         <v>0</v>
       </c>
       <c r="BU20" s="22"/>
       <c r="BV20" s="22">
-        <f>-[4]Oct!$J$1</f>
+        <f>-[4]Jan!$J$1</f>
         <v>0</v>
       </c>
       <c r="BW20" s="22">
-        <f>-[5]Oct!$J$1</f>
+        <f>-[5]Jan!$J$1</f>
         <v>0</v>
       </c>
       <c r="BX20" s="22">
-        <f>-[6]Oct!$J$1</f>
+        <f>-[6]Jan!$J$1</f>
         <v>0</v>
       </c>
       <c r="BY20" s="22">
-        <f>-[7]Oct!$J$1</f>
+        <f>-[7]Jan!$J$1</f>
         <v>0</v>
       </c>
       <c r="BZ20" s="22"/>
@@ -21472,24 +21472,24 @@
       </c>
       <c r="CD20" s="21"/>
       <c r="CE20" s="22">
-        <f>[3]Nov!$F$1-[3]Nov!$V$1</f>
+        <f>[3]Feb!$F$1-[3]Feb!$V$1</f>
         <v>0</v>
       </c>
       <c r="CF20" s="22"/>
       <c r="CG20" s="22">
-        <f>-[4]Nov!$J$1</f>
+        <f>-[4]Feb!$J$1</f>
         <v>0</v>
       </c>
       <c r="CH20" s="22">
-        <f>-[5]Nov!$J$1</f>
+        <f>-[5]Feb!$J$1</f>
         <v>0</v>
       </c>
       <c r="CI20" s="22">
-        <f>-[6]Nov!$J$1</f>
+        <f>-[6]Feb!$J$1</f>
         <v>0</v>
       </c>
       <c r="CJ20" s="22">
-        <f>-[7]Nov!$J$1</f>
+        <f>-[7]Feb!$J$1</f>
         <v>0</v>
       </c>
       <c r="CK20" s="22"/>
@@ -21501,24 +21501,24 @@
       </c>
       <c r="CO20" s="21"/>
       <c r="CP20" s="22">
-        <f>[3]Dec!$F$1-[3]Dec!$V$1</f>
+        <f>[3]Mar!$F$1-[3]Mar!$V$1</f>
         <v>0</v>
       </c>
       <c r="CQ20" s="22"/>
       <c r="CR20" s="22">
-        <f>-[4]Dec!$J$1</f>
+        <f>-[4]Mar!$J$1</f>
         <v>0</v>
       </c>
       <c r="CS20" s="22">
-        <f>-[5]Dec!$J$1</f>
+        <f>-[5]Mar!$J$1</f>
         <v>0</v>
       </c>
       <c r="CT20" s="22">
-        <f>-[6]Dec!$J$1</f>
+        <f>-[6]Mar!$J$1</f>
         <v>0</v>
       </c>
       <c r="CU20" s="22">
-        <f>-[7]Dec!$J$1</f>
+        <f>-[7]Mar!$J$1</f>
         <v>0</v>
       </c>
       <c r="CV20" s="22"/>
@@ -21530,24 +21530,24 @@
       </c>
       <c r="CZ20" s="21"/>
       <c r="DA20" s="22">
-        <f>[3]Jan!$F$1-[3]Jan!$V$1</f>
+        <f>[3]Apr!$F$1-[3]Apr!$V$1</f>
         <v>0</v>
       </c>
       <c r="DB20" s="22"/>
       <c r="DC20" s="22">
-        <f>-[4]Jan!$J$1</f>
+        <f>-[4]Apr!$J$1</f>
         <v>0</v>
       </c>
       <c r="DD20" s="22">
-        <f>-[5]Jan!$J$1</f>
+        <f>-[5]Apr!$J$1</f>
         <v>0</v>
       </c>
       <c r="DE20" s="22">
-        <f>-[6]Jan!$J$1</f>
+        <f>-[6]Apr!$J$1</f>
         <v>0</v>
       </c>
       <c r="DF20" s="22">
-        <f>-[7]Jan!$J$1</f>
+        <f>-[7]Apr!$J$1</f>
         <v>0</v>
       </c>
       <c r="DG20" s="22"/>
@@ -21559,24 +21559,24 @@
       </c>
       <c r="DK20" s="21"/>
       <c r="DL20" s="22">
-        <f>[3]Feb!$F$1-[3]Feb!$V$1</f>
+        <f>[3]May!$F$1-[3]May!$V$1</f>
         <v>0</v>
       </c>
       <c r="DM20" s="22"/>
       <c r="DN20" s="22">
-        <f>-[4]Feb!$J$1</f>
+        <f>-[4]May!$J$1</f>
         <v>0</v>
       </c>
       <c r="DO20" s="22">
-        <f>-[5]Feb!$J$1</f>
+        <f>-[5]May!$J$1</f>
         <v>0</v>
       </c>
       <c r="DP20" s="22">
-        <f>-[6]Feb!$J$1</f>
+        <f>-[6]May!$J$1</f>
         <v>0</v>
       </c>
       <c r="DQ20" s="22">
-        <f>-[7]Feb!$J$1</f>
+        <f>-[7]May!$J$1</f>
         <v>0</v>
       </c>
       <c r="DR20" s="22"/>
@@ -21588,24 +21588,24 @@
       </c>
       <c r="DV20" s="21"/>
       <c r="DW20" s="22">
-        <f>[3]Mar!$F$1-[3]Mar!$V$1</f>
+        <f>[3]Jun!$F$1-[3]Jun!$V$1</f>
         <v>0</v>
       </c>
       <c r="DX20" s="22"/>
       <c r="DY20" s="22">
-        <f>-[4]Mar!$J$1</f>
+        <f>-[4]Jun!$J$1</f>
         <v>0</v>
       </c>
       <c r="DZ20" s="22">
-        <f>-[5]Mar!$J$1</f>
+        <f>-[5]Jun!$J$1</f>
         <v>0</v>
       </c>
       <c r="EA20" s="22">
-        <f>-[6]Mar!$J$1</f>
+        <f>-[6]Jun!$J$1</f>
         <v>0</v>
       </c>
       <c r="EB20" s="22">
-        <f>-[7]Mar!$J$1</f>
+        <f>-[7]Jun!$J$1</f>
         <v>0</v>
       </c>
       <c r="EC20" s="22"/>
@@ -21784,7 +21784,7 @@
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
       <c r="H22" s="22">
-        <f>[4]Apr!$F$1-[4]Apr!$X$1</f>
+        <f>[4]Jul!$F$1-[4]Jul!$X$1</f>
         <v>0</v>
       </c>
       <c r="I22" s="22"/>
@@ -21800,7 +21800,7 @@
       <c r="Q22" s="22"/>
       <c r="R22" s="22"/>
       <c r="S22" s="22">
-        <f>[4]May!$F$1-[4]May!$X$1</f>
+        <f>[4]Aug!$F$1-[4]Aug!$X$1</f>
         <v>0</v>
       </c>
       <c r="T22" s="22"/>
@@ -21817,7 +21817,7 @@
       <c r="AB22" s="22"/>
       <c r="AC22" s="22"/>
       <c r="AD22" s="22">
-        <f>[4]Jun!$F$1-[4]Jun!$X$1</f>
+        <f>[4]Sep!$F$1-[4]Sep!$X$1</f>
         <v>0</v>
       </c>
       <c r="AE22" s="22"/>
@@ -21834,7 +21834,7 @@
       <c r="AM22" s="22"/>
       <c r="AN22" s="22"/>
       <c r="AO22" s="22">
-        <f>[4]Jul!$F$1-[4]Jul!$X$1</f>
+        <f>[4]Oct!$F$1-[4]Oct!$X$1</f>
         <v>0</v>
       </c>
       <c r="AP22" s="22"/>
@@ -21851,7 +21851,7 @@
       <c r="AX22" s="22"/>
       <c r="AY22" s="22"/>
       <c r="AZ22" s="22">
-        <f>[4]Aug!$F$1-[4]Aug!$X$1</f>
+        <f>[4]Nov!$F$1-[4]Nov!$X$1</f>
         <v>0</v>
       </c>
       <c r="BA22" s="22"/>
@@ -21868,7 +21868,7 @@
       <c r="BI22" s="22"/>
       <c r="BJ22" s="22"/>
       <c r="BK22" s="22">
-        <f>[4]Sep!$F$1-[4]Sep!$X$1</f>
+        <f>[4]Dec!$F$1-[4]Dec!$X$1</f>
         <v>0</v>
       </c>
       <c r="BL22" s="22"/>
@@ -21885,7 +21885,7 @@
       <c r="BT22" s="22"/>
       <c r="BU22" s="22"/>
       <c r="BV22" s="22">
-        <f>[4]Oct!$F$1-[4]Oct!$X$1</f>
+        <f>[4]Jan!$F$1-[4]Jan!$X$1</f>
         <v>0</v>
       </c>
       <c r="BW22" s="22"/>
@@ -21902,7 +21902,7 @@
       <c r="CE22" s="22"/>
       <c r="CF22" s="22"/>
       <c r="CG22" s="22">
-        <f>[4]Nov!$F$1-[4]Nov!$X$1</f>
+        <f>[4]Feb!$F$1-[4]Feb!$X$1</f>
         <v>0</v>
       </c>
       <c r="CH22" s="22"/>
@@ -21919,7 +21919,7 @@
       <c r="CP22" s="22"/>
       <c r="CQ22" s="22"/>
       <c r="CR22" s="22">
-        <f>[4]Dec!$F$1-[4]Dec!$X$1</f>
+        <f>[4]Mar!$F$1-[4]Mar!$X$1</f>
         <v>0</v>
       </c>
       <c r="CS22" s="22"/>
@@ -21936,7 +21936,7 @@
       <c r="DA22" s="22"/>
       <c r="DB22" s="22"/>
       <c r="DC22" s="22">
-        <f>[4]Jan!$F$1-[4]Jan!$X$1</f>
+        <f>[4]Apr!$F$1-[4]Apr!$X$1</f>
         <v>0</v>
       </c>
       <c r="DD22" s="22"/>
@@ -21953,7 +21953,7 @@
       <c r="DL22" s="22"/>
       <c r="DM22" s="22"/>
       <c r="DN22" s="22">
-        <f>[4]Feb!$F$1-[4]Feb!$X$1</f>
+        <f>[4]May!$F$1-[4]May!$X$1</f>
         <v>0</v>
       </c>
       <c r="DO22" s="22"/>
@@ -21970,7 +21970,7 @@
       <c r="DW22" s="22"/>
       <c r="DX22" s="22"/>
       <c r="DY22" s="22">
-        <f>[4]Mar!$F$1-[4]Mar!$X$1</f>
+        <f>[4]Jun!$F$1-[4]Jun!$X$1</f>
         <v>0</v>
       </c>
       <c r="DZ22" s="22"/>
@@ -22008,7 +22008,7 @@
       <c r="G23" s="22"/>
       <c r="H23" s="22"/>
       <c r="I23" s="22">
-        <f>[5]Apr!$F$1-[5]Apr!$X$1</f>
+        <f>[5]Jul!$F$1-[5]Jul!$X$1</f>
         <v>0</v>
       </c>
       <c r="J23" s="22"/>
@@ -22024,7 +22024,7 @@
       <c r="R23" s="22"/>
       <c r="S23" s="22"/>
       <c r="T23" s="22">
-        <f>[5]May!$F$1-[5]May!$X$1</f>
+        <f>[5]Aug!$F$1-[5]Aug!$X$1</f>
         <v>0</v>
       </c>
       <c r="U23" s="22"/>
@@ -22041,7 +22041,7 @@
       <c r="AC23" s="22"/>
       <c r="AD23" s="22"/>
       <c r="AE23" s="22">
-        <f>[5]Jun!$F$1-[5]Jun!$X$1</f>
+        <f>[5]Sep!$F$1-[5]Sep!$X$1</f>
         <v>0</v>
       </c>
       <c r="AF23" s="22"/>
@@ -22058,7 +22058,7 @@
       <c r="AN23" s="22"/>
       <c r="AO23" s="22"/>
       <c r="AP23" s="22">
-        <f>[5]Jul!$F$1-[5]Jul!$X$1</f>
+        <f>[5]Oct!$F$1-[5]Oct!$X$1</f>
         <v>0</v>
       </c>
       <c r="AQ23" s="22"/>
@@ -22075,7 +22075,7 @@
       <c r="AY23" s="22"/>
       <c r="AZ23" s="22"/>
       <c r="BA23" s="22">
-        <f>[5]Aug!$F$1-[5]Aug!$X$1</f>
+        <f>[5]Nov!$F$1-[5]Nov!$X$1</f>
         <v>0</v>
       </c>
       <c r="BB23" s="22"/>
@@ -22092,7 +22092,7 @@
       <c r="BJ23" s="22"/>
       <c r="BK23" s="22"/>
       <c r="BL23" s="22">
-        <f>[5]Sep!$F$1-[5]Sep!$X$1</f>
+        <f>[5]Dec!$F$1-[5]Dec!$X$1</f>
         <v>0</v>
       </c>
       <c r="BM23" s="22"/>
@@ -22109,7 +22109,7 @@
       <c r="BU23" s="22"/>
       <c r="BV23" s="22"/>
       <c r="BW23" s="22">
-        <f>[5]Oct!$F$1-[5]Oct!$X$1</f>
+        <f>[5]Jan!$F$1-[5]Jan!$X$1</f>
         <v>0</v>
       </c>
       <c r="BX23" s="22"/>
@@ -22126,7 +22126,7 @@
       <c r="CF23" s="22"/>
       <c r="CG23" s="22"/>
       <c r="CH23" s="22">
-        <f>[5]Nov!$F$1-[5]Nov!$X$1</f>
+        <f>[5]Feb!$F$1-[5]Feb!$X$1</f>
         <v>0</v>
       </c>
       <c r="CI23" s="22"/>
@@ -22143,7 +22143,7 @@
       <c r="CQ23" s="22"/>
       <c r="CR23" s="22"/>
       <c r="CS23" s="22">
-        <f>[5]Dec!$F$1-[5]Dec!$X$1</f>
+        <f>[5]Mar!$F$1-[5]Mar!$X$1</f>
         <v>0</v>
       </c>
       <c r="CT23" s="22"/>
@@ -22160,7 +22160,7 @@
       <c r="DB23" s="22"/>
       <c r="DC23" s="22"/>
       <c r="DD23" s="22">
-        <f>[5]Jan!$F$1-[5]Jan!$X$1</f>
+        <f>[5]Apr!$F$1-[5]Apr!$X$1</f>
         <v>0</v>
       </c>
       <c r="DE23" s="22"/>
@@ -22177,7 +22177,7 @@
       <c r="DM23" s="22"/>
       <c r="DN23" s="22"/>
       <c r="DO23" s="22">
-        <f>[5]Feb!$F$1-[5]Feb!$X$1</f>
+        <f>[5]May!$F$1-[5]May!$X$1</f>
         <v>0</v>
       </c>
       <c r="DP23" s="22"/>
@@ -22194,7 +22194,7 @@
       <c r="DX23" s="22"/>
       <c r="DY23" s="22"/>
       <c r="DZ23" s="22">
-        <f>[5]Mar!$F$1-[5]Mar!$X$1</f>
+        <f>[5]Jun!$F$1-[5]Jun!$X$1</f>
         <v>0</v>
       </c>
       <c r="EA23" s="22"/>
@@ -22232,7 +22232,7 @@
       <c r="H24" s="22"/>
       <c r="I24" s="22"/>
       <c r="J24" s="22">
-        <f>[6]Apr!$F$1-[6]Apr!$X$1</f>
+        <f>[6]Jul!$F$1-[6]Jul!$X$1</f>
         <v>0</v>
       </c>
       <c r="K24" s="22"/>
@@ -22248,7 +22248,7 @@
       <c r="S24" s="22"/>
       <c r="T24" s="22"/>
       <c r="U24" s="22">
-        <f>[6]May!$F$1-[6]May!$X$1</f>
+        <f>[6]Aug!$F$1-[6]Aug!$X$1</f>
         <v>0</v>
       </c>
       <c r="V24" s="22"/>
@@ -22265,7 +22265,7 @@
       <c r="AD24" s="22"/>
       <c r="AE24" s="22"/>
       <c r="AF24" s="22">
-        <f>[6]Jun!$F$1-[6]Jun!$X$1</f>
+        <f>[6]Sep!$F$1-[6]Sep!$X$1</f>
         <v>0</v>
       </c>
       <c r="AG24" s="22"/>
@@ -22282,7 +22282,7 @@
       <c r="AO24" s="22"/>
       <c r="AP24" s="22"/>
       <c r="AQ24" s="22">
-        <f>[6]Jul!$F$1-[6]Jul!$X$1</f>
+        <f>[6]Oct!$F$1-[6]Oct!$X$1</f>
         <v>0</v>
       </c>
       <c r="AR24" s="22"/>
@@ -22299,7 +22299,7 @@
       <c r="AZ24" s="22"/>
       <c r="BA24" s="22"/>
       <c r="BB24" s="22">
-        <f>[6]Aug!$F$1-[6]Aug!$X$1</f>
+        <f>[6]Nov!$F$1-[6]Nov!$X$1</f>
         <v>0</v>
       </c>
       <c r="BC24" s="22"/>
@@ -22316,7 +22316,7 @@
       <c r="BK24" s="22"/>
       <c r="BL24" s="22"/>
       <c r="BM24" s="22">
-        <f>[6]Sep!$F$1-[6]Sep!$X$1</f>
+        <f>[6]Dec!$F$1-[6]Dec!$X$1</f>
         <v>0</v>
       </c>
       <c r="BN24" s="22"/>
@@ -22333,7 +22333,7 @@
       <c r="BV24" s="22"/>
       <c r="BW24" s="22"/>
       <c r="BX24" s="22">
-        <f>[6]Oct!$F$1-[6]Oct!$X$1</f>
+        <f>[6]Jan!$F$1-[6]Jan!$X$1</f>
         <v>0</v>
       </c>
       <c r="BY24" s="22"/>
@@ -22350,7 +22350,7 @@
       <c r="CG24" s="22"/>
       <c r="CH24" s="22"/>
       <c r="CI24" s="22">
-        <f>[6]Nov!$F$1-[6]Nov!$X$1</f>
+        <f>[6]Feb!$F$1-[6]Feb!$X$1</f>
         <v>0</v>
       </c>
       <c r="CJ24" s="22"/>
@@ -22367,7 +22367,7 @@
       <c r="CR24" s="22"/>
       <c r="CS24" s="22"/>
       <c r="CT24" s="22">
-        <f>[6]Dec!$F$1-[6]Dec!$X$1</f>
+        <f>[6]Mar!$F$1-[6]Mar!$X$1</f>
         <v>0</v>
       </c>
       <c r="CU24" s="22"/>
@@ -22384,7 +22384,7 @@
       <c r="DC24" s="22"/>
       <c r="DD24" s="22"/>
       <c r="DE24" s="22">
-        <f>[6]Jan!$F$1-[6]Jan!$X$1</f>
+        <f>[6]Apr!$F$1-[6]Apr!$X$1</f>
         <v>0</v>
       </c>
       <c r="DF24" s="22"/>
@@ -22401,7 +22401,7 @@
       <c r="DN24" s="22"/>
       <c r="DO24" s="22"/>
       <c r="DP24" s="22">
-        <f>[6]Feb!$F$1-[6]Feb!$X$1</f>
+        <f>[6]May!$F$1-[6]May!$X$1</f>
         <v>0</v>
       </c>
       <c r="DQ24" s="22"/>
@@ -22418,7 +22418,7 @@
       <c r="DY24" s="22"/>
       <c r="DZ24" s="22"/>
       <c r="EA24" s="22">
-        <f>[6]Mar!$F$1-[6]Mar!$X$1</f>
+        <f>[6]Jun!$F$1-[6]Jun!$X$1</f>
         <v>0</v>
       </c>
       <c r="EB24" s="22"/>
@@ -22456,7 +22456,7 @@
       <c r="I25" s="22"/>
       <c r="J25" s="22"/>
       <c r="K25" s="22">
-        <f>[7]Apr!$F$1-[7]Apr!$U$1</f>
+        <f>[7]Jul!$F$1-[7]Jul!$U$1</f>
         <v>0</v>
       </c>
       <c r="L25" s="22"/>
@@ -22472,7 +22472,7 @@
       <c r="T25" s="22"/>
       <c r="U25" s="22"/>
       <c r="V25" s="22">
-        <f>[7]May!$F$1-[7]May!$U$1</f>
+        <f>[7]Aug!$F$1-[7]Aug!$U$1</f>
         <v>0</v>
       </c>
       <c r="W25" s="22"/>
@@ -22489,7 +22489,7 @@
       <c r="AE25" s="22"/>
       <c r="AF25" s="22"/>
       <c r="AG25" s="22">
-        <f>[7]Jun!$F$1-[7]Jun!$U$1</f>
+        <f>[7]Sep!$F$1-[7]Sep!$U$1</f>
         <v>0</v>
       </c>
       <c r="AH25" s="22"/>
@@ -22506,7 +22506,7 @@
       <c r="AP25" s="22"/>
       <c r="AQ25" s="22"/>
       <c r="AR25" s="22">
-        <f>[7]Jul!$F$1-[7]Jul!$U$1</f>
+        <f>[7]Oct!$F$1-[7]Oct!$U$1</f>
         <v>0</v>
       </c>
       <c r="AS25" s="22"/>
@@ -22523,7 +22523,7 @@
       <c r="BA25" s="22"/>
       <c r="BB25" s="22"/>
       <c r="BC25" s="22">
-        <f>[7]Aug!$F$1-[7]Aug!$U$1</f>
+        <f>[7]Nov!$F$1-[7]Nov!$U$1</f>
         <v>0</v>
       </c>
       <c r="BD25" s="22"/>
@@ -22540,7 +22540,7 @@
       <c r="BL25" s="22"/>
       <c r="BM25" s="22"/>
       <c r="BN25" s="22">
-        <f>[7]Sep!$F$1-[7]Sep!$U$1</f>
+        <f>[7]Dec!$F$1-[7]Dec!$U$1</f>
         <v>0</v>
       </c>
       <c r="BO25" s="22"/>
@@ -22557,7 +22557,7 @@
       <c r="BW25" s="22"/>
       <c r="BX25" s="22"/>
       <c r="BY25" s="22">
-        <f>[7]Oct!$F$1-[7]Oct!$U$1</f>
+        <f>[7]Jan!$F$1-[7]Jan!$U$1</f>
         <v>0</v>
       </c>
       <c r="BZ25" s="22"/>
@@ -22574,7 +22574,7 @@
       <c r="CH25" s="22"/>
       <c r="CI25" s="22"/>
       <c r="CJ25" s="22">
-        <f>[7]Nov!$F$1-[7]Nov!$U$1</f>
+        <f>[7]Feb!$F$1-[7]Feb!$U$1</f>
         <v>0</v>
       </c>
       <c r="CK25" s="22"/>
@@ -22591,7 +22591,7 @@
       <c r="CS25" s="22"/>
       <c r="CT25" s="22"/>
       <c r="CU25" s="22">
-        <f>[7]Dec!$F$1-[7]Dec!$U$1</f>
+        <f>[7]Mar!$F$1-[7]Mar!$U$1</f>
         <v>0</v>
       </c>
       <c r="CV25" s="22"/>
@@ -22608,7 +22608,7 @@
       <c r="DD25" s="22"/>
       <c r="DE25" s="22"/>
       <c r="DF25" s="22">
-        <f>[7]Jan!$F$1-[7]Jan!$U$1</f>
+        <f>[7]Apr!$F$1-[7]Apr!$U$1</f>
         <v>0</v>
       </c>
       <c r="DG25" s="22"/>
@@ -22625,7 +22625,7 @@
       <c r="DO25" s="22"/>
       <c r="DP25" s="22"/>
       <c r="DQ25" s="22">
-        <f>[7]Feb!$F$1-[7]Feb!$U$1</f>
+        <f>[7]May!$F$1-[7]May!$U$1</f>
         <v>0</v>
       </c>
       <c r="DR25" s="22"/>
@@ -22642,7 +22642,7 @@
       <c r="DZ25" s="22"/>
       <c r="EA25" s="22"/>
       <c r="EB25" s="22">
-        <f>[7]Mar!$F$1-[7]Mar!$U$1</f>
+        <f>[7]Jun!$F$1-[7]Jun!$U$1</f>
         <v>0</v>
       </c>
       <c r="EC25" s="22"/>
@@ -22677,19 +22677,19 @@
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
       <c r="H26" s="22">
-        <f>-[4]Apr!$G$1-[4]Apr!$H$1-[4]Apr!$I$1+[4]Apr!$Y$1+[4]Apr!$Z$1+[4]Apr!$AA$1</f>
+        <f>-[4]Jul!$G$1-[4]Jul!$H$1-[4]Jul!$I$1+[4]Jul!$Y$1+[4]Jul!$Z$1+[4]Jul!$AA$1</f>
         <v>0</v>
       </c>
       <c r="I26" s="22">
-        <f>-[5]Apr!$G$1-[5]Apr!$H$1-[5]Apr!$I$1+[5]Apr!$Y$1+[5]Apr!$Z$1+[5]Apr!$AA$1</f>
+        <f>-[5]Jul!$G$1-[5]Jul!$H$1-[5]Jul!$I$1+[5]Jul!$Y$1+[5]Jul!$Z$1+[5]Jul!$AA$1</f>
         <v>0</v>
       </c>
       <c r="J26" s="22">
-        <f>-[6]Apr!$G$1-[6]Apr!$H$1-[6]Apr!$I$1+[6]Apr!$Y$1+[6]Apr!$Z$1+[6]Apr!$AA$1</f>
+        <f>-[6]Jul!$G$1-[6]Jul!$H$1-[6]Jul!$I$1+[6]Jul!$Y$1+[6]Jul!$Z$1+[6]Jul!$AA$1</f>
         <v>0</v>
       </c>
       <c r="K26" s="22">
-        <f>-[7]Apr!$G$1-[7]Apr!$H$1-[7]Apr!$I$1+[7]Apr!$V$1+[7]Apr!$W$1+[7]Apr!$X$1</f>
+        <f>-[7]Jul!$G$1-[7]Jul!$H$1-[7]Jul!$I$1+[7]Jul!$V$1+[7]Jul!$W$1+[7]Jul!$X$1</f>
         <v>0</v>
       </c>
       <c r="L26" s="22"/>
@@ -22702,19 +22702,19 @@
       <c r="Q26" s="22"/>
       <c r="R26" s="22"/>
       <c r="S26" s="22">
-        <f>-[4]May!$G$1-[4]May!$H$1-[4]May!$I$1+[4]May!$Y$1+[4]May!$Z$1+[4]May!$AA$1</f>
+        <f>-[4]Aug!$G$1-[4]Aug!$H$1-[4]Aug!$I$1+[4]Aug!$Y$1+[4]Aug!$Z$1+[4]Aug!$AA$1</f>
         <v>0</v>
       </c>
       <c r="T26" s="22">
-        <f>-[5]May!$G$1-[5]May!$H$1-[5]May!$I$1+[5]May!$Y$1+[5]May!$Z$1+[5]May!$AA$1</f>
+        <f>-[5]Aug!$G$1-[5]Aug!$H$1-[5]Aug!$I$1+[5]Aug!$Y$1+[5]Aug!$Z$1+[5]Aug!$AA$1</f>
         <v>0</v>
       </c>
       <c r="U26" s="22">
-        <f>-[6]May!$G$1-[6]May!$H$1-[6]May!$I$1+[6]May!$Y$1+[6]May!$Z$1+[6]May!$AA$1</f>
+        <f>-[6]Aug!$G$1-[6]Aug!$H$1-[6]Aug!$I$1+[6]Aug!$Y$1+[6]Aug!$Z$1+[6]Aug!$AA$1</f>
         <v>0</v>
       </c>
       <c r="V26" s="22">
-        <f>-[7]May!$G$1-[7]May!$H$1-[7]May!$I$1+[7]May!$V$1+[7]May!$W$1+[7]May!$X$1</f>
+        <f>-[7]Aug!$G$1-[7]Aug!$H$1-[7]Aug!$I$1+[7]Aug!$V$1+[7]Aug!$W$1+[7]Aug!$X$1</f>
         <v>0</v>
       </c>
       <c r="W26" s="22"/>
@@ -22728,19 +22728,19 @@
       <c r="AB26" s="22"/>
       <c r="AC26" s="22"/>
       <c r="AD26" s="22">
-        <f>-[4]Jun!$G$1-[4]Jun!$H$1-[4]Jun!$I$1+[4]Jun!$Y$1+[4]Jun!$Z$1+[4]Jun!$AA$1</f>
+        <f>-[4]Sep!$G$1-[4]Sep!$H$1-[4]Sep!$I$1+[4]Sep!$Y$1+[4]Sep!$Z$1+[4]Sep!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AE26" s="22">
-        <f>-[5]Jun!$G$1-[5]Jun!$H$1-[5]Jun!$I$1+[5]Jun!$Y$1+[5]Jun!$Z$1+[5]Jun!$AA$1</f>
+        <f>-[5]Sep!$G$1-[5]Sep!$H$1-[5]Sep!$I$1+[5]Sep!$Y$1+[5]Sep!$Z$1+[5]Sep!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AF26" s="22">
-        <f>-[6]Jun!$G$1-[6]Jun!$H$1-[6]Jun!$I$1+[6]Jun!$Y$1+[6]Jun!$Z$1+[6]Jun!$AA$1</f>
+        <f>-[6]Sep!$G$1-[6]Sep!$H$1-[6]Sep!$I$1+[6]Sep!$Y$1+[6]Sep!$Z$1+[6]Sep!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AG26" s="22">
-        <f>-[7]Jun!$G$1-[7]Jun!$H$1-[7]Jun!$I$1+[7]Jun!$V$1+[7]Jun!$W$1+[7]Jun!$X$1</f>
+        <f>-[7]Sep!$G$1-[7]Sep!$H$1-[7]Sep!$I$1+[7]Sep!$V$1+[7]Sep!$W$1+[7]Sep!$X$1</f>
         <v>0</v>
       </c>
       <c r="AH26" s="22"/>
@@ -22754,19 +22754,19 @@
       <c r="AM26" s="22"/>
       <c r="AN26" s="22"/>
       <c r="AO26" s="22">
-        <f>-[4]Jul!$G$1-[4]Jul!$H$1-[4]Jul!$I$1+[4]Jul!$Y$1+[4]Jul!$Z$1+[4]Jul!$AA$1</f>
+        <f>-[4]Oct!$G$1-[4]Oct!$H$1-[4]Oct!$I$1+[4]Oct!$Y$1+[4]Oct!$Z$1+[4]Oct!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AP26" s="22">
-        <f>-[5]Jul!$G$1-[5]Jul!$H$1-[5]Jul!$I$1+[5]Jul!$Y$1+[5]Jul!$Z$1+[5]Jul!$AA$1</f>
+        <f>-[5]Oct!$G$1-[5]Oct!$H$1-[5]Oct!$I$1+[5]Oct!$Y$1+[5]Oct!$Z$1+[5]Oct!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AQ26" s="22">
-        <f>-[6]Jul!$G$1-[6]Jul!$H$1-[6]Jul!$I$1+[6]Jul!$Y$1+[6]Jul!$Z$1+[6]Jul!$AA$1</f>
+        <f>-[6]Oct!$G$1-[6]Oct!$H$1-[6]Oct!$I$1+[6]Oct!$Y$1+[6]Oct!$Z$1+[6]Oct!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AR26" s="22">
-        <f>-[7]Jul!$G$1-[7]Jul!$H$1-[7]Jul!$I$1+[7]Jul!$V$1+[7]Jul!$W$1+[7]Jul!$X$1</f>
+        <f>-[7]Oct!$G$1-[7]Oct!$H$1-[7]Oct!$I$1+[7]Oct!$V$1+[7]Oct!$W$1+[7]Oct!$X$1</f>
         <v>0</v>
       </c>
       <c r="AS26" s="22"/>
@@ -22780,19 +22780,19 @@
       <c r="AX26" s="22"/>
       <c r="AY26" s="22"/>
       <c r="AZ26" s="22">
-        <f>-[4]Aug!$G$1-[4]Aug!$H$1-[4]Aug!$I$1+[4]Aug!$Y$1+[4]Aug!$Z$1+[4]Aug!$AA$1</f>
+        <f>-[4]Nov!$G$1-[4]Nov!$H$1-[4]Nov!$I$1+[4]Nov!$Y$1+[4]Nov!$Z$1+[4]Nov!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BA26" s="22">
-        <f>-[5]Aug!$G$1-[5]Aug!$H$1-[5]Aug!$I$1+[5]Aug!$Y$1+[5]Aug!$Z$1+[5]Aug!$AA$1</f>
+        <f>-[5]Nov!$G$1-[5]Nov!$H$1-[5]Nov!$I$1+[5]Nov!$Y$1+[5]Nov!$Z$1+[5]Nov!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BB26" s="22">
-        <f>-[6]Aug!$G$1-[6]Aug!$H$1-[6]Aug!$I$1+[6]Aug!$Y$1+[6]Aug!$Z$1+[6]Aug!$AA$1</f>
+        <f>-[6]Nov!$G$1-[6]Nov!$H$1-[6]Nov!$I$1+[6]Nov!$Y$1+[6]Nov!$Z$1+[6]Nov!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BC26" s="22">
-        <f>-[7]Aug!$G$1-[7]Aug!$H$1-[7]Aug!$I$1+[7]Aug!$V$1+[7]Aug!$W$1+[7]Aug!$X$1</f>
+        <f>-[7]Nov!$G$1-[7]Nov!$H$1-[7]Nov!$I$1+[7]Nov!$V$1+[7]Nov!$W$1+[7]Nov!$X$1</f>
         <v>0</v>
       </c>
       <c r="BD26" s="22"/>
@@ -22806,19 +22806,19 @@
       <c r="BI26" s="22"/>
       <c r="BJ26" s="22"/>
       <c r="BK26" s="22">
-        <f>-[4]Sep!$G$1-[4]Sep!$H$1-[4]Sep!$I$1+[4]Sep!$Y$1+[4]Sep!$Z$1+[4]Sep!$AA$1</f>
+        <f>-[4]Dec!$G$1-[4]Dec!$H$1-[4]Dec!$I$1+[4]Dec!$Y$1+[4]Dec!$Z$1+[4]Dec!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BL26" s="22">
-        <f>-[5]Sep!$G$1-[5]Sep!$H$1-[5]Sep!$I$1+[5]Sep!$Y$1+[5]Sep!$Z$1+[5]Sep!$AA$1</f>
+        <f>-[5]Dec!$G$1-[5]Dec!$H$1-[5]Dec!$I$1+[5]Dec!$Y$1+[5]Dec!$Z$1+[5]Dec!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BM26" s="22">
-        <f>-[6]Sep!$G$1-[6]Sep!$H$1-[6]Sep!$I$1+[6]Sep!$Y$1+[6]Sep!$Z$1+[6]Sep!$AA$1</f>
+        <f>-[6]Dec!$G$1-[6]Dec!$H$1-[6]Dec!$I$1+[6]Dec!$Y$1+[6]Dec!$Z$1+[6]Dec!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BN26" s="22">
-        <f>-[7]Sep!$G$1-[7]Sep!$H$1-[7]Sep!$I$1+[7]Sep!$V$1+[7]Sep!$W$1+[7]Sep!$X$1</f>
+        <f>-[7]Dec!$G$1-[7]Dec!$H$1-[7]Dec!$I$1+[7]Dec!$V$1+[7]Dec!$W$1+[7]Dec!$X$1</f>
         <v>0</v>
       </c>
       <c r="BO26" s="22"/>
@@ -22832,19 +22832,19 @@
       <c r="BT26" s="22"/>
       <c r="BU26" s="22"/>
       <c r="BV26" s="22">
-        <f>-[4]Oct!$G$1-[4]Oct!$H$1-[4]Oct!$I$1+[4]Oct!$Y$1+[4]Oct!$Z$1+[4]Oct!$AA$1</f>
+        <f>-[4]Jan!$G$1-[4]Jan!$H$1-[4]Jan!$I$1+[4]Jan!$Y$1+[4]Jan!$Z$1+[4]Jan!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BW26" s="22">
-        <f>-[5]Oct!$G$1-[5]Oct!$H$1-[5]Oct!$I$1+[5]Oct!$Y$1+[5]Oct!$Z$1+[5]Oct!$AA$1</f>
+        <f>-[5]Jan!$G$1-[5]Jan!$H$1-[5]Jan!$I$1+[5]Jan!$Y$1+[5]Jan!$Z$1+[5]Jan!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BX26" s="22">
-        <f>-[6]Oct!$G$1-[6]Oct!$H$1-[6]Oct!$I$1+[6]Oct!$Y$1+[6]Oct!$Z$1+[6]Oct!$AA$1</f>
+        <f>-[6]Jan!$G$1-[6]Jan!$H$1-[6]Jan!$I$1+[6]Jan!$Y$1+[6]Jan!$Z$1+[6]Jan!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BY26" s="22">
-        <f>-[7]Oct!$G$1-[7]Oct!$H$1-[7]Oct!$I$1+[7]Oct!$V$1+[7]Oct!$W$1+[7]Oct!$X$1</f>
+        <f>-[7]Jan!$G$1-[7]Jan!$H$1-[7]Jan!$I$1+[7]Jan!$V$1+[7]Jan!$W$1+[7]Jan!$X$1</f>
         <v>0</v>
       </c>
       <c r="BZ26" s="22"/>
@@ -22858,19 +22858,19 @@
       <c r="CE26" s="22"/>
       <c r="CF26" s="22"/>
       <c r="CG26" s="22">
-        <f>-[4]Nov!$G$1-[4]Nov!$H$1-[4]Nov!$I$1+[4]Nov!$Y$1+[4]Nov!$Z$1+[4]Nov!$AA$1</f>
+        <f>-[4]Feb!$G$1-[4]Feb!$H$1-[4]Feb!$I$1+[4]Feb!$Y$1+[4]Feb!$Z$1+[4]Feb!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CH26" s="22">
-        <f>-[5]Nov!$G$1-[5]Nov!$H$1-[5]Nov!$I$1+[5]Nov!$Y$1+[5]Nov!$Z$1+[5]Nov!$AA$1</f>
+        <f>-[5]Feb!$G$1-[5]Feb!$H$1-[5]Feb!$I$1+[5]Feb!$Y$1+[5]Feb!$Z$1+[5]Feb!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CI26" s="22">
-        <f>-[6]Nov!$G$1-[6]Nov!$H$1-[6]Nov!$I$1+[6]Nov!$Y$1+[6]Nov!$Z$1+[6]Nov!$AA$1</f>
+        <f>-[6]Feb!$G$1-[6]Feb!$H$1-[6]Feb!$I$1+[6]Feb!$Y$1+[6]Feb!$Z$1+[6]Feb!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CJ26" s="22">
-        <f>-[7]Nov!$G$1-[7]Nov!$H$1-[7]Nov!$I$1+[7]Nov!$V$1+[7]Nov!$W$1+[7]Nov!$X$1</f>
+        <f>-[7]Feb!$G$1-[7]Feb!$H$1-[7]Feb!$I$1+[7]Feb!$V$1+[7]Feb!$W$1+[7]Feb!$X$1</f>
         <v>0</v>
       </c>
       <c r="CK26" s="22"/>
@@ -22884,19 +22884,19 @@
       <c r="CP26" s="22"/>
       <c r="CQ26" s="22"/>
       <c r="CR26" s="22">
-        <f>-[4]Dec!$G$1-[4]Dec!$H$1-[4]Dec!$I$1+[4]Dec!$Y$1+[4]Dec!$Z$1+[4]Dec!$AA$1</f>
+        <f>-[4]Mar!$G$1-[4]Mar!$H$1-[4]Mar!$I$1+[4]Mar!$Y$1+[4]Mar!$Z$1+[4]Mar!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CS26" s="22">
-        <f>-[5]Dec!$G$1-[5]Dec!$H$1-[5]Dec!$I$1+[5]Dec!$Y$1+[5]Dec!$Z$1+[5]Dec!$AA$1</f>
+        <f>-[5]Mar!$G$1-[5]Mar!$H$1-[5]Mar!$I$1+[5]Mar!$Y$1+[5]Mar!$Z$1+[5]Mar!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CT26" s="22">
-        <f>-[6]Dec!$G$1-[6]Dec!$H$1-[6]Dec!$I$1+[6]Dec!$Y$1+[6]Dec!$Z$1+[6]Dec!$AA$1</f>
+        <f>-[6]Mar!$G$1-[6]Mar!$H$1-[6]Mar!$I$1+[6]Mar!$Y$1+[6]Mar!$Z$1+[6]Mar!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CU26" s="22">
-        <f>-[7]Dec!$G$1-[7]Dec!$H$1-[7]Dec!$I$1+[7]Dec!$V$1+[7]Dec!$W$1+[7]Dec!$X$1</f>
+        <f>-[7]Mar!$G$1-[7]Mar!$H$1-[7]Mar!$I$1+[7]Mar!$V$1+[7]Mar!$W$1+[7]Mar!$X$1</f>
         <v>0</v>
       </c>
       <c r="CV26" s="22"/>
@@ -22910,19 +22910,19 @@
       <c r="DA26" s="22"/>
       <c r="DB26" s="22"/>
       <c r="DC26" s="22">
-        <f>-[4]Jan!$G$1-[4]Jan!$H$1-[4]Jan!$I$1+[4]Jan!$Y$1+[4]Jan!$Z$1+[4]Jan!$AA$1</f>
+        <f>-[4]Apr!$G$1-[4]Apr!$H$1-[4]Apr!$I$1+[4]Apr!$Y$1+[4]Apr!$Z$1+[4]Apr!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DD26" s="22">
-        <f>-[5]Jan!$G$1-[5]Jan!$H$1-[5]Jan!$I$1+[5]Jan!$Y$1+[5]Jan!$Z$1+[5]Jan!$AA$1</f>
+        <f>-[5]Apr!$G$1-[5]Apr!$H$1-[5]Apr!$I$1+[5]Apr!$Y$1+[5]Apr!$Z$1+[5]Apr!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DE26" s="22">
-        <f>-[6]Jan!$G$1-[6]Jan!$H$1-[6]Jan!$I$1+[6]Jan!$Y$1+[6]Jan!$Z$1+[6]Jan!$AA$1</f>
+        <f>-[6]Apr!$G$1-[6]Apr!$H$1-[6]Apr!$I$1+[6]Apr!$Y$1+[6]Apr!$Z$1+[6]Apr!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DF26" s="22">
-        <f>-[7]Jan!$G$1-[7]Jan!$H$1-[7]Jan!$I$1+[7]Jan!$V$1+[7]Jan!$W$1+[7]Jan!$X$1</f>
+        <f>-[7]Apr!$G$1-[7]Apr!$H$1-[7]Apr!$I$1+[7]Apr!$V$1+[7]Apr!$W$1+[7]Apr!$X$1</f>
         <v>0</v>
       </c>
       <c r="DG26" s="22"/>
@@ -22936,19 +22936,19 @@
       <c r="DL26" s="22"/>
       <c r="DM26" s="22"/>
       <c r="DN26" s="22">
-        <f>-[4]Feb!$G$1-[4]Feb!$H$1-[4]Feb!$I$1+[4]Feb!$Y$1+[4]Feb!$Z$1+[4]Feb!$AA$1</f>
+        <f>-[4]May!$G$1-[4]May!$H$1-[4]May!$I$1+[4]May!$Y$1+[4]May!$Z$1+[4]May!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DO26" s="22">
-        <f>-[5]Feb!$G$1-[5]Feb!$H$1-[5]Feb!$I$1+[5]Feb!$Y$1+[5]Feb!$Z$1+[5]Feb!$AA$1</f>
+        <f>-[5]May!$G$1-[5]May!$H$1-[5]May!$I$1+[5]May!$Y$1+[5]May!$Z$1+[5]May!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DP26" s="22">
-        <f>-[6]Feb!$G$1-[6]Feb!$H$1-[6]Feb!$I$1+[6]Feb!$Y$1+[6]Feb!$Z$1+[6]Feb!$AA$1</f>
+        <f>-[6]May!$G$1-[6]May!$H$1-[6]May!$I$1+[6]May!$Y$1+[6]May!$Z$1+[6]May!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DQ26" s="22">
-        <f>-[7]Feb!$G$1-[7]Feb!$H$1-[7]Feb!$I$1+[7]Feb!$V$1+[7]Feb!$W$1+[7]Feb!$X$1</f>
+        <f>-[7]May!$G$1-[7]May!$H$1-[7]May!$I$1+[7]May!$V$1+[7]May!$W$1+[7]May!$X$1</f>
         <v>0</v>
       </c>
       <c r="DR26" s="22"/>
@@ -22962,19 +22962,19 @@
       <c r="DW26" s="22"/>
       <c r="DX26" s="22"/>
       <c r="DY26" s="22">
-        <f>-[4]Mar!$G$1-[4]Mar!$H$1-[4]Mar!$I$1+[4]Mar!$Y$1+[4]Mar!$Z$1+[4]Mar!$AA$1</f>
+        <f>-[4]Jun!$G$1-[4]Jun!$H$1-[4]Jun!$I$1+[4]Jun!$Y$1+[4]Jun!$Z$1+[4]Jun!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DZ26" s="22">
-        <f>-[5]Mar!$G$1-[5]Mar!$H$1-[5]Mar!$I$1+[5]Mar!$Y$1+[5]Mar!$Z$1+[5]Mar!$AA$1</f>
+        <f>-[5]Jun!$G$1-[5]Jun!$H$1-[5]Jun!$I$1+[5]Jun!$Y$1+[5]Jun!$Z$1+[5]Jun!$AA$1</f>
         <v>0</v>
       </c>
       <c r="EA26" s="22">
-        <f>-[6]Mar!$G$1-[6]Mar!$H$1-[6]Mar!$I$1+[6]Mar!$Y$1+[6]Mar!$Z$1+[6]Mar!$AA$1</f>
+        <f>-[6]Jun!$G$1-[6]Jun!$H$1-[6]Jun!$I$1+[6]Jun!$Y$1+[6]Jun!$Z$1+[6]Jun!$AA$1</f>
         <v>0</v>
       </c>
       <c r="EB26" s="22">
-        <f>-[7]Mar!$G$1-[7]Mar!$H$1-[7]Mar!$I$1+[7]Mar!$V$1+[7]Mar!$W$1+[7]Mar!$X$1</f>
+        <f>-[7]Jun!$G$1-[7]Jun!$H$1-[7]Jun!$I$1+[7]Jun!$V$1+[7]Jun!$W$1+[7]Jun!$X$1</f>
         <v>0</v>
       </c>
       <c r="EC26" s="22"/>
@@ -23152,23 +23152,23 @@
       <c r="E28" s="21"/>
       <c r="F28" s="22"/>
       <c r="G28" s="22">
-        <f>-[2]Apr!$F$1+[2]Apr!$AK$1</f>
+        <f>-[2]Jul!$F$1+[2]Jul!$AK$1</f>
         <v>0</v>
       </c>
       <c r="H28" s="22">
-        <f>[4]Apr!$AB$1</f>
+        <f>[4]Jul!$AB$1</f>
         <v>0</v>
       </c>
       <c r="I28" s="22">
-        <f>[5]Apr!$AB$1</f>
+        <f>[5]Jul!$AB$1</f>
         <v>0</v>
       </c>
       <c r="J28" s="22">
-        <f>[6]Apr!$AB$1</f>
+        <f>[6]Jul!$AB$1</f>
         <v>0</v>
       </c>
       <c r="K28" s="22">
-        <f>[7]Apr!$Y$1</f>
+        <f>[7]Jul!$Y$1</f>
         <v>0</v>
       </c>
       <c r="L28" s="22"/>
@@ -23180,23 +23180,23 @@
       <c r="P28" s="21"/>
       <c r="Q28" s="22"/>
       <c r="R28" s="22">
-        <f>-[2]May!$F$1+[2]May!$AK$1</f>
+        <f>-[2]Aug!$F$1+[2]Aug!$AK$1</f>
         <v>0</v>
       </c>
       <c r="S28" s="22">
-        <f>[4]May!$AB$1</f>
+        <f>[4]Aug!$AB$1</f>
         <v>0</v>
       </c>
       <c r="T28" s="22">
-        <f>[5]May!$AB$1</f>
+        <f>[5]Aug!$AB$1</f>
         <v>0</v>
       </c>
       <c r="U28" s="22">
-        <f>[6]May!$AB$1</f>
+        <f>[6]Aug!$AB$1</f>
         <v>0</v>
       </c>
       <c r="V28" s="22">
-        <f>[7]May!$Y$1</f>
+        <f>[7]Aug!$Y$1</f>
         <v>0</v>
       </c>
       <c r="W28" s="22"/>
@@ -23209,23 +23209,23 @@
       <c r="AA28" s="21"/>
       <c r="AB28" s="22"/>
       <c r="AC28" s="22">
-        <f>-[2]Jun!$F$1+[2]Jun!$AK$1</f>
+        <f>-[2]Sep!$F$1+[2]Sep!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AD28" s="22">
-        <f>[4]Jun!$AB$1</f>
+        <f>[4]Sep!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AE28" s="22">
-        <f>[5]Jun!$AB$1</f>
+        <f>[5]Sep!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AF28" s="22">
-        <f>[6]Jun!$AB$1</f>
+        <f>[6]Sep!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AG28" s="22">
-        <f>[7]Jun!$Y$1</f>
+        <f>[7]Sep!$Y$1</f>
         <v>0</v>
       </c>
       <c r="AH28" s="22"/>
@@ -23238,23 +23238,23 @@
       <c r="AL28" s="21"/>
       <c r="AM28" s="22"/>
       <c r="AN28" s="22">
-        <f>-[2]Jul!$F$1+[2]Jul!$AK$1</f>
+        <f>-[2]Oct!$F$1+[2]Oct!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AO28" s="22">
-        <f>[4]Jul!$AB$1</f>
+        <f>[4]Oct!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AP28" s="22">
-        <f>[5]Jul!$AB$1</f>
+        <f>[5]Oct!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AQ28" s="22">
-        <f>[6]Jul!$AB$1</f>
+        <f>[6]Oct!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AR28" s="22">
-        <f>[7]Jul!$Y$1</f>
+        <f>[7]Oct!$Y$1</f>
         <v>0</v>
       </c>
       <c r="AS28" s="22"/>
@@ -23267,23 +23267,23 @@
       <c r="AW28" s="21"/>
       <c r="AX28" s="22"/>
       <c r="AY28" s="22">
-        <f>-[2]Aug!$F$1+[2]Aug!$AK$1</f>
+        <f>-[2]Nov!$F$1+[2]Nov!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AZ28" s="22">
-        <f>[4]Aug!$AB$1</f>
+        <f>[4]Nov!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BA28" s="22">
-        <f>[5]Aug!$AB$1</f>
+        <f>[5]Nov!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BB28" s="22">
-        <f>[6]Aug!$AB$1</f>
+        <f>[6]Nov!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BC28" s="22">
-        <f>[7]Aug!$Y$1</f>
+        <f>[7]Nov!$Y$1</f>
         <v>0</v>
       </c>
       <c r="BD28" s="22"/>
@@ -23296,23 +23296,23 @@
       <c r="BH28" s="21"/>
       <c r="BI28" s="22"/>
       <c r="BJ28" s="22">
-        <f>-[2]Sep!$F$1+[2]Sep!$AK$1</f>
+        <f>-[2]Dec!$F$1+[2]Dec!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BK28" s="22">
-        <f>[4]Sep!$AB$1</f>
+        <f>[4]Dec!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BL28" s="22">
-        <f>[5]Sep!$AB$1</f>
+        <f>[5]Dec!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BM28" s="22">
-        <f>[6]Sep!$AB$1</f>
+        <f>[6]Dec!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BN28" s="22">
-        <f>[7]Sep!$Y$1</f>
+        <f>[7]Dec!$Y$1</f>
         <v>0</v>
       </c>
       <c r="BO28" s="22"/>
@@ -23325,23 +23325,23 @@
       <c r="BS28" s="21"/>
       <c r="BT28" s="22"/>
       <c r="BU28" s="22">
-        <f>-[2]Oct!$F$1+[2]Oct!$AK$1</f>
+        <f>-[2]Jan!$F$1+[2]Jan!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BV28" s="22">
-        <f>[4]Oct!$AB$1</f>
+        <f>[4]Jan!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BW28" s="22">
-        <f>[5]Oct!$AB$1</f>
+        <f>[5]Jan!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BX28" s="22">
-        <f>[6]Oct!$AB$1</f>
+        <f>[6]Jan!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BY28" s="22">
-        <f>[7]Oct!$Y$1</f>
+        <f>[7]Jan!$Y$1</f>
         <v>0</v>
       </c>
       <c r="BZ28" s="22"/>
@@ -23354,23 +23354,23 @@
       <c r="CD28" s="21"/>
       <c r="CE28" s="22"/>
       <c r="CF28" s="22">
-        <f>-[2]Nov!$F$1+[2]Nov!$AK$1</f>
+        <f>-[2]Feb!$F$1+[2]Feb!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CG28" s="22">
-        <f>[4]Nov!$AB$1</f>
+        <f>[4]Feb!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CH28" s="22">
-        <f>[5]Nov!$AB$1</f>
+        <f>[5]Feb!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CI28" s="22">
-        <f>[6]Nov!$AB$1</f>
+        <f>[6]Feb!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CJ28" s="22">
-        <f>[7]Nov!$Y$1</f>
+        <f>[7]Feb!$Y$1</f>
         <v>0</v>
       </c>
       <c r="CK28" s="22"/>
@@ -23383,23 +23383,23 @@
       <c r="CO28" s="21"/>
       <c r="CP28" s="22"/>
       <c r="CQ28" s="22">
-        <f>-[2]Dec!$F$1+[2]Dec!$AK$1</f>
+        <f>-[2]Mar!$F$1+[2]Mar!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CR28" s="22">
-        <f>[4]Dec!$AB$1</f>
+        <f>[4]Mar!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CS28" s="22">
-        <f>[5]Dec!$AB$1</f>
+        <f>[5]Mar!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CT28" s="22">
-        <f>[6]Dec!$AB$1</f>
+        <f>[6]Mar!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CU28" s="22">
-        <f>[7]Dec!$Y$1</f>
+        <f>[7]Mar!$Y$1</f>
         <v>0</v>
       </c>
       <c r="CV28" s="22"/>
@@ -23412,23 +23412,23 @@
       <c r="CZ28" s="21"/>
       <c r="DA28" s="22"/>
       <c r="DB28" s="22">
-        <f>-[2]Jan!$F$1+[2]Jan!$AK$1</f>
+        <f>-[2]Apr!$F$1+[2]Apr!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DC28" s="22">
-        <f>[4]Jan!$AB$1</f>
+        <f>[4]Apr!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DD28" s="22">
-        <f>[5]Jan!$AB$1</f>
+        <f>[5]Apr!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DE28" s="22">
-        <f>[6]Jan!$AB$1</f>
+        <f>[6]Apr!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DF28" s="22">
-        <f>[7]Jan!$Y$1</f>
+        <f>[7]Apr!$Y$1</f>
         <v>0</v>
       </c>
       <c r="DG28" s="22"/>
@@ -23441,23 +23441,23 @@
       <c r="DK28" s="21"/>
       <c r="DL28" s="22"/>
       <c r="DM28" s="22">
-        <f>-[2]Feb!$F$1+[2]Feb!$AK$1</f>
+        <f>-[2]May!$F$1+[2]May!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DN28" s="22">
-        <f>[4]Feb!$AB$1</f>
+        <f>[4]May!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DO28" s="22">
-        <f>[5]Feb!$AB$1</f>
+        <f>[5]May!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DP28" s="22">
-        <f>[6]Feb!$AB$1</f>
+        <f>[6]May!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DQ28" s="22">
-        <f>[7]Feb!$Y$1</f>
+        <f>[7]May!$Y$1</f>
         <v>0</v>
       </c>
       <c r="DR28" s="22"/>
@@ -23470,23 +23470,23 @@
       <c r="DV28" s="21"/>
       <c r="DW28" s="22"/>
       <c r="DX28" s="22">
-        <f>-[2]Mar!$F$1+[2]Mar!$AK$1</f>
+        <f>-[2]Jun!$F$1+[2]Jun!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DY28" s="22">
-        <f>[4]Mar!$AB$1</f>
+        <f>[4]Jun!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DZ28" s="22">
-        <f>[5]Mar!$AB$1</f>
+        <f>[5]Jun!$AB$1</f>
         <v>0</v>
       </c>
       <c r="EA28" s="22">
-        <f>[6]Mar!$AB$1</f>
+        <f>[6]Jun!$AB$1</f>
         <v>0</v>
       </c>
       <c r="EB28" s="22">
-        <f>[7]Mar!$Y$1</f>
+        <f>[7]Jun!$Y$1</f>
         <v>0</v>
       </c>
       <c r="EC28" s="22"/>
@@ -23522,19 +23522,19 @@
       <c r="F29" s="22"/>
       <c r="G29" s="22"/>
       <c r="H29" s="22">
-        <f>[4]Apr!$AC$1</f>
+        <f>[4]Jul!$AC$1</f>
         <v>0</v>
       </c>
       <c r="I29" s="22">
-        <f>[5]Apr!$AC$1</f>
+        <f>[5]Jul!$AC$1</f>
         <v>0</v>
       </c>
       <c r="J29" s="22">
-        <f>[6]Apr!$AC$1</f>
+        <f>[6]Jul!$AC$1</f>
         <v>0</v>
       </c>
       <c r="K29" s="22">
-        <f>[7]Apr!$Z$1</f>
+        <f>[7]Jul!$Z$1</f>
         <v>0</v>
       </c>
       <c r="L29" s="22">
@@ -23550,19 +23550,19 @@
       <c r="Q29" s="22"/>
       <c r="R29" s="22"/>
       <c r="S29" s="22">
-        <f>[4]May!$AC$1</f>
+        <f>[4]Aug!$AC$1</f>
         <v>0</v>
       </c>
       <c r="T29" s="22">
-        <f>[5]May!$AC$1</f>
+        <f>[5]Aug!$AC$1</f>
         <v>0</v>
       </c>
       <c r="U29" s="22">
-        <f>[6]May!$AC$1</f>
+        <f>[6]Aug!$AC$1</f>
         <v>0</v>
       </c>
       <c r="V29" s="22">
-        <f>[7]May!$Z$1</f>
+        <f>[7]Aug!$Z$1</f>
         <v>0</v>
       </c>
       <c r="W29" s="22">
@@ -23579,19 +23579,19 @@
       <c r="AB29" s="22"/>
       <c r="AC29" s="22"/>
       <c r="AD29" s="22">
-        <f>[4]Jun!$AC$1</f>
+        <f>[4]Sep!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AE29" s="22">
-        <f>[5]Jun!$AC$1</f>
+        <f>[5]Sep!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AF29" s="22">
-        <f>[6]Jun!$AC$1</f>
+        <f>[6]Sep!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AG29" s="22">
-        <f>[7]Jun!$Z$1</f>
+        <f>[7]Sep!$Z$1</f>
         <v>0</v>
       </c>
       <c r="AH29" s="22">
@@ -23608,19 +23608,19 @@
       <c r="AM29" s="22"/>
       <c r="AN29" s="22"/>
       <c r="AO29" s="22">
-        <f>[4]Jul!$AC$1</f>
+        <f>[4]Oct!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AP29" s="22">
-        <f>[5]Jul!$AC$1</f>
+        <f>[5]Oct!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AQ29" s="22">
-        <f>[6]Jul!$AC$1</f>
+        <f>[6]Oct!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AR29" s="22">
-        <f>[7]Jul!$Z$1</f>
+        <f>[7]Oct!$Z$1</f>
         <v>0</v>
       </c>
       <c r="AS29" s="22">
@@ -23637,19 +23637,19 @@
       <c r="AX29" s="22"/>
       <c r="AY29" s="22"/>
       <c r="AZ29" s="22">
-        <f>[4]Aug!$AC$1</f>
+        <f>[4]Nov!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BA29" s="22">
-        <f>[5]Aug!$AC$1</f>
+        <f>[5]Nov!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BB29" s="22">
-        <f>[6]Aug!$AC$1</f>
+        <f>[6]Nov!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BC29" s="22">
-        <f>[7]Aug!$Z$1</f>
+        <f>[7]Nov!$Z$1</f>
         <v>0</v>
       </c>
       <c r="BD29" s="22">
@@ -23666,19 +23666,19 @@
       <c r="BI29" s="22"/>
       <c r="BJ29" s="22"/>
       <c r="BK29" s="22">
-        <f>[4]Sep!$AC$1</f>
+        <f>[4]Dec!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BL29" s="22">
-        <f>[5]Sep!$AC$1</f>
+        <f>[5]Dec!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BM29" s="22">
-        <f>[6]Sep!$AC$1</f>
+        <f>[6]Dec!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BN29" s="22">
-        <f>[7]Sep!$Z$1</f>
+        <f>[7]Dec!$Z$1</f>
         <v>0</v>
       </c>
       <c r="BO29" s="22">
@@ -23695,19 +23695,19 @@
       <c r="BT29" s="22"/>
       <c r="BU29" s="22"/>
       <c r="BV29" s="22">
-        <f>[4]Oct!$AC$1</f>
+        <f>[4]Jan!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BW29" s="22">
-        <f>[5]Oct!$AC$1</f>
+        <f>[5]Jan!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BX29" s="22">
-        <f>[6]Oct!$AC$1</f>
+        <f>[6]Jan!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BY29" s="22">
-        <f>[7]Oct!$Z$1</f>
+        <f>[7]Jan!$Z$1</f>
         <v>0</v>
       </c>
       <c r="BZ29" s="22">
@@ -23724,19 +23724,19 @@
       <c r="CE29" s="22"/>
       <c r="CF29" s="22"/>
       <c r="CG29" s="22">
-        <f>[4]Nov!$AC$1</f>
+        <f>[4]Feb!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CH29" s="22">
-        <f>[5]Nov!$AC$1</f>
+        <f>[5]Feb!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CI29" s="22">
-        <f>[6]Nov!$AC$1</f>
+        <f>[6]Feb!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CJ29" s="22">
-        <f>[7]Nov!$Z$1</f>
+        <f>[7]Feb!$Z$1</f>
         <v>0</v>
       </c>
       <c r="CK29" s="22">
@@ -23753,19 +23753,19 @@
       <c r="CP29" s="22"/>
       <c r="CQ29" s="22"/>
       <c r="CR29" s="22">
-        <f>[4]Dec!$AC$1</f>
+        <f>[4]Mar!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CS29" s="22">
-        <f>[5]Dec!$AC$1</f>
+        <f>[5]Mar!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CT29" s="22">
-        <f>[6]Dec!$AC$1</f>
+        <f>[6]Mar!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CU29" s="22">
-        <f>[7]Dec!$Z$1</f>
+        <f>[7]Mar!$Z$1</f>
         <v>0</v>
       </c>
       <c r="CV29" s="22">
@@ -23782,19 +23782,19 @@
       <c r="DA29" s="22"/>
       <c r="DB29" s="22"/>
       <c r="DC29" s="22">
-        <f>[4]Jan!$AC$1</f>
+        <f>[4]Apr!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DD29" s="22">
-        <f>[5]Jan!$AC$1</f>
+        <f>[5]Apr!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DE29" s="22">
-        <f>[6]Jan!$AC$1</f>
+        <f>[6]Apr!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DF29" s="22">
-        <f>[7]Jan!$Z$1</f>
+        <f>[7]Apr!$Z$1</f>
         <v>0</v>
       </c>
       <c r="DG29" s="22">
@@ -23811,19 +23811,19 @@
       <c r="DL29" s="22"/>
       <c r="DM29" s="22"/>
       <c r="DN29" s="22">
-        <f>[4]Feb!$AC$1</f>
+        <f>[4]May!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DO29" s="22">
-        <f>[5]Feb!$AC$1</f>
+        <f>[5]May!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DP29" s="22">
-        <f>[6]Feb!$AC$1</f>
+        <f>[6]May!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DQ29" s="22">
-        <f>[7]Feb!$Z$1</f>
+        <f>[7]May!$Z$1</f>
         <v>0</v>
       </c>
       <c r="DR29" s="22">
@@ -23840,19 +23840,19 @@
       <c r="DW29" s="22"/>
       <c r="DX29" s="22"/>
       <c r="DY29" s="22">
-        <f>[4]Mar!$AC$1</f>
+        <f>[4]Jun!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DZ29" s="22">
-        <f>[5]Mar!$AC$1</f>
+        <f>[5]Jun!$AC$1</f>
         <v>0</v>
       </c>
       <c r="EA29" s="22">
-        <f>[6]Mar!$AC$1</f>
+        <f>[6]Jun!$AC$1</f>
         <v>0</v>
       </c>
       <c r="EB29" s="22">
-        <f>[7]Mar!$Z$1</f>
+        <f>[7]Jun!$Z$1</f>
         <v>0</v>
       </c>
       <c r="EC29" s="22">
@@ -24110,19 +24110,19 @@
       <c r="F31" s="22"/>
       <c r="G31" s="22"/>
       <c r="H31" s="22">
-        <f>[4]Apr!$AL$1</f>
+        <f>[4]Jul!$AL$1</f>
         <v>0</v>
       </c>
       <c r="I31" s="22">
-        <f>[5]Apr!$AL$1</f>
+        <f>[5]Jul!$AL$1</f>
         <v>0</v>
       </c>
       <c r="J31" s="22">
-        <f>[6]Apr!$AL$1</f>
+        <f>[6]Jul!$AL$1</f>
         <v>0</v>
       </c>
       <c r="K31" s="22">
-        <f>[7]Apr!$AI$1</f>
+        <f>[7]Jul!$AI$1</f>
         <v>0</v>
       </c>
       <c r="L31" s="22"/>
@@ -24135,19 +24135,19 @@
       <c r="Q31" s="22"/>
       <c r="R31" s="22"/>
       <c r="S31" s="22">
-        <f>[4]May!$AL$1</f>
+        <f>[4]Aug!$AL$1</f>
         <v>0</v>
       </c>
       <c r="T31" s="22">
-        <f>[5]May!$AL$1</f>
+        <f>[5]Aug!$AL$1</f>
         <v>0</v>
       </c>
       <c r="U31" s="22">
-        <f>[6]May!$AL$1</f>
+        <f>[6]Aug!$AL$1</f>
         <v>0</v>
       </c>
       <c r="V31" s="22">
-        <f>[7]May!$AI$1</f>
+        <f>[7]Aug!$AI$1</f>
         <v>0</v>
       </c>
       <c r="W31" s="22"/>
@@ -24161,19 +24161,19 @@
       <c r="AB31" s="22"/>
       <c r="AC31" s="22"/>
       <c r="AD31" s="22">
-        <f>[4]Jun!$AL$1</f>
+        <f>[4]Sep!$AL$1</f>
         <v>0</v>
       </c>
       <c r="AE31" s="22">
-        <f>[5]Jun!$AL$1</f>
+        <f>[5]Sep!$AL$1</f>
         <v>0</v>
       </c>
       <c r="AF31" s="22">
-        <f>[6]Jun!$AL$1</f>
+        <f>[6]Sep!$AL$1</f>
         <v>0</v>
       </c>
       <c r="AG31" s="22">
-        <f>[7]Jun!$AI$1</f>
+        <f>[7]Sep!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AH31" s="22"/>
@@ -24187,19 +24187,19 @@
       <c r="AM31" s="22"/>
       <c r="AN31" s="22"/>
       <c r="AO31" s="22">
-        <f>[4]Jul!$AL$1</f>
+        <f>[4]Oct!$AL$1</f>
         <v>0</v>
       </c>
       <c r="AP31" s="22">
-        <f>[5]Jul!$AL$1</f>
+        <f>[5]Oct!$AL$1</f>
         <v>0</v>
       </c>
       <c r="AQ31" s="22">
-        <f>[6]Jul!$AL$1</f>
+        <f>[6]Oct!$AL$1</f>
         <v>0</v>
       </c>
       <c r="AR31" s="22">
-        <f>[7]Jul!$AI$1</f>
+        <f>[7]Oct!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AS31" s="22"/>
@@ -24213,19 +24213,19 @@
       <c r="AX31" s="22"/>
       <c r="AY31" s="22"/>
       <c r="AZ31" s="22">
-        <f>[4]Aug!$AL$1</f>
+        <f>[4]Nov!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BA31" s="22">
-        <f>[5]Aug!$AL$1</f>
+        <f>[5]Nov!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BB31" s="22">
-        <f>[6]Aug!$AL$1</f>
+        <f>[6]Nov!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BC31" s="22">
-        <f>[7]Aug!$AI$1</f>
+        <f>[7]Nov!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BD31" s="22"/>
@@ -24239,19 +24239,19 @@
       <c r="BI31" s="22"/>
       <c r="BJ31" s="22"/>
       <c r="BK31" s="22">
-        <f>[4]Sep!$AL$1</f>
+        <f>[4]Dec!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BL31" s="22">
-        <f>[5]Sep!$AL$1</f>
+        <f>[5]Dec!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BM31" s="22">
-        <f>[6]Sep!$AL$1</f>
+        <f>[6]Dec!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BN31" s="22">
-        <f>[7]Sep!$AI$1</f>
+        <f>[7]Dec!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BO31" s="22"/>
@@ -24265,19 +24265,19 @@
       <c r="BT31" s="22"/>
       <c r="BU31" s="22"/>
       <c r="BV31" s="22">
-        <f>[4]Oct!$AL$1</f>
+        <f>[4]Jan!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BW31" s="22">
-        <f>[5]Oct!$AL$1</f>
+        <f>[5]Jan!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BX31" s="22">
-        <f>[6]Oct!$AL$1</f>
+        <f>[6]Jan!$AL$1</f>
         <v>0</v>
       </c>
       <c r="BY31" s="22">
-        <f>[7]Oct!$AI$1</f>
+        <f>[7]Jan!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BZ31" s="22"/>
@@ -24291,19 +24291,19 @@
       <c r="CE31" s="22"/>
       <c r="CF31" s="22"/>
       <c r="CG31" s="22">
-        <f>[4]Nov!$AL$1</f>
+        <f>[4]Feb!$AL$1</f>
         <v>0</v>
       </c>
       <c r="CH31" s="22">
-        <f>[5]Nov!$AL$1</f>
+        <f>[5]Feb!$AL$1</f>
         <v>0</v>
       </c>
       <c r="CI31" s="22">
-        <f>[6]Nov!$AL$1</f>
+        <f>[6]Feb!$AL$1</f>
         <v>0</v>
       </c>
       <c r="CJ31" s="22">
-        <f>[7]Nov!$AI$1</f>
+        <f>[7]Feb!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CK31" s="22"/>
@@ -24317,19 +24317,19 @@
       <c r="CP31" s="22"/>
       <c r="CQ31" s="22"/>
       <c r="CR31" s="22">
-        <f>[4]Dec!$AL$1</f>
+        <f>[4]Mar!$AL$1</f>
         <v>0</v>
       </c>
       <c r="CS31" s="22">
-        <f>[5]Dec!$AL$1</f>
+        <f>[5]Mar!$AL$1</f>
         <v>0</v>
       </c>
       <c r="CT31" s="22">
-        <f>[6]Dec!$AL$1</f>
+        <f>[6]Mar!$AL$1</f>
         <v>0</v>
       </c>
       <c r="CU31" s="22">
-        <f>[7]Dec!$AI$1</f>
+        <f>[7]Mar!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CV31" s="22"/>
@@ -24343,19 +24343,19 @@
       <c r="DA31" s="22"/>
       <c r="DB31" s="22"/>
       <c r="DC31" s="22">
-        <f>[4]Jan!$AL$1</f>
+        <f>[4]Apr!$AL$1</f>
         <v>0</v>
       </c>
       <c r="DD31" s="22">
-        <f>[5]Jan!$AL$1</f>
+        <f>[5]Apr!$AL$1</f>
         <v>0</v>
       </c>
       <c r="DE31" s="22">
-        <f>[6]Jan!$AL$1</f>
+        <f>[6]Apr!$AL$1</f>
         <v>0</v>
       </c>
       <c r="DF31" s="22">
-        <f>[7]Jan!$AI$1</f>
+        <f>[7]Apr!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DG31" s="22"/>
@@ -24369,19 +24369,19 @@
       <c r="DL31" s="22"/>
       <c r="DM31" s="22"/>
       <c r="DN31" s="22">
-        <f>[4]Feb!$AL$1</f>
+        <f>[4]May!$AL$1</f>
         <v>0</v>
       </c>
       <c r="DO31" s="22">
-        <f>[5]Feb!$AL$1</f>
+        <f>[5]May!$AL$1</f>
         <v>0</v>
       </c>
       <c r="DP31" s="22">
-        <f>[6]Feb!$AL$1</f>
+        <f>[6]May!$AL$1</f>
         <v>0</v>
       </c>
       <c r="DQ31" s="22">
-        <f>[7]Feb!$AI$1</f>
+        <f>[7]May!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DR31" s="22"/>
@@ -24395,19 +24395,19 @@
       <c r="DW31" s="22"/>
       <c r="DX31" s="22"/>
       <c r="DY31" s="22">
-        <f>[4]Mar!$AL$1</f>
+        <f>[4]Jun!$AL$1</f>
         <v>0</v>
       </c>
       <c r="DZ31" s="22">
-        <f>[5]Mar!$AL$1</f>
+        <f>[5]Jun!$AL$1</f>
         <v>0</v>
       </c>
       <c r="EA31" s="22">
-        <f>[6]Mar!$AL$1</f>
+        <f>[6]Jun!$AL$1</f>
         <v>0</v>
       </c>
       <c r="EB31" s="22">
-        <f>[7]Mar!$AI$1</f>
+        <f>[7]Jun!$AI$1</f>
         <v>0</v>
       </c>
       <c r="EC31" s="22"/>
@@ -24443,27 +24443,27 @@
       </c>
       <c r="E32" s="21"/>
       <c r="F32" s="22">
-        <f>[3]Apr!$V$1</f>
+        <f>[3]Jul!$V$1</f>
         <v>0</v>
       </c>
       <c r="G32" s="22">
-        <f>-[2]Apr!$AK$1</f>
+        <f>-[2]Jul!$AK$1</f>
         <v>0</v>
       </c>
       <c r="H32" s="22">
-        <f>-[4]Apr!$O$1+[4]Apr!$AJ$1</f>
+        <f>-[4]Jul!$O$1+[4]Jul!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="I32" s="22">
-        <f>-[5]Apr!$O$1+[5]Apr!$AJ$1</f>
+        <f>-[5]Jul!$O$1+[5]Jul!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="J32" s="22">
-        <f>-[6]Apr!$O$1+[6]Apr!$AJ$1</f>
+        <f>-[6]Jul!$O$1+[6]Jul!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="K32" s="22">
-        <f>[7]Apr!$AG$1</f>
+        <f>[7]Jul!$AG$1</f>
         <v>0</v>
       </c>
       <c r="L32" s="22"/>
@@ -24474,27 +24474,27 @@
       </c>
       <c r="P32" s="21"/>
       <c r="Q32" s="22">
-        <f>[3]May!$V$1</f>
+        <f>[3]Aug!$V$1</f>
         <v>0</v>
       </c>
       <c r="R32" s="22">
-        <f>-[2]May!$AK$1</f>
+        <f>-[2]Aug!$AK$1</f>
         <v>0</v>
       </c>
       <c r="S32" s="22">
-        <f>-[4]May!$O$1+[4]May!$AJ$1</f>
+        <f>-[4]Aug!$O$1+[4]Aug!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="T32" s="22">
-        <f>-[5]May!$O$1+[5]May!$AJ$1</f>
+        <f>-[5]Aug!$O$1+[5]Aug!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="U32" s="22">
-        <f>-[6]May!$O$1+[6]May!$AJ$1</f>
+        <f>-[6]Aug!$O$1+[6]Aug!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="V32" s="22">
-        <f>[7]May!$AG$1</f>
+        <f>[7]Aug!$AG$1</f>
         <v>0</v>
       </c>
       <c r="W32" s="22"/>
@@ -24506,27 +24506,27 @@
       </c>
       <c r="AA32" s="21"/>
       <c r="AB32" s="22">
-        <f>[3]Jun!$V$1</f>
+        <f>[3]Sep!$V$1</f>
         <v>0</v>
       </c>
       <c r="AC32" s="22">
-        <f>-[2]Jun!$AK$1</f>
+        <f>-[2]Sep!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AD32" s="22">
-        <f>-[4]Jun!$O$1+[4]Jun!$AJ$1</f>
+        <f>-[4]Sep!$O$1+[4]Sep!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AE32" s="22">
-        <f>-[5]Jun!$O$1+[5]Jun!$AJ$1</f>
+        <f>-[5]Sep!$O$1+[5]Sep!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AF32" s="22">
-        <f>-[6]Jun!$O$1+[6]Jun!$AJ$1</f>
+        <f>-[6]Sep!$O$1+[6]Sep!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AG32" s="22">
-        <f>[7]Jun!$AG$1</f>
+        <f>[7]Sep!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AH32" s="22"/>
@@ -24538,27 +24538,27 @@
       </c>
       <c r="AL32" s="21"/>
       <c r="AM32" s="22">
-        <f>[3]Jul!$V$1</f>
+        <f>[3]Oct!$V$1</f>
         <v>0</v>
       </c>
       <c r="AN32" s="22">
-        <f>-[2]Jul!$AK$1</f>
+        <f>-[2]Oct!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AO32" s="22">
-        <f>-[4]Jul!$O$1+[4]Jul!$AJ$1</f>
+        <f>-[4]Oct!$O$1+[4]Oct!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AP32" s="22">
-        <f>-[5]Jul!$O$1+[5]Jul!$AJ$1</f>
+        <f>-[5]Oct!$O$1+[5]Oct!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AQ32" s="22">
-        <f>-[6]Jul!$O$1+[6]Jul!$AJ$1</f>
+        <f>-[6]Oct!$O$1+[6]Oct!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AR32" s="22">
-        <f>[7]Jul!$AG$1</f>
+        <f>[7]Oct!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AS32" s="22"/>
@@ -24570,27 +24570,27 @@
       </c>
       <c r="AW32" s="21"/>
       <c r="AX32" s="22">
-        <f>[3]Aug!$V$1</f>
+        <f>[3]Nov!$V$1</f>
         <v>0</v>
       </c>
       <c r="AY32" s="22">
-        <f>-[2]Aug!$AK$1</f>
+        <f>-[2]Nov!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AZ32" s="22">
-        <f>-[4]Aug!$O$1+[4]Aug!$AJ$1</f>
+        <f>-[4]Nov!$O$1+[4]Nov!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BA32" s="22">
-        <f>-[5]Aug!$O$1+[5]Aug!$AJ$1</f>
+        <f>-[5]Nov!$O$1+[5]Nov!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BB32" s="22">
-        <f>-[6]Aug!$O$1+[6]Aug!$AJ$1</f>
+        <f>-[6]Nov!$O$1+[6]Nov!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BC32" s="22">
-        <f>[7]Aug!$AG$1</f>
+        <f>[7]Nov!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BD32" s="22"/>
@@ -24602,27 +24602,27 @@
       </c>
       <c r="BH32" s="21"/>
       <c r="BI32" s="22">
-        <f>[3]Sep!$V$1</f>
+        <f>[3]Dec!$V$1</f>
         <v>0</v>
       </c>
       <c r="BJ32" s="22">
-        <f>-[2]Sep!$AK$1</f>
+        <f>-[2]Dec!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BK32" s="22">
-        <f>-[4]Sep!$O$1+[4]Sep!$AJ$1</f>
+        <f>-[4]Dec!$O$1+[4]Dec!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BL32" s="22">
-        <f>-[5]Sep!$O$1+[5]Sep!$AJ$1</f>
+        <f>-[5]Dec!$O$1+[5]Dec!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BM32" s="22">
-        <f>-[6]Sep!$O$1+[6]Sep!$AJ$1</f>
+        <f>-[6]Dec!$O$1+[6]Dec!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BN32" s="22">
-        <f>[7]Sep!$AG$1</f>
+        <f>[7]Dec!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BO32" s="22"/>
@@ -24634,27 +24634,27 @@
       </c>
       <c r="BS32" s="21"/>
       <c r="BT32" s="22">
-        <f>[3]Oct!$V$1</f>
+        <f>[3]Jan!$V$1</f>
         <v>0</v>
       </c>
       <c r="BU32" s="22">
-        <f>-[2]Oct!$AK$1</f>
+        <f>-[2]Jan!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BV32" s="22">
-        <f>-[4]Oct!$O$1+[4]Oct!$AJ$1</f>
+        <f>-[4]Jan!$O$1+[4]Jan!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BW32" s="22">
-        <f>-[5]Oct!$O$1+[5]Oct!$AJ$1</f>
+        <f>-[5]Jan!$O$1+[5]Jan!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BX32" s="22">
-        <f>-[6]Oct!$O$1+[6]Oct!$AJ$1</f>
+        <f>-[6]Jan!$O$1+[6]Jan!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BY32" s="22">
-        <f>[7]Oct!$AG$1</f>
+        <f>[7]Jan!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BZ32" s="22"/>
@@ -24666,27 +24666,27 @@
       </c>
       <c r="CD32" s="21"/>
       <c r="CE32" s="22">
-        <f>[3]Nov!$V$1</f>
+        <f>[3]Feb!$V$1</f>
         <v>0</v>
       </c>
       <c r="CF32" s="22">
-        <f>-[2]Nov!$AK$1</f>
+        <f>-[2]Feb!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CG32" s="22">
-        <f>-[4]Nov!$O$1+[4]Nov!$AJ$1</f>
+        <f>-[4]Feb!$O$1+[4]Feb!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CH32" s="22">
-        <f>-[5]Nov!$O$1+[5]Nov!$AJ$1</f>
+        <f>-[5]Feb!$O$1+[5]Feb!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CI32" s="22">
-        <f>-[6]Nov!$O$1+[6]Nov!$AJ$1</f>
+        <f>-[6]Feb!$O$1+[6]Feb!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CJ32" s="22">
-        <f>[7]Nov!$AG$1</f>
+        <f>[7]Feb!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CK32" s="22"/>
@@ -24698,27 +24698,27 @@
       </c>
       <c r="CO32" s="21"/>
       <c r="CP32" s="22">
-        <f>[3]Dec!$V$1</f>
+        <f>[3]Mar!$V$1</f>
         <v>0</v>
       </c>
       <c r="CQ32" s="22">
-        <f>-[2]Dec!$AK$1</f>
+        <f>-[2]Mar!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CR32" s="22">
-        <f>-[4]Dec!$O$1+[4]Dec!$AJ$1</f>
+        <f>-[4]Mar!$O$1+[4]Mar!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CS32" s="22">
-        <f>-[5]Dec!$O$1+[5]Dec!$AJ$1</f>
+        <f>-[5]Mar!$O$1+[5]Mar!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CT32" s="22">
-        <f>-[6]Dec!$O$1+[6]Dec!$AJ$1</f>
+        <f>-[6]Mar!$O$1+[6]Mar!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CU32" s="22">
-        <f>[7]Dec!$AG$1</f>
+        <f>[7]Mar!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CV32" s="22"/>
@@ -24730,27 +24730,27 @@
       </c>
       <c r="CZ32" s="21"/>
       <c r="DA32" s="22">
-        <f>[3]Jan!$V$1</f>
+        <f>[3]Apr!$V$1</f>
         <v>0</v>
       </c>
       <c r="DB32" s="22">
-        <f>-[2]Jan!$AK$1</f>
+        <f>-[2]Apr!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DC32" s="22">
-        <f>-[4]Jan!$O$1+[4]Jan!$AJ$1</f>
+        <f>-[4]Apr!$O$1+[4]Apr!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DD32" s="22">
-        <f>-[5]Jan!$O$1+[5]Jan!$AJ$1</f>
+        <f>-[5]Apr!$O$1+[5]Apr!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DE32" s="22">
-        <f>-[6]Jan!$O$1+[6]Jan!$AJ$1</f>
+        <f>-[6]Apr!$O$1+[6]Apr!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DF32" s="22">
-        <f>[7]Jan!$AG$1</f>
+        <f>[7]Apr!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DG32" s="22"/>
@@ -24762,27 +24762,27 @@
       </c>
       <c r="DK32" s="21"/>
       <c r="DL32" s="22">
-        <f>[3]Feb!$V$1</f>
+        <f>[3]May!$V$1</f>
         <v>0</v>
       </c>
       <c r="DM32" s="22">
-        <f>-[2]Feb!$AK$1</f>
+        <f>-[2]May!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DN32" s="22">
-        <f>-[4]Feb!$O$1+[4]Feb!$AJ$1</f>
+        <f>-[4]May!$O$1+[4]May!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DO32" s="22">
-        <f>-[5]Feb!$O$1+[5]Feb!$AJ$1</f>
+        <f>-[5]May!$O$1+[5]May!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DP32" s="22">
-        <f>-[6]Feb!$O$1+[6]Feb!$AJ$1</f>
+        <f>-[6]May!$O$1+[6]May!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DQ32" s="22">
-        <f>[7]Feb!$AG$1</f>
+        <f>[7]May!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DR32" s="22"/>
@@ -24794,27 +24794,27 @@
       </c>
       <c r="DV32" s="21"/>
       <c r="DW32" s="22">
-        <f>[3]Mar!$V$1</f>
+        <f>[3]Jun!$V$1</f>
         <v>0</v>
       </c>
       <c r="DX32" s="22">
-        <f>-[2]Mar!$AK$1</f>
+        <f>-[2]Jun!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DY32" s="22">
-        <f>-[4]Mar!$O$1+[4]Mar!$AJ$1</f>
+        <f>-[4]Jun!$O$1+[4]Jun!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DZ32" s="22">
-        <f>-[5]Mar!$O$1+[5]Mar!$AJ$1</f>
+        <f>-[5]Jun!$O$1+[5]Jun!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="EA32" s="22">
-        <f>-[6]Mar!$O$1+[6]Mar!$AJ$1</f>
+        <f>-[6]Jun!$O$1+[6]Jun!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="EB32" s="22">
-        <f>[7]Mar!$AG$1</f>
+        <f>[7]Jun!$AG$1</f>
         <v>0</v>
       </c>
       <c r="EC32" s="22"/>
@@ -24846,27 +24846,27 @@
       </c>
       <c r="E33" s="21"/>
       <c r="F33" s="22">
-        <f>-[3]Apr!$G$1</f>
+        <f>-[3]Jul!$G$1</f>
         <v>0</v>
       </c>
       <c r="G33" s="22">
-        <f>[2]Apr!$G$1</f>
+        <f>[2]Jul!$G$1</f>
         <v>0</v>
       </c>
       <c r="H33" s="22">
-        <f>-[4]Apr!$N$1+[4]Apr!$AI$1</f>
+        <f>-[4]Jul!$N$1+[4]Jul!$AI$1</f>
         <v>0</v>
       </c>
       <c r="I33" s="22">
-        <f>-[5]Apr!$N$1+[5]Apr!$AI$1</f>
+        <f>-[5]Jul!$N$1+[5]Jul!$AI$1</f>
         <v>0</v>
       </c>
       <c r="J33" s="22">
-        <f>-[6]Apr!$N$1+[6]Apr!$AI$1</f>
+        <f>-[6]Jul!$N$1+[6]Jul!$AI$1</f>
         <v>0</v>
       </c>
       <c r="K33" s="22">
-        <f>[7]Apr!$AF$1</f>
+        <f>[7]Jul!$AF$1</f>
         <v>0</v>
       </c>
       <c r="L33" s="22"/>
@@ -24877,27 +24877,27 @@
       </c>
       <c r="P33" s="21"/>
       <c r="Q33" s="22">
-        <f>-[3]May!$G$1</f>
+        <f>-[3]Aug!$G$1</f>
         <v>0</v>
       </c>
       <c r="R33" s="22">
-        <f>[2]May!$G$1</f>
+        <f>[2]Aug!$G$1</f>
         <v>0</v>
       </c>
       <c r="S33" s="22">
-        <f>-[4]May!$N$1+[4]May!$AI$1</f>
+        <f>-[4]Aug!$N$1+[4]Aug!$AI$1</f>
         <v>0</v>
       </c>
       <c r="T33" s="22">
-        <f>-[5]May!$N$1+[5]May!$AI$1</f>
+        <f>-[5]Aug!$N$1+[5]Aug!$AI$1</f>
         <v>0</v>
       </c>
       <c r="U33" s="22">
-        <f>-[6]May!$N$1+[6]May!$AI$1</f>
+        <f>-[6]Aug!$N$1+[6]Aug!$AI$1</f>
         <v>0</v>
       </c>
       <c r="V33" s="22">
-        <f>[7]May!$AF$1</f>
+        <f>[7]Aug!$AF$1</f>
         <v>0</v>
       </c>
       <c r="W33" s="22"/>
@@ -24909,27 +24909,27 @@
       </c>
       <c r="AA33" s="21"/>
       <c r="AB33" s="22">
-        <f>-[3]Jun!$G$1</f>
+        <f>-[3]Sep!$G$1</f>
         <v>0</v>
       </c>
       <c r="AC33" s="22">
-        <f>[2]Jun!$G$1</f>
+        <f>[2]Sep!$G$1</f>
         <v>0</v>
       </c>
       <c r="AD33" s="22">
-        <f>-[4]Jun!$N$1+[4]Jun!$AI$1</f>
+        <f>-[4]Sep!$N$1+[4]Sep!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AE33" s="22">
-        <f>-[5]Jun!$N$1+[5]Jun!$AI$1</f>
+        <f>-[5]Sep!$N$1+[5]Sep!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AF33" s="22">
-        <f>-[6]Jun!$N$1+[6]Jun!$AI$1</f>
+        <f>-[6]Sep!$N$1+[6]Sep!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AG33" s="22">
-        <f>[7]Jun!$AF$1</f>
+        <f>[7]Sep!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AH33" s="22"/>
@@ -24941,27 +24941,27 @@
       </c>
       <c r="AL33" s="21"/>
       <c r="AM33" s="22">
-        <f>-[3]Jul!$G$1</f>
+        <f>-[3]Oct!$G$1</f>
         <v>0</v>
       </c>
       <c r="AN33" s="22">
-        <f>[2]Jul!$G$1</f>
+        <f>[2]Oct!$G$1</f>
         <v>0</v>
       </c>
       <c r="AO33" s="22">
-        <f>-[4]Jul!$N$1+[4]Jul!$AI$1</f>
+        <f>-[4]Oct!$N$1+[4]Oct!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AP33" s="22">
-        <f>-[5]Jul!$N$1+[5]Jul!$AI$1</f>
+        <f>-[5]Oct!$N$1+[5]Oct!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AQ33" s="22">
-        <f>-[6]Jul!$N$1+[6]Jul!$AI$1</f>
+        <f>-[6]Oct!$N$1+[6]Oct!$AI$1</f>
         <v>0</v>
       </c>
       <c r="AR33" s="22">
-        <f>[7]Jul!$AF$1</f>
+        <f>[7]Oct!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AS33" s="22"/>
@@ -24973,27 +24973,27 @@
       </c>
       <c r="AW33" s="21"/>
       <c r="AX33" s="22">
-        <f>-[3]Aug!$G$1</f>
+        <f>-[3]Nov!$G$1</f>
         <v>0</v>
       </c>
       <c r="AY33" s="22">
-        <f>[2]Aug!$G$1</f>
+        <f>[2]Nov!$G$1</f>
         <v>0</v>
       </c>
       <c r="AZ33" s="22">
-        <f>-[4]Aug!$N$1+[4]Aug!$AI$1</f>
+        <f>-[4]Nov!$N$1+[4]Nov!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BA33" s="22">
-        <f>-[5]Aug!$N$1+[5]Aug!$AI$1</f>
+        <f>-[5]Nov!$N$1+[5]Nov!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BB33" s="22">
-        <f>-[6]Aug!$N$1+[6]Aug!$AI$1</f>
+        <f>-[6]Nov!$N$1+[6]Nov!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BC33" s="22">
-        <f>[7]Aug!$AF$1</f>
+        <f>[7]Nov!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BD33" s="22"/>
@@ -25005,27 +25005,27 @@
       </c>
       <c r="BH33" s="21"/>
       <c r="BI33" s="22">
-        <f>-[3]Sep!$G$1</f>
+        <f>-[3]Dec!$G$1</f>
         <v>0</v>
       </c>
       <c r="BJ33" s="22">
-        <f>[2]Sep!$G$1</f>
+        <f>[2]Dec!$G$1</f>
         <v>0</v>
       </c>
       <c r="BK33" s="22">
-        <f>-[4]Sep!$N$1+[4]Sep!$AI$1</f>
+        <f>-[4]Dec!$N$1+[4]Dec!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BL33" s="22">
-        <f>-[5]Sep!$N$1+[5]Sep!$AI$1</f>
+        <f>-[5]Dec!$N$1+[5]Dec!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BM33" s="22">
-        <f>-[6]Sep!$N$1+[6]Sep!$AI$1</f>
+        <f>-[6]Dec!$N$1+[6]Dec!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BN33" s="22">
-        <f>[7]Sep!$AF$1</f>
+        <f>[7]Dec!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BO33" s="22"/>
@@ -25037,27 +25037,27 @@
       </c>
       <c r="BS33" s="21"/>
       <c r="BT33" s="22">
-        <f>-[3]Oct!$G$1</f>
+        <f>-[3]Jan!$G$1</f>
         <v>0</v>
       </c>
       <c r="BU33" s="22">
-        <f>[2]Oct!$G$1</f>
+        <f>[2]Jan!$G$1</f>
         <v>0</v>
       </c>
       <c r="BV33" s="22">
-        <f>-[4]Oct!$N$1+[4]Oct!$AI$1</f>
+        <f>-[4]Jan!$N$1+[4]Jan!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BW33" s="22">
-        <f>-[5]Oct!$N$1+[5]Oct!$AI$1</f>
+        <f>-[5]Jan!$N$1+[5]Jan!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BX33" s="22">
-        <f>-[6]Oct!$N$1+[6]Oct!$AI$1</f>
+        <f>-[6]Jan!$N$1+[6]Jan!$AI$1</f>
         <v>0</v>
       </c>
       <c r="BY33" s="22">
-        <f>[7]Oct!$AF$1</f>
+        <f>[7]Jan!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BZ33" s="22"/>
@@ -25069,27 +25069,27 @@
       </c>
       <c r="CD33" s="21"/>
       <c r="CE33" s="22">
-        <f>-[3]Nov!$G$1</f>
+        <f>-[3]Feb!$G$1</f>
         <v>0</v>
       </c>
       <c r="CF33" s="22">
-        <f>[2]Nov!$G$1</f>
+        <f>[2]Feb!$G$1</f>
         <v>0</v>
       </c>
       <c r="CG33" s="22">
-        <f>-[4]Nov!$N$1+[4]Nov!$AI$1</f>
+        <f>-[4]Feb!$N$1+[4]Feb!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CH33" s="22">
-        <f>-[5]Nov!$N$1+[5]Nov!$AI$1</f>
+        <f>-[5]Feb!$N$1+[5]Feb!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CI33" s="22">
-        <f>-[6]Nov!$N$1+[6]Nov!$AI$1</f>
+        <f>-[6]Feb!$N$1+[6]Feb!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CJ33" s="22">
-        <f>[7]Nov!$AF$1</f>
+        <f>[7]Feb!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CK33" s="22"/>
@@ -25101,27 +25101,27 @@
       </c>
       <c r="CO33" s="21"/>
       <c r="CP33" s="22">
-        <f>-[3]Dec!$G$1</f>
+        <f>-[3]Mar!$G$1</f>
         <v>0</v>
       </c>
       <c r="CQ33" s="22">
-        <f>[2]Dec!$G$1</f>
+        <f>[2]Mar!$G$1</f>
         <v>0</v>
       </c>
       <c r="CR33" s="22">
-        <f>-[4]Dec!$N$1+[4]Dec!$AI$1</f>
+        <f>-[4]Mar!$N$1+[4]Mar!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CS33" s="22">
-        <f>-[5]Dec!$N$1+[5]Dec!$AI$1</f>
+        <f>-[5]Mar!$N$1+[5]Mar!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CT33" s="22">
-        <f>-[6]Dec!$N$1+[6]Dec!$AI$1</f>
+        <f>-[6]Mar!$N$1+[6]Mar!$AI$1</f>
         <v>0</v>
       </c>
       <c r="CU33" s="22">
-        <f>[7]Dec!$AF$1</f>
+        <f>[7]Mar!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CV33" s="22"/>
@@ -25133,27 +25133,27 @@
       </c>
       <c r="CZ33" s="21"/>
       <c r="DA33" s="22">
-        <f>-[3]Jan!$G$1</f>
+        <f>-[3]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="DB33" s="22">
-        <f>[2]Jan!$G$1</f>
+        <f>[2]Apr!$G$1</f>
         <v>0</v>
       </c>
       <c r="DC33" s="22">
-        <f>-[4]Jan!$N$1+[4]Jan!$AI$1</f>
+        <f>-[4]Apr!$N$1+[4]Apr!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DD33" s="22">
-        <f>-[5]Jan!$N$1+[5]Jan!$AI$1</f>
+        <f>-[5]Apr!$N$1+[5]Apr!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DE33" s="22">
-        <f>-[6]Jan!$N$1+[6]Jan!$AI$1</f>
+        <f>-[6]Apr!$N$1+[6]Apr!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DF33" s="22">
-        <f>[7]Jan!$AF$1</f>
+        <f>[7]Apr!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DG33" s="22"/>
@@ -25165,27 +25165,27 @@
       </c>
       <c r="DK33" s="21"/>
       <c r="DL33" s="22">
-        <f>-[3]Feb!$G$1</f>
+        <f>-[3]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="DM33" s="22">
-        <f>[2]Feb!$G$1</f>
+        <f>[2]May!$G$1</f>
         <v>0</v>
       </c>
       <c r="DN33" s="22">
-        <f>-[4]Feb!$N$1+[4]Feb!$AI$1</f>
+        <f>-[4]May!$N$1+[4]May!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DO33" s="22">
-        <f>-[5]Feb!$N$1+[5]Feb!$AI$1</f>
+        <f>-[5]May!$N$1+[5]May!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DP33" s="22">
-        <f>-[6]Feb!$N$1+[6]Feb!$AI$1</f>
+        <f>-[6]May!$N$1+[6]May!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DQ33" s="22">
-        <f>[7]Feb!$AF$1</f>
+        <f>[7]May!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DR33" s="22"/>
@@ -25197,27 +25197,27 @@
       </c>
       <c r="DV33" s="21"/>
       <c r="DW33" s="22">
-        <f>-[3]Mar!$G$1</f>
+        <f>-[3]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="DX33" s="22">
-        <f>[2]Mar!$G$1</f>
+        <f>[2]Jun!$G$1</f>
         <v>0</v>
       </c>
       <c r="DY33" s="22">
-        <f>-[4]Mar!$N$1+[4]Mar!$AI$1</f>
+        <f>-[4]Jun!$N$1+[4]Jun!$AI$1</f>
         <v>0</v>
       </c>
       <c r="DZ33" s="22">
-        <f>-[5]Mar!$N$1+[5]Mar!$AI$1</f>
+        <f>-[5]Jun!$N$1+[5]Jun!$AI$1</f>
         <v>0</v>
       </c>
       <c r="EA33" s="22">
-        <f>-[6]Mar!$N$1+[6]Mar!$AI$1</f>
+        <f>-[6]Jun!$N$1+[6]Jun!$AI$1</f>
         <v>0</v>
       </c>
       <c r="EB33" s="22">
-        <f>[7]Mar!$AF$1</f>
+        <f>[7]Jun!$AF$1</f>
         <v>0</v>
       </c>
       <c r="EC33" s="22"/>
@@ -25251,19 +25251,19 @@
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22">
-        <f>[4]Apr!$AH$1</f>
+        <f>[4]Jul!$AH$1</f>
         <v>0</v>
       </c>
       <c r="I34" s="22">
-        <f>[5]Apr!$AH$1</f>
+        <f>[5]Jul!$AH$1</f>
         <v>0</v>
       </c>
       <c r="J34" s="22">
-        <f>[6]Apr!$AH$1</f>
+        <f>[6]Jul!$AH$1</f>
         <v>0</v>
       </c>
       <c r="K34" s="22">
-        <f>[7]Apr!$AE$1</f>
+        <f>[7]Jul!$AE$1</f>
         <v>0</v>
       </c>
       <c r="L34" s="22">
@@ -25279,19 +25279,19 @@
       <c r="Q34" s="22"/>
       <c r="R34" s="22"/>
       <c r="S34" s="22">
-        <f>[4]May!$AH$1</f>
+        <f>[4]Aug!$AH$1</f>
         <v>0</v>
       </c>
       <c r="T34" s="22">
-        <f>[5]May!$AH$1</f>
+        <f>[5]Aug!$AH$1</f>
         <v>0</v>
       </c>
       <c r="U34" s="22">
-        <f>[6]May!$AH$1</f>
+        <f>[6]Aug!$AH$1</f>
         <v>0</v>
       </c>
       <c r="V34" s="22">
-        <f>[7]May!$AE$1</f>
+        <f>[7]Aug!$AE$1</f>
         <v>0</v>
       </c>
       <c r="W34" s="22">
@@ -25308,19 +25308,19 @@
       <c r="AB34" s="22"/>
       <c r="AC34" s="22"/>
       <c r="AD34" s="22">
-        <f>[4]Jun!$AH$1</f>
+        <f>[4]Sep!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AE34" s="22">
-        <f>[5]Jun!$AH$1</f>
+        <f>[5]Sep!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AF34" s="22">
-        <f>[6]Jun!$AH$1</f>
+        <f>[6]Sep!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AG34" s="22">
-        <f>[7]Jun!$AE$1</f>
+        <f>[7]Sep!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AH34" s="22">
@@ -25337,19 +25337,19 @@
       <c r="AM34" s="22"/>
       <c r="AN34" s="22"/>
       <c r="AO34" s="22">
-        <f>[4]Jul!$AH$1</f>
+        <f>[4]Oct!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AP34" s="22">
-        <f>[5]Jul!$AH$1</f>
+        <f>[5]Oct!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AQ34" s="22">
-        <f>[6]Jul!$AH$1</f>
+        <f>[6]Oct!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AR34" s="22">
-        <f>[7]Jul!$AE$1</f>
+        <f>[7]Oct!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AS34" s="22">
@@ -25366,19 +25366,19 @@
       <c r="AX34" s="22"/>
       <c r="AY34" s="22"/>
       <c r="AZ34" s="22">
-        <f>[4]Aug!$AH$1</f>
+        <f>[4]Nov!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BA34" s="22">
-        <f>[5]Aug!$AH$1</f>
+        <f>[5]Nov!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BB34" s="22">
-        <f>[6]Aug!$AH$1</f>
+        <f>[6]Nov!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BC34" s="22">
-        <f>[7]Aug!$AE$1</f>
+        <f>[7]Nov!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BD34" s="22">
@@ -25395,19 +25395,19 @@
       <c r="BI34" s="22"/>
       <c r="BJ34" s="22"/>
       <c r="BK34" s="22">
-        <f>[4]Sep!$AH$1</f>
+        <f>[4]Dec!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BL34" s="22">
-        <f>[5]Sep!$AH$1</f>
+        <f>[5]Dec!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BM34" s="22">
-        <f>[6]Sep!$AH$1</f>
+        <f>[6]Dec!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BN34" s="22">
-        <f>[7]Sep!$AE$1</f>
+        <f>[7]Dec!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BO34" s="22">
@@ -25424,19 +25424,19 @@
       <c r="BT34" s="22"/>
       <c r="BU34" s="22"/>
       <c r="BV34" s="22">
-        <f>[4]Oct!$AH$1</f>
+        <f>[4]Jan!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BW34" s="22">
-        <f>[5]Oct!$AH$1</f>
+        <f>[5]Jan!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BX34" s="22">
-        <f>[6]Oct!$AH$1</f>
+        <f>[6]Jan!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BY34" s="22">
-        <f>[7]Oct!$AE$1</f>
+        <f>[7]Jan!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BZ34" s="22">
@@ -25453,19 +25453,19 @@
       <c r="CE34" s="22"/>
       <c r="CF34" s="22"/>
       <c r="CG34" s="22">
-        <f>[4]Nov!$AH$1</f>
+        <f>[4]Feb!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CH34" s="22">
-        <f>[5]Nov!$AH$1</f>
+        <f>[5]Feb!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CI34" s="22">
-        <f>[6]Nov!$AH$1</f>
+        <f>[6]Feb!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CJ34" s="22">
-        <f>[7]Nov!$AE$1</f>
+        <f>[7]Feb!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CK34" s="22">
@@ -25482,19 +25482,19 @@
       <c r="CP34" s="22"/>
       <c r="CQ34" s="22"/>
       <c r="CR34" s="22">
-        <f>[4]Dec!$AH$1</f>
+        <f>[4]Mar!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CS34" s="22">
-        <f>[5]Dec!$AH$1</f>
+        <f>[5]Mar!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CT34" s="22">
-        <f>[6]Dec!$AH$1</f>
+        <f>[6]Mar!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CU34" s="22">
-        <f>[7]Dec!$AE$1</f>
+        <f>[7]Mar!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CV34" s="22">
@@ -25511,19 +25511,19 @@
       <c r="DA34" s="22"/>
       <c r="DB34" s="22"/>
       <c r="DC34" s="22">
-        <f>[4]Jan!$AH$1</f>
+        <f>[4]Apr!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DD34" s="22">
-        <f>[5]Jan!$AH$1</f>
+        <f>[5]Apr!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DE34" s="22">
-        <f>[6]Jan!$AH$1</f>
+        <f>[6]Apr!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DF34" s="22">
-        <f>[7]Jan!$AE$1</f>
+        <f>[7]Apr!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DG34" s="22">
@@ -25540,19 +25540,19 @@
       <c r="DL34" s="22"/>
       <c r="DM34" s="22"/>
       <c r="DN34" s="22">
-        <f>[4]Feb!$AH$1</f>
+        <f>[4]May!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DO34" s="22">
-        <f>[5]Feb!$AH$1</f>
+        <f>[5]May!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DP34" s="22">
-        <f>[6]Feb!$AH$1</f>
+        <f>[6]May!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DQ34" s="22">
-        <f>[7]Feb!$AE$1</f>
+        <f>[7]May!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DR34" s="22">
@@ -25569,19 +25569,19 @@
       <c r="DW34" s="22"/>
       <c r="DX34" s="22"/>
       <c r="DY34" s="22">
-        <f>[4]Mar!$AH$1</f>
+        <f>[4]Jun!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DZ34" s="22">
-        <f>[5]Mar!$AH$1</f>
+        <f>[5]Jun!$AH$1</f>
         <v>0</v>
       </c>
       <c r="EA34" s="22">
-        <f>[6]Mar!$AH$1</f>
+        <f>[6]Jun!$AH$1</f>
         <v>0</v>
       </c>
       <c r="EB34" s="22">
-        <f>[7]Mar!$AE$1</f>
+        <f>[7]Jun!$AE$1</f>
         <v>0</v>
       </c>
       <c r="EC34" s="22">
@@ -25618,19 +25618,19 @@
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22">
-        <f>[4]Apr!$AK$1</f>
+        <f>[4]Jul!$AK$1</f>
         <v>0</v>
       </c>
       <c r="I35" s="22">
-        <f>[5]Apr!$AK$1</f>
+        <f>[5]Jul!$AK$1</f>
         <v>0</v>
       </c>
       <c r="J35" s="22">
-        <f>[6]Apr!$AK$1</f>
+        <f>[6]Jul!$AK$1</f>
         <v>0</v>
       </c>
       <c r="K35" s="22">
-        <f>[7]Apr!$AH$1</f>
+        <f>[7]Jul!$AH$1</f>
         <v>0</v>
       </c>
       <c r="L35" s="22"/>
@@ -25643,19 +25643,19 @@
       <c r="Q35" s="22"/>
       <c r="R35" s="22"/>
       <c r="S35" s="22">
-        <f>[4]May!$AK$1</f>
+        <f>[4]Aug!$AK$1</f>
         <v>0</v>
       </c>
       <c r="T35" s="22">
-        <f>[5]May!$AK$1</f>
+        <f>[5]Aug!$AK$1</f>
         <v>0</v>
       </c>
       <c r="U35" s="22">
-        <f>[6]May!$AK$1</f>
+        <f>[6]Aug!$AK$1</f>
         <v>0</v>
       </c>
       <c r="V35" s="22">
-        <f>[7]May!$AH$1</f>
+        <f>[7]Aug!$AH$1</f>
         <v>0</v>
       </c>
       <c r="W35" s="22"/>
@@ -25669,19 +25669,19 @@
       <c r="AB35" s="22"/>
       <c r="AC35" s="22"/>
       <c r="AD35" s="22">
-        <f>[4]Jun!$AK$1</f>
+        <f>[4]Sep!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AE35" s="22">
-        <f>[5]Jun!$AK$1</f>
+        <f>[5]Sep!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AF35" s="22">
-        <f>[6]Jun!$AK$1</f>
+        <f>[6]Sep!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AG35" s="22">
-        <f>[7]Jun!$AH$1</f>
+        <f>[7]Sep!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AH35" s="22"/>
@@ -25695,19 +25695,19 @@
       <c r="AM35" s="22"/>
       <c r="AN35" s="22"/>
       <c r="AO35" s="22">
-        <f>[4]Jul!$AK$1</f>
+        <f>[4]Oct!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AP35" s="22">
-        <f>[5]Jul!$AK$1</f>
+        <f>[5]Oct!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AQ35" s="22">
-        <f>[6]Jul!$AK$1</f>
+        <f>[6]Oct!$AK$1</f>
         <v>0</v>
       </c>
       <c r="AR35" s="22">
-        <f>[7]Jul!$AH$1</f>
+        <f>[7]Oct!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AS35" s="22"/>
@@ -25721,19 +25721,19 @@
       <c r="AX35" s="22"/>
       <c r="AY35" s="22"/>
       <c r="AZ35" s="22">
-        <f>[4]Aug!$AK$1</f>
+        <f>[4]Nov!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BA35" s="22">
-        <f>[5]Aug!$AK$1</f>
+        <f>[5]Nov!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BB35" s="22">
-        <f>[6]Aug!$AK$1</f>
+        <f>[6]Nov!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BC35" s="22">
-        <f>[7]Aug!$AH$1</f>
+        <f>[7]Nov!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BD35" s="22"/>
@@ -25747,19 +25747,19 @@
       <c r="BI35" s="22"/>
       <c r="BJ35" s="22"/>
       <c r="BK35" s="22">
-        <f>[4]Sep!$AK$1</f>
+        <f>[4]Dec!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BL35" s="22">
-        <f>[5]Sep!$AK$1</f>
+        <f>[5]Dec!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BM35" s="22">
-        <f>[6]Sep!$AK$1</f>
+        <f>[6]Dec!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BN35" s="22">
-        <f>[7]Sep!$AH$1</f>
+        <f>[7]Dec!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BO35" s="22"/>
@@ -25773,19 +25773,19 @@
       <c r="BT35" s="22"/>
       <c r="BU35" s="22"/>
       <c r="BV35" s="22">
-        <f>[4]Oct!$AK$1</f>
+        <f>[4]Jan!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BW35" s="22">
-        <f>[5]Oct!$AK$1</f>
+        <f>[5]Jan!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BX35" s="22">
-        <f>[6]Oct!$AK$1</f>
+        <f>[6]Jan!$AK$1</f>
         <v>0</v>
       </c>
       <c r="BY35" s="22">
-        <f>[7]Oct!$AH$1</f>
+        <f>[7]Jan!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BZ35" s="22"/>
@@ -25799,19 +25799,19 @@
       <c r="CE35" s="22"/>
       <c r="CF35" s="22"/>
       <c r="CG35" s="22">
-        <f>[4]Nov!$AK$1</f>
+        <f>[4]Feb!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CH35" s="22">
-        <f>[5]Nov!$AK$1</f>
+        <f>[5]Feb!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CI35" s="22">
-        <f>[6]Nov!$AK$1</f>
+        <f>[6]Feb!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CJ35" s="22">
-        <f>[7]Nov!$AH$1</f>
+        <f>[7]Feb!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CK35" s="22"/>
@@ -25825,19 +25825,19 @@
       <c r="CP35" s="22"/>
       <c r="CQ35" s="22"/>
       <c r="CR35" s="22">
-        <f>[4]Dec!$AK$1</f>
+        <f>[4]Mar!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CS35" s="22">
-        <f>[5]Dec!$AK$1</f>
+        <f>[5]Mar!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CT35" s="22">
-        <f>[6]Dec!$AK$1</f>
+        <f>[6]Mar!$AK$1</f>
         <v>0</v>
       </c>
       <c r="CU35" s="22">
-        <f>[7]Dec!$AH$1</f>
+        <f>[7]Mar!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CV35" s="22"/>
@@ -25851,19 +25851,19 @@
       <c r="DA35" s="22"/>
       <c r="DB35" s="22"/>
       <c r="DC35" s="22">
-        <f>[4]Jan!$AK$1</f>
+        <f>[4]Apr!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DD35" s="22">
-        <f>[5]Jan!$AK$1</f>
+        <f>[5]Apr!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DE35" s="22">
-        <f>[6]Jan!$AK$1</f>
+        <f>[6]Apr!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DF35" s="22">
-        <f>[7]Jan!$AH$1</f>
+        <f>[7]Apr!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DG35" s="22"/>
@@ -25877,19 +25877,19 @@
       <c r="DL35" s="22"/>
       <c r="DM35" s="22"/>
       <c r="DN35" s="22">
-        <f>[4]Feb!$AK$1</f>
+        <f>[4]May!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DO35" s="22">
-        <f>[5]Feb!$AK$1</f>
+        <f>[5]May!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DP35" s="22">
-        <f>[6]Feb!$AK$1</f>
+        <f>[6]May!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DQ35" s="22">
-        <f>[7]Feb!$AH$1</f>
+        <f>[7]May!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DR35" s="22"/>
@@ -25903,19 +25903,19 @@
       <c r="DW35" s="22"/>
       <c r="DX35" s="22"/>
       <c r="DY35" s="22">
-        <f>[4]Mar!$AK$1</f>
+        <f>[4]Jun!$AK$1</f>
         <v>0</v>
       </c>
       <c r="DZ35" s="22">
-        <f>[5]Mar!$AK$1</f>
+        <f>[5]Jun!$AK$1</f>
         <v>0</v>
       </c>
       <c r="EA35" s="22">
-        <f>[6]Mar!$AK$1</f>
+        <f>[6]Jun!$AK$1</f>
         <v>0</v>
       </c>
       <c r="EB35" s="22">
-        <f>[7]Mar!$AH$1</f>
+        <f>[7]Jun!$AH$1</f>
         <v>0</v>
       </c>
       <c r="EC35" s="22"/>
@@ -26101,19 +26101,19 @@
       <c r="F37" s="22"/>
       <c r="G37" s="22"/>
       <c r="H37" s="22">
-        <f>-[4]Apr!$L$1+[4]Apr!$AF$1</f>
+        <f>-[4]Jul!$L$1+[4]Jul!$AF$1</f>
         <v>0</v>
       </c>
       <c r="I37" s="22">
-        <f>-[5]Apr!$L$1+[5]Apr!$AF$1</f>
+        <f>-[5]Jul!$L$1+[5]Jul!$AF$1</f>
         <v>0</v>
       </c>
       <c r="J37" s="22">
-        <f>-[6]Apr!$L$1+[6]Apr!$AF$1</f>
+        <f>-[6]Jul!$L$1+[6]Jul!$AF$1</f>
         <v>0</v>
       </c>
       <c r="K37" s="22">
-        <f>-[7]Apr!$L$1+[7]Apr!$AC$1</f>
+        <f>-[7]Jul!$L$1+[7]Jul!$AC$1</f>
         <v>0</v>
       </c>
       <c r="L37" s="22"/>
@@ -26126,19 +26126,19 @@
       <c r="Q37" s="22"/>
       <c r="R37" s="22"/>
       <c r="S37" s="22">
-        <f>-[4]May!$L$1+[4]May!$AF$1</f>
+        <f>-[4]Aug!$L$1+[4]Aug!$AF$1</f>
         <v>0</v>
       </c>
       <c r="T37" s="22">
-        <f>-[5]May!$L$1+[5]May!$AF$1</f>
+        <f>-[5]Aug!$L$1+[5]Aug!$AF$1</f>
         <v>0</v>
       </c>
       <c r="U37" s="22">
-        <f>-[6]May!$L$1+[6]May!$AF$1</f>
+        <f>-[6]Aug!$L$1+[6]Aug!$AF$1</f>
         <v>0</v>
       </c>
       <c r="V37" s="22">
-        <f>-[7]May!$L$1+[7]May!$AC$1</f>
+        <f>-[7]Aug!$L$1+[7]Aug!$AC$1</f>
         <v>0</v>
       </c>
       <c r="W37" s="22"/>
@@ -26152,19 +26152,19 @@
       <c r="AB37" s="22"/>
       <c r="AC37" s="22"/>
       <c r="AD37" s="22">
-        <f>-[4]Jun!$L$1+[4]Jun!$AF$1</f>
+        <f>-[4]Sep!$L$1+[4]Sep!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AE37" s="22">
-        <f>-[5]Jun!$L$1+[5]Jun!$AF$1</f>
+        <f>-[5]Sep!$L$1+[5]Sep!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AF37" s="22">
-        <f>-[6]Jun!$L$1+[6]Jun!$AF$1</f>
+        <f>-[6]Sep!$L$1+[6]Sep!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AG37" s="22">
-        <f>-[7]Jun!$L$1+[7]Jun!$AC$1</f>
+        <f>-[7]Sep!$L$1+[7]Sep!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AH37" s="22"/>
@@ -26178,19 +26178,19 @@
       <c r="AM37" s="22"/>
       <c r="AN37" s="22"/>
       <c r="AO37" s="22">
-        <f>-[4]Jul!$L$1+[4]Jul!$AF$1</f>
+        <f>-[4]Oct!$L$1+[4]Oct!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AP37" s="22">
-        <f>-[5]Jul!$L$1+[5]Jul!$AF$1</f>
+        <f>-[5]Oct!$L$1+[5]Oct!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AQ37" s="22">
-        <f>-[6]Jul!$L$1+[6]Jul!$AF$1</f>
+        <f>-[6]Oct!$L$1+[6]Oct!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AR37" s="22">
-        <f>-[7]Jul!$L$1+[7]Jul!$AC$1</f>
+        <f>-[7]Oct!$L$1+[7]Oct!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AS37" s="22"/>
@@ -26204,19 +26204,19 @@
       <c r="AX37" s="22"/>
       <c r="AY37" s="22"/>
       <c r="AZ37" s="22">
-        <f>-[4]Aug!$L$1+[4]Aug!$AF$1</f>
+        <f>-[4]Nov!$L$1+[4]Nov!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BA37" s="22">
-        <f>-[5]Aug!$L$1+[5]Aug!$AF$1</f>
+        <f>-[5]Nov!$L$1+[5]Nov!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BB37" s="22">
-        <f>-[6]Aug!$L$1+[6]Aug!$AF$1</f>
+        <f>-[6]Nov!$L$1+[6]Nov!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BC37" s="22">
-        <f>-[7]Aug!$L$1+[7]Aug!$AC$1</f>
+        <f>-[7]Nov!$L$1+[7]Nov!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BD37" s="22"/>
@@ -26230,19 +26230,19 @@
       <c r="BI37" s="22"/>
       <c r="BJ37" s="22"/>
       <c r="BK37" s="22">
-        <f>-[4]Sep!$L$1+[4]Sep!$AF$1</f>
+        <f>-[4]Dec!$L$1+[4]Dec!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BL37" s="22">
-        <f>-[5]Sep!$L$1+[5]Sep!$AF$1</f>
+        <f>-[5]Dec!$L$1+[5]Dec!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BM37" s="22">
-        <f>-[6]Sep!$L$1+[6]Sep!$AF$1</f>
+        <f>-[6]Dec!$L$1+[6]Dec!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BN37" s="22">
-        <f>-[7]Sep!$L$1+[7]Sep!$AC$1</f>
+        <f>-[7]Dec!$L$1+[7]Dec!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BO37" s="22"/>
@@ -26256,19 +26256,19 @@
       <c r="BT37" s="22"/>
       <c r="BU37" s="22"/>
       <c r="BV37" s="22">
-        <f>-[4]Oct!$L$1+[4]Oct!$AF$1</f>
+        <f>-[4]Jan!$L$1+[4]Jan!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BW37" s="22">
-        <f>-[5]Oct!$L$1+[5]Oct!$AF$1</f>
+        <f>-[5]Jan!$L$1+[5]Jan!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BX37" s="22">
-        <f>-[6]Oct!$L$1+[6]Oct!$AF$1</f>
+        <f>-[6]Jan!$L$1+[6]Jan!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BY37" s="22">
-        <f>-[7]Oct!$L$1+[7]Oct!$AC$1</f>
+        <f>-[7]Jan!$L$1+[7]Jan!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BZ37" s="22"/>
@@ -26282,19 +26282,19 @@
       <c r="CE37" s="22"/>
       <c r="CF37" s="22"/>
       <c r="CG37" s="22">
-        <f>-[4]Nov!$L$1+[4]Nov!$AF$1</f>
+        <f>-[4]Feb!$L$1+[4]Feb!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CH37" s="22">
-        <f>-[5]Nov!$L$1+[5]Nov!$AF$1</f>
+        <f>-[5]Feb!$L$1+[5]Feb!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CI37" s="22">
-        <f>-[6]Nov!$L$1+[6]Nov!$AF$1</f>
+        <f>-[6]Feb!$L$1+[6]Feb!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CJ37" s="22">
-        <f>-[7]Nov!$L$1+[7]Nov!$AC$1</f>
+        <f>-[7]Feb!$L$1+[7]Feb!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CK37" s="22"/>
@@ -26308,19 +26308,19 @@
       <c r="CP37" s="22"/>
       <c r="CQ37" s="22"/>
       <c r="CR37" s="22">
-        <f>-[4]Dec!$L$1+[4]Dec!$AF$1</f>
+        <f>-[4]Mar!$L$1+[4]Mar!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CS37" s="22">
-        <f>-[5]Dec!$L$1+[5]Dec!$AF$1</f>
+        <f>-[5]Mar!$L$1+[5]Mar!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CT37" s="22">
-        <f>-[6]Dec!$L$1+[6]Dec!$AF$1</f>
+        <f>-[6]Mar!$L$1+[6]Mar!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CU37" s="22">
-        <f>-[7]Dec!$L$1+[7]Dec!$AC$1</f>
+        <f>-[7]Mar!$L$1+[7]Mar!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CV37" s="22"/>
@@ -26334,19 +26334,19 @@
       <c r="DA37" s="22"/>
       <c r="DB37" s="22"/>
       <c r="DC37" s="22">
-        <f>-[4]Jan!$L$1+[4]Jan!$AF$1</f>
+        <f>-[4]Apr!$L$1+[4]Apr!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DD37" s="22">
-        <f>-[5]Jan!$L$1+[5]Jan!$AF$1</f>
+        <f>-[5]Apr!$L$1+[5]Apr!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DE37" s="22">
-        <f>-[6]Jan!$L$1+[6]Jan!$AF$1</f>
+        <f>-[6]Apr!$L$1+[6]Apr!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DF37" s="22">
-        <f>-[7]Jan!$L$1+[7]Jan!$AC$1</f>
+        <f>-[7]Apr!$L$1+[7]Apr!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DG37" s="22"/>
@@ -26360,19 +26360,19 @@
       <c r="DL37" s="22"/>
       <c r="DM37" s="22"/>
       <c r="DN37" s="22">
-        <f>-[4]Feb!$L$1+[4]Feb!$AF$1</f>
+        <f>-[4]May!$L$1+[4]May!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DO37" s="22">
-        <f>-[5]Feb!$L$1+[5]Feb!$AF$1</f>
+        <f>-[5]May!$L$1+[5]May!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DP37" s="22">
-        <f>-[6]Feb!$L$1+[6]Feb!$AF$1</f>
+        <f>-[6]May!$L$1+[6]May!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DQ37" s="22">
-        <f>-[7]Feb!$L$1+[7]Feb!$AC$1</f>
+        <f>-[7]May!$L$1+[7]May!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DR37" s="22"/>
@@ -26386,19 +26386,19 @@
       <c r="DW37" s="22"/>
       <c r="DX37" s="22"/>
       <c r="DY37" s="22">
-        <f>-[4]Mar!$L$1+[4]Mar!$AF$1</f>
+        <f>-[4]Jun!$L$1+[4]Jun!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DZ37" s="22">
-        <f>-[5]Mar!$L$1+[5]Mar!$AF$1</f>
+        <f>-[5]Jun!$L$1+[5]Jun!$AF$1</f>
         <v>0</v>
       </c>
       <c r="EA37" s="22">
-        <f>-[6]Mar!$L$1+[6]Mar!$AF$1</f>
+        <f>-[6]Jun!$L$1+[6]Jun!$AF$1</f>
         <v>0</v>
       </c>
       <c r="EB37" s="22">
-        <f>-[7]Mar!$L$1+[7]Mar!$AC$1</f>
+        <f>-[7]Jun!$L$1+[7]Jun!$AC$1</f>
         <v>0</v>
       </c>
       <c r="EC37" s="22"/>
@@ -26577,19 +26577,19 @@
       <c r="F39" s="22"/>
       <c r="G39" s="22"/>
       <c r="H39" s="22">
-        <f>-[4]Apr!$P$1+[4]Apr!$AM$1</f>
+        <f>-[4]Jul!$P$1+[4]Jul!$AM$1</f>
         <v>0</v>
       </c>
       <c r="I39" s="22">
-        <f>-[5]Apr!$P$1+[5]Apr!$AM$1</f>
+        <f>-[5]Jul!$P$1+[5]Jul!$AM$1</f>
         <v>0</v>
       </c>
       <c r="J39" s="22">
-        <f>-[6]Apr!$P$1+[6]Apr!$AM$1</f>
+        <f>-[6]Jul!$P$1+[6]Jul!$AM$1</f>
         <v>0</v>
       </c>
       <c r="K39" s="22">
-        <f>-[7]Apr!$N$1+[7]Apr!$AJ$1</f>
+        <f>-[7]Jul!$N$1+[7]Jul!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="L39" s="22"/>
@@ -26602,19 +26602,19 @@
       <c r="Q39" s="22"/>
       <c r="R39" s="22"/>
       <c r="S39" s="22">
-        <f>-[4]May!$P$1+[4]May!$AM$1</f>
+        <f>-[4]Aug!$P$1+[4]Aug!$AM$1</f>
         <v>0</v>
       </c>
       <c r="T39" s="22">
-        <f>-[5]May!$P$1+[5]May!$AM$1</f>
+        <f>-[5]Aug!$P$1+[5]Aug!$AM$1</f>
         <v>0</v>
       </c>
       <c r="U39" s="22">
-        <f>-[6]May!$P$1+[6]May!$AM$1</f>
+        <f>-[6]Aug!$P$1+[6]Aug!$AM$1</f>
         <v>0</v>
       </c>
       <c r="V39" s="22">
-        <f>-[7]May!$N$1+[7]May!$AJ$1</f>
+        <f>-[7]Aug!$N$1+[7]Aug!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="W39" s="22"/>
@@ -26628,19 +26628,19 @@
       <c r="AB39" s="22"/>
       <c r="AC39" s="22"/>
       <c r="AD39" s="22">
-        <f>-[4]Jun!$P$1+[4]Jun!$AM$1</f>
+        <f>-[4]Sep!$P$1+[4]Sep!$AM$1</f>
         <v>0</v>
       </c>
       <c r="AE39" s="22">
-        <f>-[5]Jun!$P$1+[5]Jun!$AM$1</f>
+        <f>-[5]Sep!$P$1+[5]Sep!$AM$1</f>
         <v>0</v>
       </c>
       <c r="AF39" s="22">
-        <f>-[6]Jun!$P$1+[6]Jun!$AM$1</f>
+        <f>-[6]Sep!$P$1+[6]Sep!$AM$1</f>
         <v>0</v>
       </c>
       <c r="AG39" s="22">
-        <f>-[7]Jun!$N$1+[7]Jun!$AJ$1</f>
+        <f>-[7]Sep!$N$1+[7]Sep!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AH39" s="22"/>
@@ -26654,19 +26654,19 @@
       <c r="AM39" s="22"/>
       <c r="AN39" s="22"/>
       <c r="AO39" s="22">
-        <f>-[4]Jul!$P$1+[4]Jul!$AM$1</f>
+        <f>-[4]Oct!$P$1+[4]Oct!$AM$1</f>
         <v>0</v>
       </c>
       <c r="AP39" s="22">
-        <f>-[5]Jul!$P$1+[5]Jul!$AM$1</f>
+        <f>-[5]Oct!$P$1+[5]Oct!$AM$1</f>
         <v>0</v>
       </c>
       <c r="AQ39" s="22">
-        <f>-[6]Jul!$P$1+[6]Jul!$AM$1</f>
+        <f>-[6]Oct!$P$1+[6]Oct!$AM$1</f>
         <v>0</v>
       </c>
       <c r="AR39" s="22">
-        <f>-[7]Jul!$N$1+[7]Jul!$AJ$1</f>
+        <f>-[7]Oct!$N$1+[7]Oct!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="AS39" s="22"/>
@@ -26680,19 +26680,19 @@
       <c r="AX39" s="22"/>
       <c r="AY39" s="22"/>
       <c r="AZ39" s="22">
-        <f>-[4]Aug!$P$1+[4]Aug!$AM$1</f>
+        <f>-[4]Nov!$P$1+[4]Nov!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BA39" s="22">
-        <f>-[5]Aug!$P$1+[5]Aug!$AM$1</f>
+        <f>-[5]Nov!$P$1+[5]Nov!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BB39" s="22">
-        <f>-[6]Aug!$P$1+[6]Aug!$AM$1</f>
+        <f>-[6]Nov!$P$1+[6]Nov!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BC39" s="22">
-        <f>-[7]Aug!$N$1+[7]Aug!$AJ$1</f>
+        <f>-[7]Nov!$N$1+[7]Nov!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BD39" s="22"/>
@@ -26706,19 +26706,19 @@
       <c r="BI39" s="22"/>
       <c r="BJ39" s="22"/>
       <c r="BK39" s="22">
-        <f>-[4]Sep!$P$1+[4]Sep!$AM$1</f>
+        <f>-[4]Dec!$P$1+[4]Dec!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BL39" s="22">
-        <f>-[5]Sep!$P$1+[5]Sep!$AM$1</f>
+        <f>-[5]Dec!$P$1+[5]Dec!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BM39" s="22">
-        <f>-[6]Sep!$P$1+[6]Sep!$AM$1</f>
+        <f>-[6]Dec!$P$1+[6]Dec!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BN39" s="22">
-        <f>-[7]Sep!$N$1+[7]Sep!$AJ$1</f>
+        <f>-[7]Dec!$N$1+[7]Dec!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BO39" s="22"/>
@@ -26732,19 +26732,19 @@
       <c r="BT39" s="22"/>
       <c r="BU39" s="22"/>
       <c r="BV39" s="22">
-        <f>-[4]Oct!$P$1+[4]Oct!$AM$1</f>
+        <f>-[4]Jan!$P$1+[4]Jan!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BW39" s="22">
-        <f>-[5]Oct!$P$1+[5]Oct!$AM$1</f>
+        <f>-[5]Jan!$P$1+[5]Jan!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BX39" s="22">
-        <f>-[6]Oct!$P$1+[6]Oct!$AM$1</f>
+        <f>-[6]Jan!$P$1+[6]Jan!$AM$1</f>
         <v>0</v>
       </c>
       <c r="BY39" s="22">
-        <f>-[7]Oct!$N$1+[7]Oct!$AJ$1</f>
+        <f>-[7]Jan!$N$1+[7]Jan!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="BZ39" s="22"/>
@@ -26758,19 +26758,19 @@
       <c r="CE39" s="22"/>
       <c r="CF39" s="22"/>
       <c r="CG39" s="22">
-        <f>-[4]Nov!$P$1+[4]Nov!$AM$1</f>
+        <f>-[4]Feb!$P$1+[4]Feb!$AM$1</f>
         <v>0</v>
       </c>
       <c r="CH39" s="22">
-        <f>-[5]Nov!$P$1+[5]Nov!$AM$1</f>
+        <f>-[5]Feb!$P$1+[5]Feb!$AM$1</f>
         <v>0</v>
       </c>
       <c r="CI39" s="22">
-        <f>-[6]Nov!$P$1+[6]Nov!$AM$1</f>
+        <f>-[6]Feb!$P$1+[6]Feb!$AM$1</f>
         <v>0</v>
       </c>
       <c r="CJ39" s="22">
-        <f>-[7]Nov!$N$1+[7]Nov!$AJ$1</f>
+        <f>-[7]Feb!$N$1+[7]Feb!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CK39" s="22"/>
@@ -26784,19 +26784,19 @@
       <c r="CP39" s="22"/>
       <c r="CQ39" s="22"/>
       <c r="CR39" s="22">
-        <f>-[4]Dec!$P$1+[4]Dec!$AM$1</f>
+        <f>-[4]Mar!$P$1+[4]Mar!$AM$1</f>
         <v>0</v>
       </c>
       <c r="CS39" s="22">
-        <f>-[5]Dec!$P$1+[5]Dec!$AM$1</f>
+        <f>-[5]Mar!$P$1+[5]Mar!$AM$1</f>
         <v>0</v>
       </c>
       <c r="CT39" s="22">
-        <f>-[6]Dec!$P$1+[6]Dec!$AM$1</f>
+        <f>-[6]Mar!$P$1+[6]Mar!$AM$1</f>
         <v>0</v>
       </c>
       <c r="CU39" s="22">
-        <f>-[7]Dec!$N$1+[7]Dec!$AJ$1</f>
+        <f>-[7]Mar!$N$1+[7]Mar!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="CV39" s="22"/>
@@ -26810,19 +26810,19 @@
       <c r="DA39" s="22"/>
       <c r="DB39" s="22"/>
       <c r="DC39" s="22">
-        <f>-[4]Jan!$P$1+[4]Jan!$AM$1</f>
+        <f>-[4]Apr!$P$1+[4]Apr!$AM$1</f>
         <v>0</v>
       </c>
       <c r="DD39" s="22">
-        <f>-[5]Jan!$P$1+[5]Jan!$AM$1</f>
+        <f>-[5]Apr!$P$1+[5]Apr!$AM$1</f>
         <v>0</v>
       </c>
       <c r="DE39" s="22">
-        <f>-[6]Jan!$P$1+[6]Jan!$AM$1</f>
+        <f>-[6]Apr!$P$1+[6]Apr!$AM$1</f>
         <v>0</v>
       </c>
       <c r="DF39" s="22">
-        <f>-[7]Jan!$N$1+[7]Jan!$AJ$1</f>
+        <f>-[7]Apr!$N$1+[7]Apr!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DG39" s="22"/>
@@ -26836,19 +26836,19 @@
       <c r="DL39" s="22"/>
       <c r="DM39" s="22"/>
       <c r="DN39" s="22">
-        <f>-[4]Feb!$P$1+[4]Feb!$AM$1</f>
+        <f>-[4]May!$P$1+[4]May!$AM$1</f>
         <v>0</v>
       </c>
       <c r="DO39" s="22">
-        <f>-[5]Feb!$P$1+[5]Feb!$AM$1</f>
+        <f>-[5]May!$P$1+[5]May!$AM$1</f>
         <v>0</v>
       </c>
       <c r="DP39" s="22">
-        <f>-[6]Feb!$P$1+[6]Feb!$AM$1</f>
+        <f>-[6]May!$P$1+[6]May!$AM$1</f>
         <v>0</v>
       </c>
       <c r="DQ39" s="22">
-        <f>-[7]Feb!$N$1+[7]Feb!$AJ$1</f>
+        <f>-[7]May!$N$1+[7]May!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="DR39" s="22"/>
@@ -26862,19 +26862,19 @@
       <c r="DW39" s="22"/>
       <c r="DX39" s="22"/>
       <c r="DY39" s="22">
-        <f>-[4]Mar!$P$1+[4]Mar!$AM$1</f>
+        <f>-[4]Jun!$P$1+[4]Jun!$AM$1</f>
         <v>0</v>
       </c>
       <c r="DZ39" s="22">
-        <f>-[5]Mar!$P$1+[5]Mar!$AM$1</f>
+        <f>-[5]Jun!$P$1+[5]Jun!$AM$1</f>
         <v>0</v>
       </c>
       <c r="EA39" s="22">
-        <f>-[6]Mar!$P$1+[6]Mar!$AM$1</f>
+        <f>-[6]Jun!$P$1+[6]Jun!$AM$1</f>
         <v>0</v>
       </c>
       <c r="EB39" s="22">
-        <f>-[7]Mar!$N$1+[7]Mar!$AJ$1</f>
+        <f>-[7]Jun!$N$1+[7]Jun!$AJ$1</f>
         <v>0</v>
       </c>
       <c r="EC39" s="22"/>
@@ -26908,19 +26908,19 @@
       <c r="F40" s="22"/>
       <c r="G40" s="22"/>
       <c r="H40" s="22">
-        <f>-[4]Apr!$M$1+[4]Apr!$AG$1</f>
+        <f>-[4]Jul!$M$1+[4]Jul!$AG$1</f>
         <v>0</v>
       </c>
       <c r="I40" s="22">
-        <f>-[5]Apr!$M$1+[5]Apr!$AG$1</f>
+        <f>-[5]Jul!$M$1+[5]Jul!$AG$1</f>
         <v>0</v>
       </c>
       <c r="J40" s="22">
-        <f>-[6]Apr!$M$1+[6]Apr!$AG$1</f>
+        <f>-[6]Jul!$M$1+[6]Jul!$AG$1</f>
         <v>0</v>
       </c>
       <c r="K40" s="22">
-        <f>-[7]Apr!$M$1+[7]Apr!$AD$1</f>
+        <f>-[7]Jul!$M$1+[7]Jul!$AD$1</f>
         <v>0</v>
       </c>
       <c r="L40" s="22"/>
@@ -26933,19 +26933,19 @@
       <c r="Q40" s="22"/>
       <c r="R40" s="22"/>
       <c r="S40" s="22">
-        <f>-[4]May!$M$1+[4]May!$AG$1</f>
+        <f>-[4]Aug!$M$1+[4]Aug!$AG$1</f>
         <v>0</v>
       </c>
       <c r="T40" s="22">
-        <f>-[5]May!$M$1+[5]May!$AG$1</f>
+        <f>-[5]Aug!$M$1+[5]Aug!$AG$1</f>
         <v>0</v>
       </c>
       <c r="U40" s="22">
-        <f>-[6]May!$M$1+[6]May!$AG$1</f>
+        <f>-[6]Aug!$M$1+[6]Aug!$AG$1</f>
         <v>0</v>
       </c>
       <c r="V40" s="22">
-        <f>-[7]May!$M$1+[7]May!$AD$1</f>
+        <f>-[7]Aug!$M$1+[7]Aug!$AD$1</f>
         <v>0</v>
       </c>
       <c r="W40" s="22"/>
@@ -26959,19 +26959,19 @@
       <c r="AB40" s="22"/>
       <c r="AC40" s="22"/>
       <c r="AD40" s="22">
-        <f>-[4]Jun!$M$1+[4]Jun!$AG$1</f>
+        <f>-[4]Sep!$M$1+[4]Sep!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AE40" s="22">
-        <f>-[5]Jun!$M$1+[5]Jun!$AG$1</f>
+        <f>-[5]Sep!$M$1+[5]Sep!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AF40" s="22">
-        <f>-[6]Jun!$M$1+[6]Jun!$AG$1</f>
+        <f>-[6]Sep!$M$1+[6]Sep!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AG40" s="22">
-        <f>-[7]Jun!$M$1+[7]Jun!$AD$1</f>
+        <f>-[7]Sep!$M$1+[7]Sep!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AH40" s="22"/>
@@ -26985,19 +26985,19 @@
       <c r="AM40" s="22"/>
       <c r="AN40" s="22"/>
       <c r="AO40" s="22">
-        <f>-[4]Jul!$M$1+[4]Jul!$AG$1</f>
+        <f>-[4]Oct!$M$1+[4]Oct!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AP40" s="22">
-        <f>-[5]Jul!$M$1+[5]Jul!$AG$1</f>
+        <f>-[5]Oct!$M$1+[5]Oct!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AQ40" s="22">
-        <f>-[6]Jul!$M$1+[6]Jul!$AG$1</f>
+        <f>-[6]Oct!$M$1+[6]Oct!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AR40" s="22">
-        <f>-[7]Jul!$M$1+[7]Jul!$AD$1</f>
+        <f>-[7]Oct!$M$1+[7]Oct!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AS40" s="22"/>
@@ -27011,19 +27011,19 @@
       <c r="AX40" s="22"/>
       <c r="AY40" s="22"/>
       <c r="AZ40" s="22">
-        <f>-[4]Aug!$M$1+[4]Aug!$AG$1</f>
+        <f>-[4]Nov!$M$1+[4]Nov!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BA40" s="22">
-        <f>-[5]Aug!$M$1+[5]Aug!$AG$1</f>
+        <f>-[5]Nov!$M$1+[5]Nov!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BB40" s="22">
-        <f>-[6]Aug!$M$1+[6]Aug!$AG$1</f>
+        <f>-[6]Nov!$M$1+[6]Nov!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BC40" s="22">
-        <f>-[7]Aug!$M$1+[7]Aug!$AD$1</f>
+        <f>-[7]Nov!$M$1+[7]Nov!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BD40" s="22"/>
@@ -27037,19 +27037,19 @@
       <c r="BI40" s="22"/>
       <c r="BJ40" s="22"/>
       <c r="BK40" s="22">
-        <f>-[4]Sep!$M$1+[4]Sep!$AG$1</f>
+        <f>-[4]Dec!$M$1+[4]Dec!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BL40" s="22">
-        <f>-[5]Sep!$M$1+[5]Sep!$AG$1</f>
+        <f>-[5]Dec!$M$1+[5]Dec!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BM40" s="22">
-        <f>-[6]Sep!$M$1+[6]Sep!$AG$1</f>
+        <f>-[6]Dec!$M$1+[6]Dec!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BN40" s="22">
-        <f>-[7]Sep!$M$1+[7]Sep!$AD$1</f>
+        <f>-[7]Dec!$M$1+[7]Dec!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BO40" s="22"/>
@@ -27063,19 +27063,19 @@
       <c r="BT40" s="22"/>
       <c r="BU40" s="22"/>
       <c r="BV40" s="22">
-        <f>-[4]Oct!$M$1+[4]Oct!$AG$1</f>
+        <f>-[4]Jan!$M$1+[4]Jan!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BW40" s="22">
-        <f>-[5]Oct!$M$1+[5]Oct!$AG$1</f>
+        <f>-[5]Jan!$M$1+[5]Jan!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BX40" s="22">
-        <f>-[6]Oct!$M$1+[6]Oct!$AG$1</f>
+        <f>-[6]Jan!$M$1+[6]Jan!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BY40" s="22">
-        <f>-[7]Oct!$M$1+[7]Oct!$AD$1</f>
+        <f>-[7]Jan!$M$1+[7]Jan!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BZ40" s="22"/>
@@ -27089,19 +27089,19 @@
       <c r="CE40" s="22"/>
       <c r="CF40" s="22"/>
       <c r="CG40" s="22">
-        <f>-[4]Nov!$M$1+[4]Nov!$AG$1</f>
+        <f>-[4]Feb!$M$1+[4]Feb!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CH40" s="22">
-        <f>-[5]Nov!$M$1+[5]Nov!$AG$1</f>
+        <f>-[5]Feb!$M$1+[5]Feb!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CI40" s="22">
-        <f>-[6]Nov!$M$1+[6]Nov!$AG$1</f>
+        <f>-[6]Feb!$M$1+[6]Feb!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CJ40" s="22">
-        <f>-[7]Nov!$M$1+[7]Nov!$AD$1</f>
+        <f>-[7]Feb!$M$1+[7]Feb!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CK40" s="22"/>
@@ -27115,19 +27115,19 @@
       <c r="CP40" s="22"/>
       <c r="CQ40" s="22"/>
       <c r="CR40" s="22">
-        <f>-[4]Dec!$M$1+[4]Dec!$AG$1</f>
+        <f>-[4]Mar!$M$1+[4]Mar!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CS40" s="22">
-        <f>-[5]Dec!$M$1+[5]Dec!$AG$1</f>
+        <f>-[5]Mar!$M$1+[5]Mar!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CT40" s="22">
-        <f>-[6]Dec!$M$1+[6]Dec!$AG$1</f>
+        <f>-[6]Mar!$M$1+[6]Mar!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CU40" s="22">
-        <f>-[7]Dec!$M$1+[7]Dec!$AD$1</f>
+        <f>-[7]Mar!$M$1+[7]Mar!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CV40" s="22"/>
@@ -27141,19 +27141,19 @@
       <c r="DA40" s="22"/>
       <c r="DB40" s="22"/>
       <c r="DC40" s="22">
-        <f>-[4]Jan!$M$1+[4]Jan!$AG$1</f>
+        <f>-[4]Apr!$M$1+[4]Apr!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DD40" s="22">
-        <f>-[5]Jan!$M$1+[5]Jan!$AG$1</f>
+        <f>-[5]Apr!$M$1+[5]Apr!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DE40" s="22">
-        <f>-[6]Jan!$M$1+[6]Jan!$AG$1</f>
+        <f>-[6]Apr!$M$1+[6]Apr!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DF40" s="22">
-        <f>-[7]Jan!$M$1+[7]Jan!$AD$1</f>
+        <f>-[7]Apr!$M$1+[7]Apr!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DG40" s="22"/>
@@ -27167,19 +27167,19 @@
       <c r="DL40" s="22"/>
       <c r="DM40" s="22"/>
       <c r="DN40" s="22">
-        <f>-[4]Feb!$M$1+[4]Feb!$AG$1</f>
+        <f>-[4]May!$M$1+[4]May!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DO40" s="22">
-        <f>-[5]Feb!$M$1+[5]Feb!$AG$1</f>
+        <f>-[5]May!$M$1+[5]May!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DP40" s="22">
-        <f>-[6]Feb!$M$1+[6]Feb!$AG$1</f>
+        <f>-[6]May!$M$1+[6]May!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DQ40" s="22">
-        <f>-[7]Feb!$M$1+[7]Feb!$AD$1</f>
+        <f>-[7]May!$M$1+[7]May!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DR40" s="22"/>
@@ -27193,19 +27193,19 @@
       <c r="DW40" s="22"/>
       <c r="DX40" s="22"/>
       <c r="DY40" s="22">
-        <f>-[4]Mar!$M$1+[4]Mar!$AG$1</f>
+        <f>-[4]Jun!$M$1+[4]Jun!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DZ40" s="22">
-        <f>-[5]Mar!$M$1+[5]Mar!$AG$1</f>
+        <f>-[5]Jun!$M$1+[5]Jun!$AG$1</f>
         <v>0</v>
       </c>
       <c r="EA40" s="22">
-        <f>-[6]Mar!$M$1+[6]Mar!$AG$1</f>
+        <f>-[6]Jun!$M$1+[6]Jun!$AG$1</f>
         <v>0</v>
       </c>
       <c r="EB40" s="22">
-        <f>-[7]Mar!$M$1+[7]Mar!$AD$1</f>
+        <f>-[7]Jun!$M$1+[7]Jun!$AD$1</f>
         <v>0</v>
       </c>
       <c r="EC40" s="22"/>
@@ -29226,7 +29226,7 @@
       <c r="D53" s="21"/>
       <c r="E53" s="21"/>
       <c r="F53" s="22">
-        <f>-[3]Apr!$O$1</f>
+        <f>-[3]Jul!$O$1</f>
         <v>0</v>
       </c>
       <c r="G53" s="22"/>
@@ -29242,7 +29242,7 @@
       </c>
       <c r="P53" s="21"/>
       <c r="Q53" s="22">
-        <f>-[3]May!$O$1</f>
+        <f>-[3]Aug!$O$1</f>
         <v>0</v>
       </c>
       <c r="R53" s="22"/>
@@ -29259,7 +29259,7 @@
       </c>
       <c r="AA53" s="21"/>
       <c r="AB53" s="22">
-        <f>-[3]Jun!$O$1</f>
+        <f>-[3]Sep!$O$1</f>
         <v>0</v>
       </c>
       <c r="AC53" s="22"/>
@@ -29276,7 +29276,7 @@
       </c>
       <c r="AL53" s="21"/>
       <c r="AM53" s="22">
-        <f>-[3]Jul!$O$1</f>
+        <f>-[3]Oct!$O$1</f>
         <v>0</v>
       </c>
       <c r="AN53" s="22"/>
@@ -29293,7 +29293,7 @@
       </c>
       <c r="AW53" s="21"/>
       <c r="AX53" s="22">
-        <f>-[3]Aug!$O$1</f>
+        <f>-[3]Nov!$O$1</f>
         <v>0</v>
       </c>
       <c r="AY53" s="22"/>
@@ -29310,7 +29310,7 @@
       </c>
       <c r="BH53" s="21"/>
       <c r="BI53" s="22">
-        <f>-[3]Sep!$O$1</f>
+        <f>-[3]Dec!$O$1</f>
         <v>0</v>
       </c>
       <c r="BJ53" s="22"/>
@@ -29327,7 +29327,7 @@
       </c>
       <c r="BS53" s="21"/>
       <c r="BT53" s="22">
-        <f>-[3]Oct!$O$1</f>
+        <f>-[3]Jan!$O$1</f>
         <v>0</v>
       </c>
       <c r="BU53" s="22"/>
@@ -29344,7 +29344,7 @@
       </c>
       <c r="CD53" s="21"/>
       <c r="CE53" s="22">
-        <f>-[3]Nov!$O$1</f>
+        <f>-[3]Feb!$O$1</f>
         <v>0</v>
       </c>
       <c r="CF53" s="22"/>
@@ -29361,7 +29361,7 @@
       </c>
       <c r="CO53" s="21"/>
       <c r="CP53" s="22">
-        <f>-[3]Dec!$O$1</f>
+        <f>-[3]Mar!$O$1</f>
         <v>0</v>
       </c>
       <c r="CQ53" s="22"/>
@@ -29378,7 +29378,7 @@
       </c>
       <c r="CZ53" s="21"/>
       <c r="DA53" s="22">
-        <f>-[3]Jan!$O$1</f>
+        <f>-[3]Apr!$O$1</f>
         <v>0</v>
       </c>
       <c r="DB53" s="22"/>
@@ -29395,7 +29395,7 @@
       </c>
       <c r="DK53" s="21"/>
       <c r="DL53" s="22">
-        <f>-[3]Feb!$O$1</f>
+        <f>-[3]May!$O$1</f>
         <v>0</v>
       </c>
       <c r="DM53" s="22"/>
@@ -29412,7 +29412,7 @@
       </c>
       <c r="DV53" s="21"/>
       <c r="DW53" s="22">
-        <f>-[3]Mar!$O$1</f>
+        <f>-[3]Jun!$O$1</f>
         <v>0</v>
       </c>
       <c r="DX53" s="22"/>
@@ -29446,7 +29446,7 @@
       <c r="D54" s="21"/>
       <c r="E54" s="21"/>
       <c r="F54" s="22">
-        <f>-[3]Apr!$P$1</f>
+        <f>-[3]Jul!$P$1</f>
         <v>0</v>
       </c>
       <c r="G54" s="22"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="P54" s="21"/>
       <c r="Q54" s="22">
-        <f>-[3]May!$P$1</f>
+        <f>-[3]Aug!$P$1</f>
         <v>0</v>
       </c>
       <c r="R54" s="22"/>
@@ -29479,7 +29479,7 @@
       </c>
       <c r="AA54" s="21"/>
       <c r="AB54" s="22">
-        <f>-[3]Jun!$P$1</f>
+        <f>-[3]Sep!$P$1</f>
         <v>0</v>
       </c>
       <c r="AC54" s="22"/>
@@ -29496,7 +29496,7 @@
       </c>
       <c r="AL54" s="21"/>
       <c r="AM54" s="22">
-        <f>-[3]Jul!$P$1</f>
+        <f>-[3]Oct!$P$1</f>
         <v>0</v>
       </c>
       <c r="AN54" s="22"/>
@@ -29513,7 +29513,7 @@
       </c>
       <c r="AW54" s="21"/>
       <c r="AX54" s="22">
-        <f>-[3]Aug!$P$1</f>
+        <f>-[3]Nov!$P$1</f>
         <v>0</v>
       </c>
       <c r="AY54" s="22"/>
@@ -29530,7 +29530,7 @@
       </c>
       <c r="BH54" s="21"/>
       <c r="BI54" s="22">
-        <f>-[3]Sep!$P$1</f>
+        <f>-[3]Dec!$P$1</f>
         <v>0</v>
       </c>
       <c r="BJ54" s="22"/>
@@ -29547,7 +29547,7 @@
       </c>
       <c r="BS54" s="21"/>
       <c r="BT54" s="22">
-        <f>-[3]Oct!$P$1</f>
+        <f>-[3]Jan!$P$1</f>
         <v>0</v>
       </c>
       <c r="BU54" s="22"/>
@@ -29564,7 +29564,7 @@
       </c>
       <c r="CD54" s="21"/>
       <c r="CE54" s="22">
-        <f>-[3]Nov!$P$1</f>
+        <f>-[3]Feb!$P$1</f>
         <v>0</v>
       </c>
       <c r="CF54" s="22"/>
@@ -29581,7 +29581,7 @@
       </c>
       <c r="CO54" s="21"/>
       <c r="CP54" s="22">
-        <f>-[3]Dec!$P$1</f>
+        <f>-[3]Mar!$P$1</f>
         <v>0</v>
       </c>
       <c r="CQ54" s="22"/>
@@ -29598,7 +29598,7 @@
       </c>
       <c r="CZ54" s="21"/>
       <c r="DA54" s="22">
-        <f>-[3]Jan!$P$1</f>
+        <f>-[3]Apr!$P$1</f>
         <v>0</v>
       </c>
       <c r="DB54" s="22"/>
@@ -29615,7 +29615,7 @@
       </c>
       <c r="DK54" s="21"/>
       <c r="DL54" s="22">
-        <f>-[3]Feb!$P$1</f>
+        <f>-[3]May!$P$1</f>
         <v>0</v>
       </c>
       <c r="DM54" s="22"/>
@@ -29632,7 +29632,7 @@
       </c>
       <c r="DV54" s="21"/>
       <c r="DW54" s="22">
-        <f>-[3]Mar!$P$1</f>
+        <f>-[3]Jun!$P$1</f>
         <v>0</v>
       </c>
       <c r="DX54" s="22"/>
@@ -29666,7 +29666,7 @@
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="22">
-        <f>-[3]Apr!$Q$1</f>
+        <f>-[3]Jul!$Q$1</f>
         <v>0</v>
       </c>
       <c r="G55" s="22"/>
@@ -29682,7 +29682,7 @@
       </c>
       <c r="P55" s="21"/>
       <c r="Q55" s="22">
-        <f>-[3]May!$Q$1</f>
+        <f>-[3]Aug!$Q$1</f>
         <v>0</v>
       </c>
       <c r="R55" s="22"/>
@@ -29699,7 +29699,7 @@
       </c>
       <c r="AA55" s="21"/>
       <c r="AB55" s="22">
-        <f>-[3]Jun!$Q$1</f>
+        <f>-[3]Sep!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AC55" s="22"/>
@@ -29716,7 +29716,7 @@
       </c>
       <c r="AL55" s="21"/>
       <c r="AM55" s="22">
-        <f>-[3]Jul!$Q$1</f>
+        <f>-[3]Oct!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AN55" s="22"/>
@@ -29733,7 +29733,7 @@
       </c>
       <c r="AW55" s="21"/>
       <c r="AX55" s="22">
-        <f>-[3]Aug!$Q$1</f>
+        <f>-[3]Nov!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AY55" s="22"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="BH55" s="21"/>
       <c r="BI55" s="22">
-        <f>-[3]Sep!$Q$1</f>
+        <f>-[3]Dec!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BJ55" s="22"/>
@@ -29767,7 +29767,7 @@
       </c>
       <c r="BS55" s="21"/>
       <c r="BT55" s="22">
-        <f>-[3]Oct!$Q$1</f>
+        <f>-[3]Jan!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BU55" s="22"/>
@@ -29784,7 +29784,7 @@
       </c>
       <c r="CD55" s="21"/>
       <c r="CE55" s="22">
-        <f>-[3]Nov!$Q$1</f>
+        <f>-[3]Feb!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CF55" s="22"/>
@@ -29801,7 +29801,7 @@
       </c>
       <c r="CO55" s="21"/>
       <c r="CP55" s="22">
-        <f>-[3]Dec!$Q$1</f>
+        <f>-[3]Mar!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CQ55" s="22"/>
@@ -29818,7 +29818,7 @@
       </c>
       <c r="CZ55" s="21"/>
       <c r="DA55" s="22">
-        <f>-[3]Jan!$Q$1</f>
+        <f>-[3]Apr!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DB55" s="22"/>
@@ -29835,7 +29835,7 @@
       </c>
       <c r="DK55" s="21"/>
       <c r="DL55" s="22">
-        <f>-[3]Feb!$Q$1</f>
+        <f>-[3]May!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DM55" s="22"/>
@@ -29852,7 +29852,7 @@
       </c>
       <c r="DV55" s="21"/>
       <c r="DW55" s="22">
-        <f>-[3]Mar!$Q$1</f>
+        <f>-[3]Jun!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DX55" s="22"/>
@@ -29886,7 +29886,7 @@
       <c r="D56" s="21"/>
       <c r="E56" s="21"/>
       <c r="F56" s="22">
-        <f>-[3]Apr!$R$1</f>
+        <f>-[3]Jul!$R$1</f>
         <v>0</v>
       </c>
       <c r="G56" s="22"/>
@@ -29902,7 +29902,7 @@
       </c>
       <c r="P56" s="21"/>
       <c r="Q56" s="22">
-        <f>-[3]May!$R$1</f>
+        <f>-[3]Aug!$R$1</f>
         <v>0</v>
       </c>
       <c r="R56" s="22"/>
@@ -29919,7 +29919,7 @@
       </c>
       <c r="AA56" s="21"/>
       <c r="AB56" s="22">
-        <f>-[3]Jun!$R$1</f>
+        <f>-[3]Sep!$R$1</f>
         <v>0</v>
       </c>
       <c r="AC56" s="22"/>
@@ -29936,7 +29936,7 @@
       </c>
       <c r="AL56" s="21"/>
       <c r="AM56" s="22">
-        <f>-[3]Jul!$R$1</f>
+        <f>-[3]Oct!$R$1</f>
         <v>0</v>
       </c>
       <c r="AN56" s="22"/>
@@ -29953,7 +29953,7 @@
       </c>
       <c r="AW56" s="21"/>
       <c r="AX56" s="22">
-        <f>-[3]Aug!$R$1</f>
+        <f>-[3]Nov!$R$1</f>
         <v>0</v>
       </c>
       <c r="AY56" s="22"/>
@@ -29970,7 +29970,7 @@
       </c>
       <c r="BH56" s="21"/>
       <c r="BI56" s="22">
-        <f>-[3]Sep!$R$1</f>
+        <f>-[3]Dec!$R$1</f>
         <v>0</v>
       </c>
       <c r="BJ56" s="22"/>
@@ -29987,7 +29987,7 @@
       </c>
       <c r="BS56" s="21"/>
       <c r="BT56" s="22">
-        <f>-[3]Oct!$R$1</f>
+        <f>-[3]Jan!$R$1</f>
         <v>0</v>
       </c>
       <c r="BU56" s="22"/>
@@ -30004,7 +30004,7 @@
       </c>
       <c r="CD56" s="21"/>
       <c r="CE56" s="22">
-        <f>-[3]Nov!$R$1</f>
+        <f>-[3]Feb!$R$1</f>
         <v>0</v>
       </c>
       <c r="CF56" s="22"/>
@@ -30021,7 +30021,7 @@
       </c>
       <c r="CO56" s="21"/>
       <c r="CP56" s="22">
-        <f>-[3]Dec!$R$1</f>
+        <f>-[3]Mar!$R$1</f>
         <v>0</v>
       </c>
       <c r="CQ56" s="22"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="CZ56" s="21"/>
       <c r="DA56" s="22">
-        <f>-[3]Jan!$R$1</f>
+        <f>-[3]Apr!$R$1</f>
         <v>0</v>
       </c>
       <c r="DB56" s="22"/>
@@ -30055,7 +30055,7 @@
       </c>
       <c r="DK56" s="21"/>
       <c r="DL56" s="22">
-        <f>-[3]Feb!$R$1</f>
+        <f>-[3]May!$R$1</f>
         <v>0</v>
       </c>
       <c r="DM56" s="22"/>
@@ -30072,7 +30072,7 @@
       </c>
       <c r="DV56" s="21"/>
       <c r="DW56" s="22">
-        <f>-[3]Mar!$R$1</f>
+        <f>-[3]Jun!$R$1</f>
         <v>0</v>
       </c>
       <c r="DX56" s="22"/>
@@ -30106,7 +30106,7 @@
       <c r="D57" s="21"/>
       <c r="E57" s="21"/>
       <c r="F57" s="22">
-        <f>-[3]Apr!$S$1</f>
+        <f>-[3]Jul!$S$1</f>
         <v>0</v>
       </c>
       <c r="G57" s="22"/>
@@ -30122,7 +30122,7 @@
       </c>
       <c r="P57" s="21"/>
       <c r="Q57" s="22">
-        <f>-[3]May!$S$1</f>
+        <f>-[3]Aug!$S$1</f>
         <v>0</v>
       </c>
       <c r="R57" s="22"/>
@@ -30139,7 +30139,7 @@
       </c>
       <c r="AA57" s="21"/>
       <c r="AB57" s="22">
-        <f>-[3]Jun!$S$1</f>
+        <f>-[3]Sep!$S$1</f>
         <v>0</v>
       </c>
       <c r="AC57" s="22"/>
@@ -30156,7 +30156,7 @@
       </c>
       <c r="AL57" s="21"/>
       <c r="AM57" s="22">
-        <f>-[3]Jul!$S$1</f>
+        <f>-[3]Oct!$S$1</f>
         <v>0</v>
       </c>
       <c r="AN57" s="22"/>
@@ -30173,7 +30173,7 @@
       </c>
       <c r="AW57" s="21"/>
       <c r="AX57" s="22">
-        <f>-[3]Aug!$S$1</f>
+        <f>-[3]Nov!$S$1</f>
         <v>0</v>
       </c>
       <c r="AY57" s="22"/>
@@ -30190,7 +30190,7 @@
       </c>
       <c r="BH57" s="21"/>
       <c r="BI57" s="22">
-        <f>-[3]Sep!$S$1</f>
+        <f>-[3]Dec!$S$1</f>
         <v>0</v>
       </c>
       <c r="BJ57" s="22"/>
@@ -30207,7 +30207,7 @@
       </c>
       <c r="BS57" s="21"/>
       <c r="BT57" s="22">
-        <f>-[3]Oct!$S$1</f>
+        <f>-[3]Jan!$S$1</f>
         <v>0</v>
       </c>
       <c r="BU57" s="22"/>
@@ -30224,7 +30224,7 @@
       </c>
       <c r="CD57" s="21"/>
       <c r="CE57" s="22">
-        <f>-[3]Nov!$S$1</f>
+        <f>-[3]Feb!$S$1</f>
         <v>0</v>
       </c>
       <c r="CF57" s="22"/>
@@ -30241,7 +30241,7 @@
       </c>
       <c r="CO57" s="21"/>
       <c r="CP57" s="22">
-        <f>-[3]Dec!$S$1</f>
+        <f>-[3]Mar!$S$1</f>
         <v>0</v>
       </c>
       <c r="CQ57" s="22"/>
@@ -30258,7 +30258,7 @@
       </c>
       <c r="CZ57" s="21"/>
       <c r="DA57" s="22">
-        <f>-[3]Jan!$S$1</f>
+        <f>-[3]Apr!$S$1</f>
         <v>0</v>
       </c>
       <c r="DB57" s="22"/>
@@ -30275,7 +30275,7 @@
       </c>
       <c r="DK57" s="21"/>
       <c r="DL57" s="22">
-        <f>-[3]Feb!$S$1</f>
+        <f>-[3]May!$S$1</f>
         <v>0</v>
       </c>
       <c r="DM57" s="22"/>
@@ -30292,7 +30292,7 @@
       </c>
       <c r="DV57" s="21"/>
       <c r="DW57" s="22">
-        <f>-[3]Mar!$S$1</f>
+        <f>-[3]Jun!$S$1</f>
         <v>0</v>
       </c>
       <c r="DX57" s="22"/>
@@ -30328,19 +30328,19 @@
       <c r="F58" s="22"/>
       <c r="G58" s="22"/>
       <c r="H58" s="22">
-        <f>-[4]Apr!$K$1</f>
+        <f>-[4]Jul!$K$1</f>
         <v>0</v>
       </c>
       <c r="I58" s="22">
-        <f>-[5]Apr!$K$1</f>
+        <f>-[5]Jul!$K$1</f>
         <v>0</v>
       </c>
       <c r="J58" s="22">
-        <f>-[6]Apr!$K$1</f>
+        <f>-[6]Jul!$K$1</f>
         <v>0</v>
       </c>
       <c r="K58" s="22">
-        <f>-[7]Apr!$K$1</f>
+        <f>-[7]Jul!$K$1</f>
         <v>0</v>
       </c>
       <c r="L58" s="22"/>
@@ -30353,19 +30353,19 @@
       <c r="Q58" s="22"/>
       <c r="R58" s="22"/>
       <c r="S58" s="22">
-        <f>-[4]May!$K$1</f>
+        <f>-[4]Aug!$K$1</f>
         <v>0</v>
       </c>
       <c r="T58" s="22">
-        <f>-[5]May!$K$1</f>
+        <f>-[5]Aug!$K$1</f>
         <v>0</v>
       </c>
       <c r="U58" s="22">
-        <f>-[6]May!$K$1</f>
+        <f>-[6]Aug!$K$1</f>
         <v>0</v>
       </c>
       <c r="V58" s="22">
-        <f>-[7]May!$K$1</f>
+        <f>-[7]Aug!$K$1</f>
         <v>0</v>
       </c>
       <c r="W58" s="22"/>
@@ -30379,19 +30379,19 @@
       <c r="AB58" s="22"/>
       <c r="AC58" s="22"/>
       <c r="AD58" s="22">
-        <f>-[4]Jun!$K$1</f>
+        <f>-[4]Sep!$K$1</f>
         <v>0</v>
       </c>
       <c r="AE58" s="22">
-        <f>-[5]Jun!$K$1</f>
+        <f>-[5]Sep!$K$1</f>
         <v>0</v>
       </c>
       <c r="AF58" s="22">
-        <f>-[6]Jun!$K$1</f>
+        <f>-[6]Sep!$K$1</f>
         <v>0</v>
       </c>
       <c r="AG58" s="22">
-        <f>-[7]Jun!$K$1</f>
+        <f>-[7]Sep!$K$1</f>
         <v>0</v>
       </c>
       <c r="AH58" s="22"/>
@@ -30405,19 +30405,19 @@
       <c r="AM58" s="22"/>
       <c r="AN58" s="22"/>
       <c r="AO58" s="22">
-        <f>-[4]Jul!$K$1</f>
+        <f>-[4]Oct!$K$1</f>
         <v>0</v>
       </c>
       <c r="AP58" s="22">
-        <f>-[5]Jul!$K$1</f>
+        <f>-[5]Oct!$K$1</f>
         <v>0</v>
       </c>
       <c r="AQ58" s="22">
-        <f>-[6]Jul!$K$1</f>
+        <f>-[6]Oct!$K$1</f>
         <v>0</v>
       </c>
       <c r="AR58" s="22">
-        <f>-[7]Jul!$K$1</f>
+        <f>-[7]Oct!$K$1</f>
         <v>0</v>
       </c>
       <c r="AS58" s="22"/>
@@ -30431,19 +30431,19 @@
       <c r="AX58" s="22"/>
       <c r="AY58" s="22"/>
       <c r="AZ58" s="22">
-        <f>-[4]Aug!$K$1</f>
+        <f>-[4]Nov!$K$1</f>
         <v>0</v>
       </c>
       <c r="BA58" s="22">
-        <f>-[5]Aug!$K$1</f>
+        <f>-[5]Nov!$K$1</f>
         <v>0</v>
       </c>
       <c r="BB58" s="22">
-        <f>-[6]Aug!$K$1</f>
+        <f>-[6]Nov!$K$1</f>
         <v>0</v>
       </c>
       <c r="BC58" s="22">
-        <f>-[7]Aug!$K$1</f>
+        <f>-[7]Nov!$K$1</f>
         <v>0</v>
       </c>
       <c r="BD58" s="22"/>
@@ -30457,19 +30457,19 @@
       <c r="BI58" s="22"/>
       <c r="BJ58" s="22"/>
       <c r="BK58" s="22">
-        <f>-[4]Sep!$K$1</f>
+        <f>-[4]Dec!$K$1</f>
         <v>0</v>
       </c>
       <c r="BL58" s="22">
-        <f>-[5]Sep!$K$1</f>
+        <f>-[5]Dec!$K$1</f>
         <v>0</v>
       </c>
       <c r="BM58" s="22">
-        <f>-[6]Sep!$K$1</f>
+        <f>-[6]Dec!$K$1</f>
         <v>0</v>
       </c>
       <c r="BN58" s="22">
-        <f>-[7]Sep!$K$1</f>
+        <f>-[7]Dec!$K$1</f>
         <v>0</v>
       </c>
       <c r="BO58" s="22"/>
@@ -30483,19 +30483,19 @@
       <c r="BT58" s="22"/>
       <c r="BU58" s="22"/>
       <c r="BV58" s="22">
-        <f>-[4]Oct!$K$1</f>
+        <f>-[4]Jan!$K$1</f>
         <v>0</v>
       </c>
       <c r="BW58" s="22">
-        <f>-[5]Oct!$K$1</f>
+        <f>-[5]Jan!$K$1</f>
         <v>0</v>
       </c>
       <c r="BX58" s="22">
-        <f>-[6]Oct!$K$1</f>
+        <f>-[6]Jan!$K$1</f>
         <v>0</v>
       </c>
       <c r="BY58" s="22">
-        <f>-[7]Oct!$K$1</f>
+        <f>-[7]Jan!$K$1</f>
         <v>0</v>
       </c>
       <c r="BZ58" s="22"/>
@@ -30509,19 +30509,19 @@
       <c r="CE58" s="22"/>
       <c r="CF58" s="22"/>
       <c r="CG58" s="22">
-        <f>-[4]Nov!$K$1</f>
+        <f>-[4]Feb!$K$1</f>
         <v>0</v>
       </c>
       <c r="CH58" s="22">
-        <f>-[5]Nov!$K$1</f>
+        <f>-[5]Feb!$K$1</f>
         <v>0</v>
       </c>
       <c r="CI58" s="22">
-        <f>-[6]Nov!$K$1</f>
+        <f>-[6]Feb!$K$1</f>
         <v>0</v>
       </c>
       <c r="CJ58" s="22">
-        <f>-[7]Nov!$K$1</f>
+        <f>-[7]Feb!$K$1</f>
         <v>0</v>
       </c>
       <c r="CK58" s="22"/>
@@ -30535,19 +30535,19 @@
       <c r="CP58" s="22"/>
       <c r="CQ58" s="22"/>
       <c r="CR58" s="22">
-        <f>-[4]Dec!$K$1</f>
+        <f>-[4]Mar!$K$1</f>
         <v>0</v>
       </c>
       <c r="CS58" s="22">
-        <f>-[5]Dec!$K$1</f>
+        <f>-[5]Mar!$K$1</f>
         <v>0</v>
       </c>
       <c r="CT58" s="22">
-        <f>-[6]Dec!$K$1</f>
+        <f>-[6]Mar!$K$1</f>
         <v>0</v>
       </c>
       <c r="CU58" s="22">
-        <f>-[7]Dec!$K$1</f>
+        <f>-[7]Mar!$K$1</f>
         <v>0</v>
       </c>
       <c r="CV58" s="22"/>
@@ -30561,19 +30561,19 @@
       <c r="DA58" s="22"/>
       <c r="DB58" s="22"/>
       <c r="DC58" s="22">
-        <f>-[4]Jan!$K$1</f>
+        <f>-[4]Apr!$K$1</f>
         <v>0</v>
       </c>
       <c r="DD58" s="22">
-        <f>-[5]Jan!$K$1</f>
+        <f>-[5]Apr!$K$1</f>
         <v>0</v>
       </c>
       <c r="DE58" s="22">
-        <f>-[6]Jan!$K$1</f>
+        <f>-[6]Apr!$K$1</f>
         <v>0</v>
       </c>
       <c r="DF58" s="22">
-        <f>-[7]Jan!$K$1</f>
+        <f>-[7]Apr!$K$1</f>
         <v>0</v>
       </c>
       <c r="DG58" s="22"/>
@@ -30587,19 +30587,19 @@
       <c r="DL58" s="22"/>
       <c r="DM58" s="22"/>
       <c r="DN58" s="22">
-        <f>-[4]Feb!$K$1</f>
+        <f>-[4]May!$K$1</f>
         <v>0</v>
       </c>
       <c r="DO58" s="22">
-        <f>-[5]Feb!$K$1</f>
+        <f>-[5]May!$K$1</f>
         <v>0</v>
       </c>
       <c r="DP58" s="22">
-        <f>-[6]Feb!$K$1</f>
+        <f>-[6]May!$K$1</f>
         <v>0</v>
       </c>
       <c r="DQ58" s="22">
-        <f>-[7]Feb!$K$1</f>
+        <f>-[7]May!$K$1</f>
         <v>0</v>
       </c>
       <c r="DR58" s="22"/>
@@ -30613,19 +30613,19 @@
       <c r="DW58" s="22"/>
       <c r="DX58" s="22"/>
       <c r="DY58" s="22">
-        <f>-[4]Mar!$K$1</f>
+        <f>-[4]Jun!$K$1</f>
         <v>0</v>
       </c>
       <c r="DZ58" s="22">
-        <f>-[5]Mar!$K$1</f>
+        <f>-[5]Jun!$K$1</f>
         <v>0</v>
       </c>
       <c r="EA58" s="22">
-        <f>-[6]Mar!$K$1</f>
+        <f>-[6]Jun!$K$1</f>
         <v>0</v>
       </c>
       <c r="EB58" s="22">
-        <f>-[7]Mar!$K$1</f>
+        <f>-[7]Jun!$K$1</f>
         <v>0</v>
       </c>
       <c r="EC58" s="22"/>
@@ -30804,7 +30804,7 @@
       <c r="E60" s="21"/>
       <c r="F60" s="22"/>
       <c r="G60" s="22">
-        <f>[2]Apr!$O$1</f>
+        <f>[2]Jul!$O$1</f>
         <v>0</v>
       </c>
       <c r="H60" s="22"/>
@@ -30824,7 +30824,7 @@
       <c r="P60" s="21"/>
       <c r="Q60" s="22"/>
       <c r="R60" s="22">
-        <f>[2]May!$O$1</f>
+        <f>[2]Aug!$O$1</f>
         <v>0</v>
       </c>
       <c r="S60" s="22"/>
@@ -30844,7 +30844,7 @@
       <c r="AA60" s="21"/>
       <c r="AB60" s="22"/>
       <c r="AC60" s="22">
-        <f>[2]Jun!$O$1</f>
+        <f>[2]Sep!$O$1</f>
         <v>0</v>
       </c>
       <c r="AD60" s="22"/>
@@ -30864,7 +30864,7 @@
       <c r="AL60" s="21"/>
       <c r="AM60" s="22"/>
       <c r="AN60" s="22">
-        <f>[2]Jul!$O$1</f>
+        <f>[2]Oct!$O$1</f>
         <v>0</v>
       </c>
       <c r="AO60" s="22"/>
@@ -30884,7 +30884,7 @@
       <c r="AW60" s="21"/>
       <c r="AX60" s="22"/>
       <c r="AY60" s="22">
-        <f>[2]Aug!$O$1</f>
+        <f>[2]Nov!$O$1</f>
         <v>0</v>
       </c>
       <c r="AZ60" s="22"/>
@@ -30904,7 +30904,7 @@
       <c r="BH60" s="21"/>
       <c r="BI60" s="22"/>
       <c r="BJ60" s="22">
-        <f>[2]Sep!$O$1</f>
+        <f>[2]Dec!$O$1</f>
         <v>0</v>
       </c>
       <c r="BK60" s="22"/>
@@ -30924,7 +30924,7 @@
       <c r="BS60" s="21"/>
       <c r="BT60" s="22"/>
       <c r="BU60" s="22">
-        <f>[2]Oct!$O$1</f>
+        <f>[2]Jan!$O$1</f>
         <v>0</v>
       </c>
       <c r="BV60" s="22"/>
@@ -30944,7 +30944,7 @@
       <c r="CD60" s="21"/>
       <c r="CE60" s="22"/>
       <c r="CF60" s="22">
-        <f>[2]Nov!$O$1</f>
+        <f>[2]Feb!$O$1</f>
         <v>0</v>
       </c>
       <c r="CG60" s="22"/>
@@ -30964,7 +30964,7 @@
       <c r="CO60" s="21"/>
       <c r="CP60" s="22"/>
       <c r="CQ60" s="22">
-        <f>[2]Dec!$O$1</f>
+        <f>[2]Mar!$O$1</f>
         <v>0</v>
       </c>
       <c r="CR60" s="22"/>
@@ -30984,7 +30984,7 @@
       <c r="CZ60" s="21"/>
       <c r="DA60" s="22"/>
       <c r="DB60" s="22">
-        <f>[2]Jan!$O$1</f>
+        <f>[2]Apr!$O$1</f>
         <v>0</v>
       </c>
       <c r="DC60" s="22"/>
@@ -31004,7 +31004,7 @@
       <c r="DK60" s="21"/>
       <c r="DL60" s="22"/>
       <c r="DM60" s="22">
-        <f>[2]Feb!$O$1</f>
+        <f>[2]May!$O$1</f>
         <v>0</v>
       </c>
       <c r="DN60" s="22"/>
@@ -31024,7 +31024,7 @@
       <c r="DV60" s="21"/>
       <c r="DW60" s="22"/>
       <c r="DX60" s="22">
-        <f>[2]Mar!$O$1</f>
+        <f>[2]Jun!$O$1</f>
         <v>0</v>
       </c>
       <c r="DY60" s="22"/>
@@ -31061,7 +31061,7 @@
       <c r="E61" s="21"/>
       <c r="F61" s="22"/>
       <c r="G61" s="22">
-        <f>[2]Apr!$P$1</f>
+        <f>[2]Jul!$P$1</f>
         <v>0</v>
       </c>
       <c r="H61" s="22"/>
@@ -31077,7 +31077,7 @@
       <c r="P61" s="21"/>
       <c r="Q61" s="22"/>
       <c r="R61" s="22">
-        <f>[2]May!$P$1</f>
+        <f>[2]Aug!$P$1</f>
         <v>0</v>
       </c>
       <c r="S61" s="22"/>
@@ -31094,7 +31094,7 @@
       <c r="AA61" s="21"/>
       <c r="AB61" s="22"/>
       <c r="AC61" s="22">
-        <f>[2]Jun!$P$1</f>
+        <f>[2]Sep!$P$1</f>
         <v>0</v>
       </c>
       <c r="AD61" s="22"/>
@@ -31111,7 +31111,7 @@
       <c r="AL61" s="21"/>
       <c r="AM61" s="22"/>
       <c r="AN61" s="22">
-        <f>[2]Jul!$P$1</f>
+        <f>[2]Oct!$P$1</f>
         <v>0</v>
       </c>
       <c r="AO61" s="22"/>
@@ -31128,7 +31128,7 @@
       <c r="AW61" s="21"/>
       <c r="AX61" s="22"/>
       <c r="AY61" s="22">
-        <f>[2]Aug!$P$1</f>
+        <f>[2]Nov!$P$1</f>
         <v>0</v>
       </c>
       <c r="AZ61" s="22"/>
@@ -31145,7 +31145,7 @@
       <c r="BH61" s="21"/>
       <c r="BI61" s="22"/>
       <c r="BJ61" s="22">
-        <f>[2]Sep!$P$1</f>
+        <f>[2]Dec!$P$1</f>
         <v>0</v>
       </c>
       <c r="BK61" s="22"/>
@@ -31162,7 +31162,7 @@
       <c r="BS61" s="21"/>
       <c r="BT61" s="22"/>
       <c r="BU61" s="22">
-        <f>[2]Oct!$P$1</f>
+        <f>[2]Jan!$P$1</f>
         <v>0</v>
       </c>
       <c r="BV61" s="22"/>
@@ -31179,7 +31179,7 @@
       <c r="CD61" s="21"/>
       <c r="CE61" s="22"/>
       <c r="CF61" s="22">
-        <f>[2]Nov!$P$1</f>
+        <f>[2]Feb!$P$1</f>
         <v>0</v>
       </c>
       <c r="CG61" s="22"/>
@@ -31196,7 +31196,7 @@
       <c r="CO61" s="21"/>
       <c r="CP61" s="22"/>
       <c r="CQ61" s="22">
-        <f>[2]Dec!$P$1</f>
+        <f>[2]Mar!$P$1</f>
         <v>0</v>
       </c>
       <c r="CR61" s="22"/>
@@ -31213,7 +31213,7 @@
       <c r="CZ61" s="21"/>
       <c r="DA61" s="22"/>
       <c r="DB61" s="22">
-        <f>[2]Jan!$P$1</f>
+        <f>[2]Apr!$P$1</f>
         <v>0</v>
       </c>
       <c r="DC61" s="22"/>
@@ -31230,7 +31230,7 @@
       <c r="DK61" s="21"/>
       <c r="DL61" s="22"/>
       <c r="DM61" s="22">
-        <f>[2]Feb!$P$1</f>
+        <f>[2]May!$P$1</f>
         <v>0</v>
       </c>
       <c r="DN61" s="22"/>
@@ -31247,7 +31247,7 @@
       <c r="DV61" s="21"/>
       <c r="DW61" s="22"/>
       <c r="DX61" s="22">
-        <f>[2]Mar!$P$1</f>
+        <f>[2]Jun!$P$1</f>
         <v>0</v>
       </c>
       <c r="DY61" s="22"/>
@@ -31281,7 +31281,7 @@
       <c r="E62" s="21"/>
       <c r="F62" s="22"/>
       <c r="G62" s="22">
-        <f>[2]Apr!$Q$1</f>
+        <f>[2]Jul!$Q$1</f>
         <v>0</v>
       </c>
       <c r="H62" s="22"/>
@@ -31297,7 +31297,7 @@
       <c r="P62" s="21"/>
       <c r="Q62" s="22"/>
       <c r="R62" s="22">
-        <f>[2]May!$Q$1</f>
+        <f>[2]Aug!$Q$1</f>
         <v>0</v>
       </c>
       <c r="S62" s="22"/>
@@ -31314,7 +31314,7 @@
       <c r="AA62" s="21"/>
       <c r="AB62" s="22"/>
       <c r="AC62" s="22">
-        <f>[2]Jun!$Q$1</f>
+        <f>[2]Sep!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AD62" s="22"/>
@@ -31331,7 +31331,7 @@
       <c r="AL62" s="21"/>
       <c r="AM62" s="22"/>
       <c r="AN62" s="22">
-        <f>[2]Jul!$Q$1</f>
+        <f>[2]Oct!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AO62" s="22"/>
@@ -31348,7 +31348,7 @@
       <c r="AW62" s="21"/>
       <c r="AX62" s="22"/>
       <c r="AY62" s="22">
-        <f>[2]Aug!$Q$1</f>
+        <f>[2]Nov!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AZ62" s="22"/>
@@ -31365,7 +31365,7 @@
       <c r="BH62" s="21"/>
       <c r="BI62" s="22"/>
       <c r="BJ62" s="22">
-        <f>[2]Sep!$Q$1</f>
+        <f>[2]Dec!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BK62" s="22"/>
@@ -31382,7 +31382,7 @@
       <c r="BS62" s="21"/>
       <c r="BT62" s="22"/>
       <c r="BU62" s="22">
-        <f>[2]Oct!$Q$1</f>
+        <f>[2]Jan!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BV62" s="22"/>
@@ -31399,7 +31399,7 @@
       <c r="CD62" s="21"/>
       <c r="CE62" s="22"/>
       <c r="CF62" s="22">
-        <f>[2]Nov!$Q$1</f>
+        <f>[2]Feb!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CG62" s="22"/>
@@ -31416,7 +31416,7 @@
       <c r="CO62" s="21"/>
       <c r="CP62" s="22"/>
       <c r="CQ62" s="22">
-        <f>[2]Dec!$Q$1</f>
+        <f>[2]Mar!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CR62" s="22"/>
@@ -31433,7 +31433,7 @@
       <c r="CZ62" s="21"/>
       <c r="DA62" s="22"/>
       <c r="DB62" s="22">
-        <f>[2]Jan!$Q$1</f>
+        <f>[2]Apr!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DC62" s="22"/>
@@ -31450,7 +31450,7 @@
       <c r="DK62" s="21"/>
       <c r="DL62" s="22"/>
       <c r="DM62" s="22">
-        <f>[2]Feb!$Q$1</f>
+        <f>[2]May!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DN62" s="22"/>
@@ -31467,7 +31467,7 @@
       <c r="DV62" s="21"/>
       <c r="DW62" s="22"/>
       <c r="DX62" s="22">
-        <f>[2]Mar!$Q$1</f>
+        <f>[2]Jun!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DY62" s="22"/>
@@ -31866,7 +31866,7 @@
       <c r="E65" s="21"/>
       <c r="F65" s="22"/>
       <c r="G65" s="22">
-        <f>[2]Apr!$S$1</f>
+        <f>[2]Jul!$S$1</f>
         <v>0</v>
       </c>
       <c r="H65" s="22"/>
@@ -31882,7 +31882,7 @@
       <c r="P65" s="21"/>
       <c r="Q65" s="22"/>
       <c r="R65" s="22">
-        <f>[2]May!$S$1</f>
+        <f>[2]Aug!$S$1</f>
         <v>0</v>
       </c>
       <c r="S65" s="22"/>
@@ -31899,7 +31899,7 @@
       <c r="AA65" s="21"/>
       <c r="AB65" s="22"/>
       <c r="AC65" s="22">
-        <f>[2]Jun!$S$1</f>
+        <f>[2]Sep!$S$1</f>
         <v>0</v>
       </c>
       <c r="AD65" s="22"/>
@@ -31916,7 +31916,7 @@
       <c r="AL65" s="21"/>
       <c r="AM65" s="22"/>
       <c r="AN65" s="22">
-        <f>[2]Jul!$S$1</f>
+        <f>[2]Oct!$S$1</f>
         <v>0</v>
       </c>
       <c r="AO65" s="22"/>
@@ -31933,7 +31933,7 @@
       <c r="AW65" s="21"/>
       <c r="AX65" s="22"/>
       <c r="AY65" s="22">
-        <f>[2]Aug!$S$1</f>
+        <f>[2]Nov!$S$1</f>
         <v>0</v>
       </c>
       <c r="AZ65" s="22"/>
@@ -31950,7 +31950,7 @@
       <c r="BH65" s="21"/>
       <c r="BI65" s="22"/>
       <c r="BJ65" s="22">
-        <f>[2]Sep!$S$1</f>
+        <f>[2]Dec!$S$1</f>
         <v>0</v>
       </c>
       <c r="BK65" s="22"/>
@@ -31967,7 +31967,7 @@
       <c r="BS65" s="21"/>
       <c r="BT65" s="22"/>
       <c r="BU65" s="22">
-        <f>[2]Oct!$S$1</f>
+        <f>[2]Jan!$S$1</f>
         <v>0</v>
       </c>
       <c r="BV65" s="22"/>
@@ -31984,7 +31984,7 @@
       <c r="CD65" s="21"/>
       <c r="CE65" s="22"/>
       <c r="CF65" s="22">
-        <f>[2]Nov!$S$1</f>
+        <f>[2]Feb!$S$1</f>
         <v>0</v>
       </c>
       <c r="CG65" s="22"/>
@@ -32001,7 +32001,7 @@
       <c r="CO65" s="21"/>
       <c r="CP65" s="22"/>
       <c r="CQ65" s="22">
-        <f>[2]Dec!$S$1</f>
+        <f>[2]Mar!$S$1</f>
         <v>0</v>
       </c>
       <c r="CR65" s="22"/>
@@ -32018,7 +32018,7 @@
       <c r="CZ65" s="21"/>
       <c r="DA65" s="22"/>
       <c r="DB65" s="22">
-        <f>[2]Jan!$S$1</f>
+        <f>[2]Apr!$S$1</f>
         <v>0</v>
       </c>
       <c r="DC65" s="22"/>
@@ -32035,7 +32035,7 @@
       <c r="DK65" s="21"/>
       <c r="DL65" s="22"/>
       <c r="DM65" s="22">
-        <f>[2]Feb!$S$1</f>
+        <f>[2]May!$S$1</f>
         <v>0</v>
       </c>
       <c r="DN65" s="22"/>
@@ -32052,7 +32052,7 @@
       <c r="DV65" s="21"/>
       <c r="DW65" s="22"/>
       <c r="DX65" s="22">
-        <f>[2]Mar!$S$1</f>
+        <f>[2]Jun!$S$1</f>
         <v>0</v>
       </c>
       <c r="DY65" s="22"/>
@@ -32086,7 +32086,7 @@
       <c r="E66" s="21"/>
       <c r="F66" s="22"/>
       <c r="G66" s="22">
-        <f>[2]Apr!$R$1</f>
+        <f>[2]Jul!$R$1</f>
         <v>0</v>
       </c>
       <c r="H66" s="22"/>
@@ -32105,7 +32105,7 @@
       <c r="P66" s="21"/>
       <c r="Q66" s="22"/>
       <c r="R66" s="22">
-        <f>[2]May!$R$1</f>
+        <f>[2]Aug!$R$1</f>
         <v>0</v>
       </c>
       <c r="S66" s="22"/>
@@ -32125,7 +32125,7 @@
       <c r="AA66" s="21"/>
       <c r="AB66" s="22"/>
       <c r="AC66" s="22">
-        <f>[2]Jun!$R$1</f>
+        <f>[2]Sep!$R$1</f>
         <v>0</v>
       </c>
       <c r="AD66" s="22"/>
@@ -32145,7 +32145,7 @@
       <c r="AL66" s="21"/>
       <c r="AM66" s="22"/>
       <c r="AN66" s="22">
-        <f>[2]Jul!$R$1</f>
+        <f>[2]Oct!$R$1</f>
         <v>0</v>
       </c>
       <c r="AO66" s="22"/>
@@ -32165,7 +32165,7 @@
       <c r="AW66" s="21"/>
       <c r="AX66" s="22"/>
       <c r="AY66" s="22">
-        <f>[2]Aug!$R$1</f>
+        <f>[2]Nov!$R$1</f>
         <v>0</v>
       </c>
       <c r="AZ66" s="22"/>
@@ -32185,7 +32185,7 @@
       <c r="BH66" s="21"/>
       <c r="BI66" s="22"/>
       <c r="BJ66" s="22">
-        <f>[2]Sep!$R$1</f>
+        <f>[2]Dec!$R$1</f>
         <v>0</v>
       </c>
       <c r="BK66" s="22"/>
@@ -32205,7 +32205,7 @@
       <c r="BS66" s="21"/>
       <c r="BT66" s="22"/>
       <c r="BU66" s="22">
-        <f>[2]Oct!$R$1</f>
+        <f>[2]Jan!$R$1</f>
         <v>0</v>
       </c>
       <c r="BV66" s="22"/>
@@ -32225,7 +32225,7 @@
       <c r="CD66" s="21"/>
       <c r="CE66" s="22"/>
       <c r="CF66" s="22">
-        <f>[2]Nov!$R$1</f>
+        <f>[2]Feb!$R$1</f>
         <v>0</v>
       </c>
       <c r="CG66" s="22"/>
@@ -32245,7 +32245,7 @@
       <c r="CO66" s="21"/>
       <c r="CP66" s="22"/>
       <c r="CQ66" s="22">
-        <f>[2]Dec!$R$1</f>
+        <f>[2]Mar!$R$1</f>
         <v>0</v>
       </c>
       <c r="CR66" s="22"/>
@@ -32265,7 +32265,7 @@
       <c r="CZ66" s="21"/>
       <c r="DA66" s="22"/>
       <c r="DB66" s="22">
-        <f>[2]Jan!$R$1</f>
+        <f>[2]Apr!$R$1</f>
         <v>0</v>
       </c>
       <c r="DC66" s="22"/>
@@ -32285,7 +32285,7 @@
       <c r="DK66" s="21"/>
       <c r="DL66" s="22"/>
       <c r="DM66" s="22">
-        <f>[2]Feb!$R$1</f>
+        <f>[2]May!$R$1</f>
         <v>0</v>
       </c>
       <c r="DN66" s="22"/>
@@ -32305,7 +32305,7 @@
       <c r="DV66" s="21"/>
       <c r="DW66" s="22"/>
       <c r="DX66" s="22">
-        <f>[2]Mar!$R$1</f>
+        <f>[2]Jun!$R$1</f>
         <v>0</v>
       </c>
       <c r="DY66" s="22"/>
@@ -32560,7 +32560,7 @@
       <c r="E68" s="21"/>
       <c r="F68" s="22"/>
       <c r="G68" s="22">
-        <f>[2]Apr!$T$1</f>
+        <f>[2]Jul!$T$1</f>
         <v>0</v>
       </c>
       <c r="H68" s="22"/>
@@ -32576,7 +32576,7 @@
       <c r="P68" s="21"/>
       <c r="Q68" s="22"/>
       <c r="R68" s="22">
-        <f>[2]May!$T$1</f>
+        <f>[2]Aug!$T$1</f>
         <v>0</v>
       </c>
       <c r="S68" s="22"/>
@@ -32593,7 +32593,7 @@
       <c r="AA68" s="21"/>
       <c r="AB68" s="22"/>
       <c r="AC68" s="22">
-        <f>[2]Jun!$T$1</f>
+        <f>[2]Sep!$T$1</f>
         <v>0</v>
       </c>
       <c r="AD68" s="22"/>
@@ -32610,7 +32610,7 @@
       <c r="AL68" s="21"/>
       <c r="AM68" s="22"/>
       <c r="AN68" s="22">
-        <f>[2]Jul!$T$1</f>
+        <f>[2]Oct!$T$1</f>
         <v>0</v>
       </c>
       <c r="AO68" s="22"/>
@@ -32627,7 +32627,7 @@
       <c r="AW68" s="21"/>
       <c r="AX68" s="22"/>
       <c r="AY68" s="22">
-        <f>[2]Aug!$T$1</f>
+        <f>[2]Nov!$T$1</f>
         <v>0</v>
       </c>
       <c r="AZ68" s="22"/>
@@ -32644,7 +32644,7 @@
       <c r="BH68" s="21"/>
       <c r="BI68" s="22"/>
       <c r="BJ68" s="22">
-        <f>[2]Sep!$T$1</f>
+        <f>[2]Dec!$T$1</f>
         <v>0</v>
       </c>
       <c r="BK68" s="22"/>
@@ -32661,7 +32661,7 @@
       <c r="BS68" s="21"/>
       <c r="BT68" s="22"/>
       <c r="BU68" s="22">
-        <f>[2]Oct!$T$1</f>
+        <f>[2]Jan!$T$1</f>
         <v>0</v>
       </c>
       <c r="BV68" s="22"/>
@@ -32678,7 +32678,7 @@
       <c r="CD68" s="21"/>
       <c r="CE68" s="22"/>
       <c r="CF68" s="22">
-        <f>[2]Nov!$T$1</f>
+        <f>[2]Feb!$T$1</f>
         <v>0</v>
       </c>
       <c r="CG68" s="22"/>
@@ -32695,7 +32695,7 @@
       <c r="CO68" s="21"/>
       <c r="CP68" s="22"/>
       <c r="CQ68" s="22">
-        <f>[2]Dec!$T$1</f>
+        <f>[2]Mar!$T$1</f>
         <v>0</v>
       </c>
       <c r="CR68" s="22"/>
@@ -32712,7 +32712,7 @@
       <c r="CZ68" s="21"/>
       <c r="DA68" s="22"/>
       <c r="DB68" s="22">
-        <f>[2]Jan!$T$1</f>
+        <f>[2]Apr!$T$1</f>
         <v>0</v>
       </c>
       <c r="DC68" s="22"/>
@@ -32729,7 +32729,7 @@
       <c r="DK68" s="21"/>
       <c r="DL68" s="22"/>
       <c r="DM68" s="22">
-        <f>[2]Feb!$T$1</f>
+        <f>[2]May!$T$1</f>
         <v>0</v>
       </c>
       <c r="DN68" s="22"/>
@@ -32746,7 +32746,7 @@
       <c r="DV68" s="21"/>
       <c r="DW68" s="22"/>
       <c r="DX68" s="22">
-        <f>[2]Mar!$T$1</f>
+        <f>[2]Jun!$T$1</f>
         <v>0</v>
       </c>
       <c r="DY68" s="22"/>
@@ -32780,7 +32780,7 @@
       <c r="E69" s="21"/>
       <c r="F69" s="22"/>
       <c r="G69" s="22">
-        <f>[2]Apr!$U$1</f>
+        <f>[2]Jul!$U$1</f>
         <v>0</v>
       </c>
       <c r="H69" s="22"/>
@@ -32796,7 +32796,7 @@
       <c r="P69" s="21"/>
       <c r="Q69" s="22"/>
       <c r="R69" s="22">
-        <f>[2]May!$U$1</f>
+        <f>[2]Aug!$U$1</f>
         <v>0</v>
       </c>
       <c r="S69" s="22"/>
@@ -32813,7 +32813,7 @@
       <c r="AA69" s="21"/>
       <c r="AB69" s="22"/>
       <c r="AC69" s="22">
-        <f>[2]Jun!$U$1</f>
+        <f>[2]Sep!$U$1</f>
         <v>0</v>
       </c>
       <c r="AD69" s="22"/>
@@ -32830,7 +32830,7 @@
       <c r="AL69" s="21"/>
       <c r="AM69" s="22"/>
       <c r="AN69" s="22">
-        <f>[2]Jul!$U$1</f>
+        <f>[2]Oct!$U$1</f>
         <v>0</v>
       </c>
       <c r="AO69" s="22"/>
@@ -32847,7 +32847,7 @@
       <c r="AW69" s="21"/>
       <c r="AX69" s="22"/>
       <c r="AY69" s="22">
-        <f>[2]Aug!$U$1</f>
+        <f>[2]Nov!$U$1</f>
         <v>0</v>
       </c>
       <c r="AZ69" s="22"/>
@@ -32864,7 +32864,7 @@
       <c r="BH69" s="21"/>
       <c r="BI69" s="22"/>
       <c r="BJ69" s="22">
-        <f>[2]Sep!$U$1</f>
+        <f>[2]Dec!$U$1</f>
         <v>0</v>
       </c>
       <c r="BK69" s="22"/>
@@ -32881,7 +32881,7 @@
       <c r="BS69" s="21"/>
       <c r="BT69" s="22"/>
       <c r="BU69" s="22">
-        <f>[2]Oct!$U$1</f>
+        <f>[2]Jan!$U$1</f>
         <v>0</v>
       </c>
       <c r="BV69" s="22"/>
@@ -32898,7 +32898,7 @@
       <c r="CD69" s="21"/>
       <c r="CE69" s="22"/>
       <c r="CF69" s="22">
-        <f>[2]Nov!$U$1</f>
+        <f>[2]Feb!$U$1</f>
         <v>0</v>
       </c>
       <c r="CG69" s="22"/>
@@ -32915,7 +32915,7 @@
       <c r="CO69" s="21"/>
       <c r="CP69" s="22"/>
       <c r="CQ69" s="22">
-        <f>[2]Dec!$U$1</f>
+        <f>[2]Mar!$U$1</f>
         <v>0</v>
       </c>
       <c r="CR69" s="22"/>
@@ -32932,7 +32932,7 @@
       <c r="CZ69" s="21"/>
       <c r="DA69" s="22"/>
       <c r="DB69" s="22">
-        <f>[2]Jan!$U$1</f>
+        <f>[2]Apr!$U$1</f>
         <v>0</v>
       </c>
       <c r="DC69" s="22"/>
@@ -32949,7 +32949,7 @@
       <c r="DK69" s="21"/>
       <c r="DL69" s="22"/>
       <c r="DM69" s="22">
-        <f>[2]Feb!$U$1</f>
+        <f>[2]May!$U$1</f>
         <v>0</v>
       </c>
       <c r="DN69" s="22"/>
@@ -32966,7 +32966,7 @@
       <c r="DV69" s="21"/>
       <c r="DW69" s="22"/>
       <c r="DX69" s="22">
-        <f>[2]Mar!$U$1</f>
+        <f>[2]Jun!$U$1</f>
         <v>0</v>
       </c>
       <c r="DY69" s="22"/>
@@ -33000,7 +33000,7 @@
       <c r="E70" s="21"/>
       <c r="F70" s="22"/>
       <c r="G70" s="22">
-        <f>[2]Apr!$V$1</f>
+        <f>[2]Jul!$V$1</f>
         <v>0</v>
       </c>
       <c r="H70" s="22"/>
@@ -33016,7 +33016,7 @@
       <c r="P70" s="21"/>
       <c r="Q70" s="22"/>
       <c r="R70" s="22">
-        <f>[2]May!$V$1</f>
+        <f>[2]Aug!$V$1</f>
         <v>0</v>
       </c>
       <c r="S70" s="22"/>
@@ -33033,7 +33033,7 @@
       <c r="AA70" s="21"/>
       <c r="AB70" s="22"/>
       <c r="AC70" s="22">
-        <f>[2]Jun!$V$1</f>
+        <f>[2]Sep!$V$1</f>
         <v>0</v>
       </c>
       <c r="AD70" s="22"/>
@@ -33050,7 +33050,7 @@
       <c r="AL70" s="21"/>
       <c r="AM70" s="22"/>
       <c r="AN70" s="22">
-        <f>[2]Jul!$V$1</f>
+        <f>[2]Oct!$V$1</f>
         <v>0</v>
       </c>
       <c r="AO70" s="22"/>
@@ -33067,7 +33067,7 @@
       <c r="AW70" s="21"/>
       <c r="AX70" s="22"/>
       <c r="AY70" s="22">
-        <f>[2]Aug!$V$1</f>
+        <f>[2]Nov!$V$1</f>
         <v>0</v>
       </c>
       <c r="AZ70" s="22"/>
@@ -33084,7 +33084,7 @@
       <c r="BH70" s="21"/>
       <c r="BI70" s="22"/>
       <c r="BJ70" s="22">
-        <f>[2]Sep!$V$1</f>
+        <f>[2]Dec!$V$1</f>
         <v>0</v>
       </c>
       <c r="BK70" s="22"/>
@@ -33101,7 +33101,7 @@
       <c r="BS70" s="21"/>
       <c r="BT70" s="22"/>
       <c r="BU70" s="22">
-        <f>[2]Oct!$V$1</f>
+        <f>[2]Jan!$V$1</f>
         <v>0</v>
       </c>
       <c r="BV70" s="22"/>
@@ -33118,7 +33118,7 @@
       <c r="CD70" s="21"/>
       <c r="CE70" s="22"/>
       <c r="CF70" s="22">
-        <f>[2]Nov!$V$1</f>
+        <f>[2]Feb!$V$1</f>
         <v>0</v>
       </c>
       <c r="CG70" s="22"/>
@@ -33135,7 +33135,7 @@
       <c r="CO70" s="21"/>
       <c r="CP70" s="22"/>
       <c r="CQ70" s="22">
-        <f>[2]Dec!$V$1</f>
+        <f>[2]Mar!$V$1</f>
         <v>0</v>
       </c>
       <c r="CR70" s="22"/>
@@ -33152,7 +33152,7 @@
       <c r="CZ70" s="21"/>
       <c r="DA70" s="22"/>
       <c r="DB70" s="22">
-        <f>[2]Jan!$V$1</f>
+        <f>[2]Apr!$V$1</f>
         <v>0</v>
       </c>
       <c r="DC70" s="22"/>
@@ -33169,7 +33169,7 @@
       <c r="DK70" s="21"/>
       <c r="DL70" s="22"/>
       <c r="DM70" s="22">
-        <f>[2]Feb!$V$1</f>
+        <f>[2]May!$V$1</f>
         <v>0</v>
       </c>
       <c r="DN70" s="22"/>
@@ -33186,7 +33186,7 @@
       <c r="DV70" s="21"/>
       <c r="DW70" s="22"/>
       <c r="DX70" s="22">
-        <f>[2]Mar!$V$1</f>
+        <f>[2]Jun!$V$1</f>
         <v>0</v>
       </c>
       <c r="DY70" s="22"/>
@@ -33220,7 +33220,7 @@
       <c r="E71" s="21"/>
       <c r="F71" s="22"/>
       <c r="G71" s="22">
-        <f>[2]Apr!$W$1</f>
+        <f>[2]Jul!$W$1</f>
         <v>0</v>
       </c>
       <c r="H71" s="22"/>
@@ -33236,7 +33236,7 @@
       <c r="P71" s="21"/>
       <c r="Q71" s="22"/>
       <c r="R71" s="22">
-        <f>[2]May!$W$1</f>
+        <f>[2]Aug!$W$1</f>
         <v>0</v>
       </c>
       <c r="S71" s="22"/>
@@ -33253,7 +33253,7 @@
       <c r="AA71" s="21"/>
       <c r="AB71" s="22"/>
       <c r="AC71" s="22">
-        <f>[2]Jun!$W$1</f>
+        <f>[2]Sep!$W$1</f>
         <v>0</v>
       </c>
       <c r="AD71" s="22"/>
@@ -33270,7 +33270,7 @@
       <c r="AL71" s="21"/>
       <c r="AM71" s="22"/>
       <c r="AN71" s="22">
-        <f>[2]Jul!$W$1</f>
+        <f>[2]Oct!$W$1</f>
         <v>0</v>
       </c>
       <c r="AO71" s="22"/>
@@ -33287,7 +33287,7 @@
       <c r="AW71" s="21"/>
       <c r="AX71" s="22"/>
       <c r="AY71" s="22">
-        <f>[2]Aug!$W$1</f>
+        <f>[2]Nov!$W$1</f>
         <v>0</v>
       </c>
       <c r="AZ71" s="22"/>
@@ -33304,7 +33304,7 @@
       <c r="BH71" s="21"/>
       <c r="BI71" s="22"/>
       <c r="BJ71" s="22">
-        <f>[2]Sep!$W$1</f>
+        <f>[2]Dec!$W$1</f>
         <v>0</v>
       </c>
       <c r="BK71" s="22"/>
@@ -33321,7 +33321,7 @@
       <c r="BS71" s="21"/>
       <c r="BT71" s="22"/>
       <c r="BU71" s="22">
-        <f>[2]Oct!$W$1</f>
+        <f>[2]Jan!$W$1</f>
         <v>0</v>
       </c>
       <c r="BV71" s="22"/>
@@ -33338,7 +33338,7 @@
       <c r="CD71" s="21"/>
       <c r="CE71" s="22"/>
       <c r="CF71" s="22">
-        <f>[2]Nov!$W$1</f>
+        <f>[2]Feb!$W$1</f>
         <v>0</v>
       </c>
       <c r="CG71" s="22"/>
@@ -33355,7 +33355,7 @@
       <c r="CO71" s="21"/>
       <c r="CP71" s="22"/>
       <c r="CQ71" s="22">
-        <f>[2]Dec!$W$1</f>
+        <f>[2]Mar!$W$1</f>
         <v>0</v>
       </c>
       <c r="CR71" s="22"/>
@@ -33372,7 +33372,7 @@
       <c r="CZ71" s="21"/>
       <c r="DA71" s="22"/>
       <c r="DB71" s="22">
-        <f>[2]Jan!$W$1</f>
+        <f>[2]Apr!$W$1</f>
         <v>0</v>
       </c>
       <c r="DC71" s="22"/>
@@ -33389,7 +33389,7 @@
       <c r="DK71" s="21"/>
       <c r="DL71" s="22"/>
       <c r="DM71" s="22">
-        <f>[2]Feb!$W$1</f>
+        <f>[2]May!$W$1</f>
         <v>0</v>
       </c>
       <c r="DN71" s="22"/>
@@ -33406,7 +33406,7 @@
       <c r="DV71" s="21"/>
       <c r="DW71" s="22"/>
       <c r="DX71" s="22">
-        <f>[2]Mar!$W$1</f>
+        <f>[2]Jun!$W$1</f>
         <v>0</v>
       </c>
       <c r="DY71" s="22"/>
@@ -33440,7 +33440,7 @@
       <c r="E72" s="21"/>
       <c r="F72" s="22"/>
       <c r="G72" s="22">
-        <f>[2]Apr!$X$1</f>
+        <f>[2]Jul!$X$1</f>
         <v>0</v>
       </c>
       <c r="H72" s="22"/>
@@ -33456,7 +33456,7 @@
       <c r="P72" s="21"/>
       <c r="Q72" s="22"/>
       <c r="R72" s="22">
-        <f>[2]May!$X$1</f>
+        <f>[2]Aug!$X$1</f>
         <v>0</v>
       </c>
       <c r="S72" s="22"/>
@@ -33473,7 +33473,7 @@
       <c r="AA72" s="21"/>
       <c r="AB72" s="22"/>
       <c r="AC72" s="22">
-        <f>[2]Jun!$X$1</f>
+        <f>[2]Sep!$X$1</f>
         <v>0</v>
       </c>
       <c r="AD72" s="22"/>
@@ -33490,7 +33490,7 @@
       <c r="AL72" s="21"/>
       <c r="AM72" s="22"/>
       <c r="AN72" s="22">
-        <f>[2]Jul!$X$1</f>
+        <f>[2]Oct!$X$1</f>
         <v>0</v>
       </c>
       <c r="AO72" s="22"/>
@@ -33507,7 +33507,7 @@
       <c r="AW72" s="21"/>
       <c r="AX72" s="22"/>
       <c r="AY72" s="22">
-        <f>[2]Aug!$X$1</f>
+        <f>[2]Nov!$X$1</f>
         <v>0</v>
       </c>
       <c r="AZ72" s="22"/>
@@ -33524,7 +33524,7 @@
       <c r="BH72" s="21"/>
       <c r="BI72" s="22"/>
       <c r="BJ72" s="22">
-        <f>[2]Sep!$X$1</f>
+        <f>[2]Dec!$X$1</f>
         <v>0</v>
       </c>
       <c r="BK72" s="22"/>
@@ -33541,7 +33541,7 @@
       <c r="BS72" s="21"/>
       <c r="BT72" s="22"/>
       <c r="BU72" s="22">
-        <f>[2]Oct!$X$1</f>
+        <f>[2]Jan!$X$1</f>
         <v>0</v>
       </c>
       <c r="BV72" s="22"/>
@@ -33558,7 +33558,7 @@
       <c r="CD72" s="21"/>
       <c r="CE72" s="22"/>
       <c r="CF72" s="22">
-        <f>[2]Nov!$X$1</f>
+        <f>[2]Feb!$X$1</f>
         <v>0</v>
       </c>
       <c r="CG72" s="22"/>
@@ -33575,7 +33575,7 @@
       <c r="CO72" s="21"/>
       <c r="CP72" s="22"/>
       <c r="CQ72" s="22">
-        <f>[2]Dec!$X$1</f>
+        <f>[2]Mar!$X$1</f>
         <v>0</v>
       </c>
       <c r="CR72" s="22"/>
@@ -33592,7 +33592,7 @@
       <c r="CZ72" s="21"/>
       <c r="DA72" s="22"/>
       <c r="DB72" s="22">
-        <f>[2]Jan!$X$1</f>
+        <f>[2]Apr!$X$1</f>
         <v>0</v>
       </c>
       <c r="DC72" s="22"/>
@@ -33609,7 +33609,7 @@
       <c r="DK72" s="21"/>
       <c r="DL72" s="22"/>
       <c r="DM72" s="22">
-        <f>[2]Feb!$X$1</f>
+        <f>[2]May!$X$1</f>
         <v>0</v>
       </c>
       <c r="DN72" s="22"/>
@@ -33626,7 +33626,7 @@
       <c r="DV72" s="21"/>
       <c r="DW72" s="22"/>
       <c r="DX72" s="22">
-        <f>[2]Mar!$X$1</f>
+        <f>[2]Jun!$X$1</f>
         <v>0</v>
       </c>
       <c r="DY72" s="22"/>
@@ -33660,7 +33660,7 @@
       <c r="E73" s="21"/>
       <c r="F73" s="22"/>
       <c r="G73" s="22">
-        <f>[2]Apr!$Y$1</f>
+        <f>[2]Jul!$Y$1</f>
         <v>0</v>
       </c>
       <c r="H73" s="22"/>
@@ -33676,7 +33676,7 @@
       <c r="P73" s="21"/>
       <c r="Q73" s="22"/>
       <c r="R73" s="22">
-        <f>[2]May!$Y$1</f>
+        <f>[2]Aug!$Y$1</f>
         <v>0</v>
       </c>
       <c r="S73" s="22"/>
@@ -33693,7 +33693,7 @@
       <c r="AA73" s="21"/>
       <c r="AB73" s="22"/>
       <c r="AC73" s="22">
-        <f>[2]Jun!$Y$1</f>
+        <f>[2]Sep!$Y$1</f>
         <v>0</v>
       </c>
       <c r="AD73" s="22"/>
@@ -33710,7 +33710,7 @@
       <c r="AL73" s="21"/>
       <c r="AM73" s="22"/>
       <c r="AN73" s="22">
-        <f>[2]Jul!$Y$1</f>
+        <f>[2]Oct!$Y$1</f>
         <v>0</v>
       </c>
       <c r="AO73" s="22"/>
@@ -33727,7 +33727,7 @@
       <c r="AW73" s="21"/>
       <c r="AX73" s="22"/>
       <c r="AY73" s="22">
-        <f>[2]Aug!$Y$1</f>
+        <f>[2]Nov!$Y$1</f>
         <v>0</v>
       </c>
       <c r="AZ73" s="22"/>
@@ -33744,7 +33744,7 @@
       <c r="BH73" s="21"/>
       <c r="BI73" s="22"/>
       <c r="BJ73" s="22">
-        <f>[2]Sep!$Y$1</f>
+        <f>[2]Dec!$Y$1</f>
         <v>0</v>
       </c>
       <c r="BK73" s="22"/>
@@ -33761,7 +33761,7 @@
       <c r="BS73" s="21"/>
       <c r="BT73" s="22"/>
       <c r="BU73" s="22">
-        <f>[2]Oct!$Y$1</f>
+        <f>[2]Jan!$Y$1</f>
         <v>0</v>
       </c>
       <c r="BV73" s="22"/>
@@ -33778,7 +33778,7 @@
       <c r="CD73" s="21"/>
       <c r="CE73" s="22"/>
       <c r="CF73" s="22">
-        <f>[2]Nov!$Y$1</f>
+        <f>[2]Feb!$Y$1</f>
         <v>0</v>
       </c>
       <c r="CG73" s="22"/>
@@ -33795,7 +33795,7 @@
       <c r="CO73" s="21"/>
       <c r="CP73" s="22"/>
       <c r="CQ73" s="22">
-        <f>[2]Dec!$Y$1</f>
+        <f>[2]Mar!$Y$1</f>
         <v>0</v>
       </c>
       <c r="CR73" s="22"/>
@@ -33812,7 +33812,7 @@
       <c r="CZ73" s="21"/>
       <c r="DA73" s="22"/>
       <c r="DB73" s="22">
-        <f>[2]Jan!$Y$1</f>
+        <f>[2]Apr!$Y$1</f>
         <v>0</v>
       </c>
       <c r="DC73" s="22"/>
@@ -33829,7 +33829,7 @@
       <c r="DK73" s="21"/>
       <c r="DL73" s="22"/>
       <c r="DM73" s="22">
-        <f>[2]Feb!$Y$1</f>
+        <f>[2]May!$Y$1</f>
         <v>0</v>
       </c>
       <c r="DN73" s="22"/>
@@ -33846,7 +33846,7 @@
       <c r="DV73" s="21"/>
       <c r="DW73" s="22"/>
       <c r="DX73" s="22">
-        <f>[2]Mar!$Y$1</f>
+        <f>[2]Jun!$Y$1</f>
         <v>0</v>
       </c>
       <c r="DY73" s="22"/>
@@ -33880,7 +33880,7 @@
       <c r="E74" s="21"/>
       <c r="F74" s="22"/>
       <c r="G74" s="22">
-        <f>[2]Apr!$Z$1</f>
+        <f>[2]Jul!$Z$1</f>
         <v>0</v>
       </c>
       <c r="H74" s="22"/>
@@ -33896,7 +33896,7 @@
       <c r="P74" s="21"/>
       <c r="Q74" s="22"/>
       <c r="R74" s="22">
-        <f>[2]May!$Z$1</f>
+        <f>[2]Aug!$Z$1</f>
         <v>0</v>
       </c>
       <c r="S74" s="22"/>
@@ -33913,7 +33913,7 @@
       <c r="AA74" s="21"/>
       <c r="AB74" s="22"/>
       <c r="AC74" s="22">
-        <f>[2]Jun!$Z$1</f>
+        <f>[2]Sep!$Z$1</f>
         <v>0</v>
       </c>
       <c r="AD74" s="22"/>
@@ -33930,7 +33930,7 @@
       <c r="AL74" s="21"/>
       <c r="AM74" s="22"/>
       <c r="AN74" s="22">
-        <f>[2]Jul!$Z$1</f>
+        <f>[2]Oct!$Z$1</f>
         <v>0</v>
       </c>
       <c r="AO74" s="22"/>
@@ -33947,7 +33947,7 @@
       <c r="AW74" s="21"/>
       <c r="AX74" s="22"/>
       <c r="AY74" s="22">
-        <f>[2]Aug!$Z$1</f>
+        <f>[2]Nov!$Z$1</f>
         <v>0</v>
       </c>
       <c r="AZ74" s="22"/>
@@ -33964,7 +33964,7 @@
       <c r="BH74" s="21"/>
       <c r="BI74" s="22"/>
       <c r="BJ74" s="22">
-        <f>[2]Sep!$Z$1</f>
+        <f>[2]Dec!$Z$1</f>
         <v>0</v>
       </c>
       <c r="BK74" s="22"/>
@@ -33981,7 +33981,7 @@
       <c r="BS74" s="21"/>
       <c r="BT74" s="22"/>
       <c r="BU74" s="22">
-        <f>[2]Oct!$Z$1</f>
+        <f>[2]Jan!$Z$1</f>
         <v>0</v>
       </c>
       <c r="BV74" s="22"/>
@@ -33998,7 +33998,7 @@
       <c r="CD74" s="21"/>
       <c r="CE74" s="22"/>
       <c r="CF74" s="22">
-        <f>[2]Nov!$Z$1</f>
+        <f>[2]Feb!$Z$1</f>
         <v>0</v>
       </c>
       <c r="CG74" s="22"/>
@@ -34015,7 +34015,7 @@
       <c r="CO74" s="21"/>
       <c r="CP74" s="22"/>
       <c r="CQ74" s="22">
-        <f>[2]Dec!$Z$1</f>
+        <f>[2]Mar!$Z$1</f>
         <v>0</v>
       </c>
       <c r="CR74" s="22"/>
@@ -34032,7 +34032,7 @@
       <c r="CZ74" s="21"/>
       <c r="DA74" s="22"/>
       <c r="DB74" s="22">
-        <f>[2]Jan!$Z$1</f>
+        <f>[2]Apr!$Z$1</f>
         <v>0</v>
       </c>
       <c r="DC74" s="22"/>
@@ -34049,7 +34049,7 @@
       <c r="DK74" s="21"/>
       <c r="DL74" s="22"/>
       <c r="DM74" s="22">
-        <f>[2]Feb!$Z$1</f>
+        <f>[2]May!$Z$1</f>
         <v>0</v>
       </c>
       <c r="DN74" s="22"/>
@@ -34066,7 +34066,7 @@
       <c r="DV74" s="21"/>
       <c r="DW74" s="22"/>
       <c r="DX74" s="22">
-        <f>[2]Mar!$Z$1</f>
+        <f>[2]Jun!$Z$1</f>
         <v>0</v>
       </c>
       <c r="DY74" s="22"/>
@@ -34100,7 +34100,7 @@
       <c r="E75" s="21"/>
       <c r="F75" s="22"/>
       <c r="G75" s="22">
-        <f>[2]Apr!$AA$1</f>
+        <f>[2]Jul!$AA$1</f>
         <v>0</v>
       </c>
       <c r="H75" s="22"/>
@@ -34116,7 +34116,7 @@
       <c r="P75" s="21"/>
       <c r="Q75" s="22"/>
       <c r="R75" s="22">
-        <f>[2]May!$AA$1</f>
+        <f>[2]Aug!$AA$1</f>
         <v>0</v>
       </c>
       <c r="S75" s="22"/>
@@ -34133,7 +34133,7 @@
       <c r="AA75" s="21"/>
       <c r="AB75" s="22"/>
       <c r="AC75" s="22">
-        <f>[2]Jun!$AA$1</f>
+        <f>[2]Sep!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AD75" s="22"/>
@@ -34150,7 +34150,7 @@
       <c r="AL75" s="21"/>
       <c r="AM75" s="22"/>
       <c r="AN75" s="22">
-        <f>[2]Jul!$AA$1</f>
+        <f>[2]Oct!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AO75" s="22"/>
@@ -34167,7 +34167,7 @@
       <c r="AW75" s="21"/>
       <c r="AX75" s="22"/>
       <c r="AY75" s="22">
-        <f>[2]Aug!$AA$1</f>
+        <f>[2]Nov!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AZ75" s="22"/>
@@ -34184,7 +34184,7 @@
       <c r="BH75" s="21"/>
       <c r="BI75" s="22"/>
       <c r="BJ75" s="22">
-        <f>[2]Sep!$AA$1</f>
+        <f>[2]Dec!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BK75" s="22"/>
@@ -34201,7 +34201,7 @@
       <c r="BS75" s="21"/>
       <c r="BT75" s="22"/>
       <c r="BU75" s="22">
-        <f>[2]Oct!$AA$1</f>
+        <f>[2]Jan!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BV75" s="22"/>
@@ -34218,7 +34218,7 @@
       <c r="CD75" s="21"/>
       <c r="CE75" s="22"/>
       <c r="CF75" s="22">
-        <f>[2]Nov!$AA$1</f>
+        <f>[2]Feb!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CG75" s="22"/>
@@ -34235,7 +34235,7 @@
       <c r="CO75" s="21"/>
       <c r="CP75" s="22"/>
       <c r="CQ75" s="22">
-        <f>[2]Dec!$AA$1</f>
+        <f>[2]Mar!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CR75" s="22"/>
@@ -34252,7 +34252,7 @@
       <c r="CZ75" s="21"/>
       <c r="DA75" s="22"/>
       <c r="DB75" s="22">
-        <f>[2]Jan!$AA$1</f>
+        <f>[2]Apr!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DC75" s="22"/>
@@ -34269,7 +34269,7 @@
       <c r="DK75" s="21"/>
       <c r="DL75" s="22"/>
       <c r="DM75" s="22">
-        <f>[2]Feb!$AA$1</f>
+        <f>[2]May!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DN75" s="22"/>
@@ -34286,7 +34286,7 @@
       <c r="DV75" s="21"/>
       <c r="DW75" s="22"/>
       <c r="DX75" s="22">
-        <f>[2]Mar!$AA$1</f>
+        <f>[2]Jun!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DY75" s="22"/>
@@ -34320,7 +34320,7 @@
       <c r="E76" s="21"/>
       <c r="F76" s="22"/>
       <c r="G76" s="22">
-        <f>[2]Apr!$AB$1</f>
+        <f>[2]Jul!$AB$1</f>
         <v>0</v>
       </c>
       <c r="H76" s="22"/>
@@ -34336,7 +34336,7 @@
       <c r="P76" s="21"/>
       <c r="Q76" s="22"/>
       <c r="R76" s="22">
-        <f>[2]May!$AB$1</f>
+        <f>[2]Aug!$AB$1</f>
         <v>0</v>
       </c>
       <c r="S76" s="22"/>
@@ -34353,7 +34353,7 @@
       <c r="AA76" s="21"/>
       <c r="AB76" s="22"/>
       <c r="AC76" s="22">
-        <f>[2]Jun!$AB$1</f>
+        <f>[2]Sep!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AD76" s="22"/>
@@ -34370,7 +34370,7 @@
       <c r="AL76" s="21"/>
       <c r="AM76" s="22"/>
       <c r="AN76" s="22">
-        <f>[2]Jul!$AB$1</f>
+        <f>[2]Oct!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AO76" s="22"/>
@@ -34387,7 +34387,7 @@
       <c r="AW76" s="21"/>
       <c r="AX76" s="22"/>
       <c r="AY76" s="22">
-        <f>[2]Aug!$AB$1</f>
+        <f>[2]Nov!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AZ76" s="22"/>
@@ -34404,7 +34404,7 @@
       <c r="BH76" s="21"/>
       <c r="BI76" s="22"/>
       <c r="BJ76" s="22">
-        <f>[2]Sep!$AB$1</f>
+        <f>[2]Dec!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BK76" s="22"/>
@@ -34421,7 +34421,7 @@
       <c r="BS76" s="21"/>
       <c r="BT76" s="22"/>
       <c r="BU76" s="22">
-        <f>[2]Oct!$AB$1</f>
+        <f>[2]Jan!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BV76" s="22"/>
@@ -34438,7 +34438,7 @@
       <c r="CD76" s="21"/>
       <c r="CE76" s="22"/>
       <c r="CF76" s="22">
-        <f>[2]Nov!$AB$1</f>
+        <f>[2]Feb!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CG76" s="22"/>
@@ -34455,7 +34455,7 @@
       <c r="CO76" s="21"/>
       <c r="CP76" s="22"/>
       <c r="CQ76" s="22">
-        <f>[2]Dec!$AB$1</f>
+        <f>[2]Mar!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CR76" s="22"/>
@@ -34472,7 +34472,7 @@
       <c r="CZ76" s="21"/>
       <c r="DA76" s="22"/>
       <c r="DB76" s="22">
-        <f>[2]Jan!$AB$1</f>
+        <f>[2]Apr!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DC76" s="22"/>
@@ -34489,7 +34489,7 @@
       <c r="DK76" s="21"/>
       <c r="DL76" s="22"/>
       <c r="DM76" s="22">
-        <f>[2]Feb!$AB$1</f>
+        <f>[2]May!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DN76" s="22"/>
@@ -34506,7 +34506,7 @@
       <c r="DV76" s="21"/>
       <c r="DW76" s="22"/>
       <c r="DX76" s="22">
-        <f>[2]Mar!$AB$1</f>
+        <f>[2]Jun!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DY76" s="22"/>
@@ -34540,7 +34540,7 @@
       <c r="E77" s="21"/>
       <c r="F77" s="22"/>
       <c r="G77" s="22">
-        <f>[2]Apr!$AC$1</f>
+        <f>[2]Jul!$AC$1</f>
         <v>0</v>
       </c>
       <c r="H77" s="22"/>
@@ -34556,7 +34556,7 @@
       <c r="P77" s="21"/>
       <c r="Q77" s="22"/>
       <c r="R77" s="22">
-        <f>[2]May!$AC$1</f>
+        <f>[2]Aug!$AC$1</f>
         <v>0</v>
       </c>
       <c r="S77" s="22"/>
@@ -34573,7 +34573,7 @@
       <c r="AA77" s="21"/>
       <c r="AB77" s="22"/>
       <c r="AC77" s="22">
-        <f>[2]Jun!$AC$1</f>
+        <f>[2]Sep!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AD77" s="22"/>
@@ -34590,7 +34590,7 @@
       <c r="AL77" s="21"/>
       <c r="AM77" s="22"/>
       <c r="AN77" s="22">
-        <f>[2]Jul!$AC$1</f>
+        <f>[2]Oct!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AO77" s="22"/>
@@ -34607,7 +34607,7 @@
       <c r="AW77" s="21"/>
       <c r="AX77" s="22"/>
       <c r="AY77" s="22">
-        <f>[2]Aug!$AC$1</f>
+        <f>[2]Nov!$AC$1</f>
         <v>0</v>
       </c>
       <c r="AZ77" s="22"/>
@@ -34624,7 +34624,7 @@
       <c r="BH77" s="21"/>
       <c r="BI77" s="22"/>
       <c r="BJ77" s="22">
-        <f>[2]Sep!$AC$1</f>
+        <f>[2]Dec!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BK77" s="22"/>
@@ -34641,7 +34641,7 @@
       <c r="BS77" s="21"/>
       <c r="BT77" s="22"/>
       <c r="BU77" s="22">
-        <f>[2]Oct!$AC$1</f>
+        <f>[2]Jan!$AC$1</f>
         <v>0</v>
       </c>
       <c r="BV77" s="22"/>
@@ -34658,7 +34658,7 @@
       <c r="CD77" s="21"/>
       <c r="CE77" s="22"/>
       <c r="CF77" s="22">
-        <f>[2]Nov!$AC$1</f>
+        <f>[2]Feb!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CG77" s="22"/>
@@ -34675,7 +34675,7 @@
       <c r="CO77" s="21"/>
       <c r="CP77" s="22"/>
       <c r="CQ77" s="22">
-        <f>[2]Dec!$AC$1</f>
+        <f>[2]Mar!$AC$1</f>
         <v>0</v>
       </c>
       <c r="CR77" s="22"/>
@@ -34692,7 +34692,7 @@
       <c r="CZ77" s="21"/>
       <c r="DA77" s="22"/>
       <c r="DB77" s="22">
-        <f>[2]Jan!$AC$1</f>
+        <f>[2]Apr!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DC77" s="22"/>
@@ -34709,7 +34709,7 @@
       <c r="DK77" s="21"/>
       <c r="DL77" s="22"/>
       <c r="DM77" s="22">
-        <f>[2]Feb!$AC$1</f>
+        <f>[2]May!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DN77" s="22"/>
@@ -34726,7 +34726,7 @@
       <c r="DV77" s="21"/>
       <c r="DW77" s="22"/>
       <c r="DX77" s="22">
-        <f>[2]Mar!$AC$1</f>
+        <f>[2]Jun!$AC$1</f>
         <v>0</v>
       </c>
       <c r="DY77" s="22"/>
@@ -34760,7 +34760,7 @@
       <c r="E78" s="21"/>
       <c r="F78" s="22"/>
       <c r="G78" s="22">
-        <f>[2]Apr!$AD$1</f>
+        <f>[2]Jul!$AD$1</f>
         <v>0</v>
       </c>
       <c r="H78" s="22"/>
@@ -34776,7 +34776,7 @@
       <c r="P78" s="21"/>
       <c r="Q78" s="22"/>
       <c r="R78" s="22">
-        <f>[2]May!$AD$1</f>
+        <f>[2]Aug!$AD$1</f>
         <v>0</v>
       </c>
       <c r="S78" s="22"/>
@@ -34793,7 +34793,7 @@
       <c r="AA78" s="21"/>
       <c r="AB78" s="22"/>
       <c r="AC78" s="22">
-        <f>[2]Jun!$AD$1</f>
+        <f>[2]Sep!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AD78" s="22"/>
@@ -34810,7 +34810,7 @@
       <c r="AL78" s="21"/>
       <c r="AM78" s="22"/>
       <c r="AN78" s="22">
-        <f>[2]Jul!$AD$1</f>
+        <f>[2]Oct!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AO78" s="22"/>
@@ -34827,7 +34827,7 @@
       <c r="AW78" s="21"/>
       <c r="AX78" s="22"/>
       <c r="AY78" s="22">
-        <f>[2]Aug!$AD$1</f>
+        <f>[2]Nov!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AZ78" s="22"/>
@@ -34844,7 +34844,7 @@
       <c r="BH78" s="21"/>
       <c r="BI78" s="22"/>
       <c r="BJ78" s="22">
-        <f>[2]Sep!$AD$1</f>
+        <f>[2]Dec!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BK78" s="22"/>
@@ -34861,7 +34861,7 @@
       <c r="BS78" s="21"/>
       <c r="BT78" s="22"/>
       <c r="BU78" s="22">
-        <f>[2]Oct!$AD$1</f>
+        <f>[2]Jan!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BV78" s="22"/>
@@ -34878,7 +34878,7 @@
       <c r="CD78" s="21"/>
       <c r="CE78" s="22"/>
       <c r="CF78" s="22">
-        <f>[2]Nov!$AD$1</f>
+        <f>[2]Feb!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CG78" s="22"/>
@@ -34895,7 +34895,7 @@
       <c r="CO78" s="21"/>
       <c r="CP78" s="22"/>
       <c r="CQ78" s="22">
-        <f>[2]Dec!$AD$1</f>
+        <f>[2]Mar!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CR78" s="22"/>
@@ -34912,7 +34912,7 @@
       <c r="CZ78" s="21"/>
       <c r="DA78" s="22"/>
       <c r="DB78" s="22">
-        <f>[2]Jan!$AD$1</f>
+        <f>[2]Apr!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DC78" s="22"/>
@@ -34929,7 +34929,7 @@
       <c r="DK78" s="21"/>
       <c r="DL78" s="22"/>
       <c r="DM78" s="22">
-        <f>[2]Feb!$AD$1</f>
+        <f>[2]May!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DN78" s="22"/>
@@ -34946,7 +34946,7 @@
       <c r="DV78" s="21"/>
       <c r="DW78" s="22"/>
       <c r="DX78" s="22">
-        <f>[2]Mar!$AD$1</f>
+        <f>[2]Jun!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DY78" s="22"/>
@@ -34980,7 +34980,7 @@
       <c r="E79" s="21"/>
       <c r="F79" s="22"/>
       <c r="G79" s="22">
-        <f>[2]Apr!$AE$1</f>
+        <f>[2]Jul!$AE$1</f>
         <v>0</v>
       </c>
       <c r="H79" s="22"/>
@@ -34996,7 +34996,7 @@
       <c r="P79" s="21"/>
       <c r="Q79" s="22"/>
       <c r="R79" s="22">
-        <f>[2]May!$AE$1</f>
+        <f>[2]Aug!$AE$1</f>
         <v>0</v>
       </c>
       <c r="S79" s="22"/>
@@ -35013,7 +35013,7 @@
       <c r="AA79" s="21"/>
       <c r="AB79" s="22"/>
       <c r="AC79" s="22">
-        <f>[2]Jun!$AE$1</f>
+        <f>[2]Sep!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AD79" s="22"/>
@@ -35030,7 +35030,7 @@
       <c r="AL79" s="21"/>
       <c r="AM79" s="22"/>
       <c r="AN79" s="22">
-        <f>[2]Jul!$AE$1</f>
+        <f>[2]Oct!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AO79" s="22"/>
@@ -35047,7 +35047,7 @@
       <c r="AW79" s="21"/>
       <c r="AX79" s="22"/>
       <c r="AY79" s="22">
-        <f>[2]Aug!$AE$1</f>
+        <f>[2]Nov!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AZ79" s="22"/>
@@ -35064,7 +35064,7 @@
       <c r="BH79" s="21"/>
       <c r="BI79" s="22"/>
       <c r="BJ79" s="22">
-        <f>[2]Sep!$AE$1</f>
+        <f>[2]Dec!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BK79" s="22"/>
@@ -35081,7 +35081,7 @@
       <c r="BS79" s="21"/>
       <c r="BT79" s="22"/>
       <c r="BU79" s="22">
-        <f>[2]Oct!$AE$1</f>
+        <f>[2]Jan!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BV79" s="22"/>
@@ -35098,7 +35098,7 @@
       <c r="CD79" s="21"/>
       <c r="CE79" s="22"/>
       <c r="CF79" s="22">
-        <f>[2]Nov!$AE$1</f>
+        <f>[2]Feb!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CG79" s="22"/>
@@ -35115,7 +35115,7 @@
       <c r="CO79" s="21"/>
       <c r="CP79" s="22"/>
       <c r="CQ79" s="22">
-        <f>[2]Dec!$AE$1</f>
+        <f>[2]Mar!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CR79" s="22"/>
@@ -35132,7 +35132,7 @@
       <c r="CZ79" s="21"/>
       <c r="DA79" s="22"/>
       <c r="DB79" s="22">
-        <f>[2]Jan!$AE$1</f>
+        <f>[2]Apr!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DC79" s="22"/>
@@ -35149,7 +35149,7 @@
       <c r="DK79" s="21"/>
       <c r="DL79" s="22"/>
       <c r="DM79" s="22">
-        <f>[2]Feb!$AE$1</f>
+        <f>[2]May!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DN79" s="22"/>
@@ -35166,7 +35166,7 @@
       <c r="DV79" s="21"/>
       <c r="DW79" s="22"/>
       <c r="DX79" s="22">
-        <f>[2]Mar!$AE$1</f>
+        <f>[2]Jun!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DY79" s="22"/>
@@ -35200,7 +35200,7 @@
       <c r="E80" s="21"/>
       <c r="F80" s="22"/>
       <c r="G80" s="22">
-        <f>[2]Apr!$AF$1</f>
+        <f>[2]Jul!$AF$1</f>
         <v>0</v>
       </c>
       <c r="H80" s="22"/>
@@ -35216,7 +35216,7 @@
       <c r="P80" s="21"/>
       <c r="Q80" s="22"/>
       <c r="R80" s="22">
-        <f>[2]May!$AF$1</f>
+        <f>[2]Aug!$AF$1</f>
         <v>0</v>
       </c>
       <c r="S80" s="22"/>
@@ -35233,7 +35233,7 @@
       <c r="AA80" s="21"/>
       <c r="AB80" s="22"/>
       <c r="AC80" s="22">
-        <f>[2]Jun!$AF$1</f>
+        <f>[2]Sep!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AD80" s="22"/>
@@ -35250,7 +35250,7 @@
       <c r="AL80" s="21"/>
       <c r="AM80" s="22"/>
       <c r="AN80" s="22">
-        <f>[2]Jul!$AF$1</f>
+        <f>[2]Oct!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AO80" s="22"/>
@@ -35267,7 +35267,7 @@
       <c r="AW80" s="21"/>
       <c r="AX80" s="22"/>
       <c r="AY80" s="22">
-        <f>[2]Aug!$AF$1</f>
+        <f>[2]Nov!$AF$1</f>
         <v>0</v>
       </c>
       <c r="AZ80" s="22"/>
@@ -35284,7 +35284,7 @@
       <c r="BH80" s="21"/>
       <c r="BI80" s="22"/>
       <c r="BJ80" s="22">
-        <f>[2]Sep!$AF$1</f>
+        <f>[2]Dec!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BK80" s="22"/>
@@ -35301,7 +35301,7 @@
       <c r="BS80" s="21"/>
       <c r="BT80" s="22"/>
       <c r="BU80" s="22">
-        <f>[2]Oct!$AF$1</f>
+        <f>[2]Jan!$AF$1</f>
         <v>0</v>
       </c>
       <c r="BV80" s="22"/>
@@ -35318,7 +35318,7 @@
       <c r="CD80" s="21"/>
       <c r="CE80" s="22"/>
       <c r="CF80" s="22">
-        <f>[2]Nov!$AF$1</f>
+        <f>[2]Feb!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CG80" s="22"/>
@@ -35335,7 +35335,7 @@
       <c r="CO80" s="21"/>
       <c r="CP80" s="22"/>
       <c r="CQ80" s="22">
-        <f>[2]Dec!$AF$1</f>
+        <f>[2]Mar!$AF$1</f>
         <v>0</v>
       </c>
       <c r="CR80" s="22"/>
@@ -35352,7 +35352,7 @@
       <c r="CZ80" s="21"/>
       <c r="DA80" s="22"/>
       <c r="DB80" s="22">
-        <f>[2]Jan!$AF$1</f>
+        <f>[2]Apr!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DC80" s="22"/>
@@ -35369,7 +35369,7 @@
       <c r="DK80" s="21"/>
       <c r="DL80" s="22"/>
       <c r="DM80" s="22">
-        <f>[2]Feb!$AF$1</f>
+        <f>[2]May!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DN80" s="22"/>
@@ -35386,7 +35386,7 @@
       <c r="DV80" s="21"/>
       <c r="DW80" s="22"/>
       <c r="DX80" s="22">
-        <f>[2]Mar!$AF$1</f>
+        <f>[2]Jun!$AF$1</f>
         <v>0</v>
       </c>
       <c r="DY80" s="22"/>
@@ -35419,7 +35419,7 @@
       <c r="D81" s="21"/>
       <c r="E81" s="21"/>
       <c r="F81" s="22">
-        <f>-[3]Apr!$T$1</f>
+        <f>-[3]Jul!$T$1</f>
         <v>0</v>
       </c>
       <c r="G81" s="22"/>
@@ -35435,7 +35435,7 @@
       </c>
       <c r="P81" s="21"/>
       <c r="Q81" s="22">
-        <f>-[3]May!$T$1</f>
+        <f>-[3]Aug!$T$1</f>
         <v>0</v>
       </c>
       <c r="R81" s="22"/>
@@ -35452,7 +35452,7 @@
       </c>
       <c r="AA81" s="21"/>
       <c r="AB81" s="22">
-        <f>-[3]Jun!$T$1</f>
+        <f>-[3]Sep!$T$1</f>
         <v>0</v>
       </c>
       <c r="AC81" s="22"/>
@@ -35469,7 +35469,7 @@
       </c>
       <c r="AL81" s="21"/>
       <c r="AM81" s="22">
-        <f>-[3]Jul!$T$1</f>
+        <f>-[3]Oct!$T$1</f>
         <v>0</v>
       </c>
       <c r="AN81" s="22"/>
@@ -35486,7 +35486,7 @@
       </c>
       <c r="AW81" s="21"/>
       <c r="AX81" s="22">
-        <f>-[3]Aug!$T$1</f>
+        <f>-[3]Nov!$T$1</f>
         <v>0</v>
       </c>
       <c r="AY81" s="22"/>
@@ -35503,7 +35503,7 @@
       </c>
       <c r="BH81" s="21"/>
       <c r="BI81" s="22">
-        <f>-[3]Sep!$T$1</f>
+        <f>-[3]Dec!$T$1</f>
         <v>0</v>
       </c>
       <c r="BJ81" s="22"/>
@@ -35520,7 +35520,7 @@
       </c>
       <c r="BS81" s="21"/>
       <c r="BT81" s="22">
-        <f>-[3]Oct!$T$1</f>
+        <f>-[3]Jan!$T$1</f>
         <v>0</v>
       </c>
       <c r="BU81" s="22"/>
@@ -35537,7 +35537,7 @@
       </c>
       <c r="CD81" s="21"/>
       <c r="CE81" s="22">
-        <f>-[3]Nov!$T$1</f>
+        <f>-[3]Feb!$T$1</f>
         <v>0</v>
       </c>
       <c r="CF81" s="22"/>
@@ -35554,7 +35554,7 @@
       </c>
       <c r="CO81" s="21"/>
       <c r="CP81" s="22">
-        <f>-[3]Dec!$T$1</f>
+        <f>-[3]Mar!$T$1</f>
         <v>0</v>
       </c>
       <c r="CQ81" s="22"/>
@@ -35571,7 +35571,7 @@
       </c>
       <c r="CZ81" s="21"/>
       <c r="DA81" s="22">
-        <f>-[3]Jan!$T$1</f>
+        <f>-[3]Apr!$T$1</f>
         <v>0</v>
       </c>
       <c r="DB81" s="22"/>
@@ -35588,7 +35588,7 @@
       </c>
       <c r="DK81" s="21"/>
       <c r="DL81" s="22">
-        <f>-[3]Feb!$T$1</f>
+        <f>-[3]May!$T$1</f>
         <v>0</v>
       </c>
       <c r="DM81" s="22"/>
@@ -35605,7 +35605,7 @@
       </c>
       <c r="DV81" s="21"/>
       <c r="DW81" s="22">
-        <f>-[3]Mar!$T$1</f>
+        <f>-[3]Jun!$T$1</f>
         <v>0</v>
       </c>
       <c r="DX81" s="22"/>
@@ -35641,19 +35641,19 @@
       <c r="F82" s="22"/>
       <c r="G82" s="22"/>
       <c r="H82" s="22">
-        <f>[4]Apr!$AE$1</f>
+        <f>[4]Jul!$AE$1</f>
         <v>0</v>
       </c>
       <c r="I82" s="22">
-        <f>[5]Apr!$AE$1</f>
+        <f>[5]Jul!$AE$1</f>
         <v>0</v>
       </c>
       <c r="J82" s="22">
-        <f>[6]Apr!$AE$1</f>
+        <f>[6]Jul!$AE$1</f>
         <v>0</v>
       </c>
       <c r="K82" s="22">
-        <f>[7]Apr!$AB$1</f>
+        <f>[7]Jul!$AB$1</f>
         <v>0</v>
       </c>
       <c r="L82" s="22"/>
@@ -35666,19 +35666,19 @@
       <c r="Q82" s="22"/>
       <c r="R82" s="22"/>
       <c r="S82" s="22">
-        <f>[4]May!$AE$1</f>
+        <f>[4]Aug!$AE$1</f>
         <v>0</v>
       </c>
       <c r="T82" s="22">
-        <f>[5]May!$AE$1</f>
+        <f>[5]Aug!$AE$1</f>
         <v>0</v>
       </c>
       <c r="U82" s="22">
-        <f>[6]May!$AE$1</f>
+        <f>[6]Aug!$AE$1</f>
         <v>0</v>
       </c>
       <c r="V82" s="22">
-        <f>[7]May!$AB$1</f>
+        <f>[7]Aug!$AB$1</f>
         <v>0</v>
       </c>
       <c r="W82" s="22"/>
@@ -35692,19 +35692,19 @@
       <c r="AB82" s="22"/>
       <c r="AC82" s="22"/>
       <c r="AD82" s="22">
-        <f>[4]Jun!$AE$1</f>
+        <f>[4]Sep!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AE82" s="22">
-        <f>[5]Jun!$AE$1</f>
+        <f>[5]Sep!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AF82" s="22">
-        <f>[6]Jun!$AE$1</f>
+        <f>[6]Sep!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AG82" s="22">
-        <f>[7]Jun!$AB$1</f>
+        <f>[7]Sep!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AH82" s="22"/>
@@ -35718,19 +35718,19 @@
       <c r="AM82" s="22"/>
       <c r="AN82" s="22"/>
       <c r="AO82" s="22">
-        <f>[4]Jul!$AE$1</f>
+        <f>[4]Oct!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AP82" s="22">
-        <f>[5]Jul!$AE$1</f>
+        <f>[5]Oct!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AQ82" s="22">
-        <f>[6]Jul!$AE$1</f>
+        <f>[6]Oct!$AE$1</f>
         <v>0</v>
       </c>
       <c r="AR82" s="22">
-        <f>[7]Jul!$AB$1</f>
+        <f>[7]Oct!$AB$1</f>
         <v>0</v>
       </c>
       <c r="AS82" s="22"/>
@@ -35744,19 +35744,19 @@
       <c r="AX82" s="22"/>
       <c r="AY82" s="22"/>
       <c r="AZ82" s="22">
-        <f>[4]Aug!$AE$1</f>
+        <f>[4]Nov!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BA82" s="22">
-        <f>[5]Aug!$AE$1</f>
+        <f>[5]Nov!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BB82" s="22">
-        <f>[6]Aug!$AE$1</f>
+        <f>[6]Nov!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BC82" s="22">
-        <f>[7]Aug!$AB$1</f>
+        <f>[7]Nov!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BD82" s="22"/>
@@ -35770,19 +35770,19 @@
       <c r="BI82" s="22"/>
       <c r="BJ82" s="22"/>
       <c r="BK82" s="22">
-        <f>[4]Sep!$AE$1</f>
+        <f>[4]Dec!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BL82" s="22">
-        <f>[5]Sep!$AE$1</f>
+        <f>[5]Dec!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BM82" s="22">
-        <f>[6]Sep!$AE$1</f>
+        <f>[6]Dec!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BN82" s="22">
-        <f>[7]Sep!$AB$1</f>
+        <f>[7]Dec!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BO82" s="22"/>
@@ -35796,19 +35796,19 @@
       <c r="BT82" s="22"/>
       <c r="BU82" s="22"/>
       <c r="BV82" s="22">
-        <f>[4]Oct!$AE$1</f>
+        <f>[4]Jan!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BW82" s="22">
-        <f>[5]Oct!$AE$1</f>
+        <f>[5]Jan!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BX82" s="22">
-        <f>[6]Oct!$AE$1</f>
+        <f>[6]Jan!$AE$1</f>
         <v>0</v>
       </c>
       <c r="BY82" s="22">
-        <f>[7]Oct!$AB$1</f>
+        <f>[7]Jan!$AB$1</f>
         <v>0</v>
       </c>
       <c r="BZ82" s="22"/>
@@ -35822,19 +35822,19 @@
       <c r="CE82" s="22"/>
       <c r="CF82" s="22"/>
       <c r="CG82" s="22">
-        <f>[4]Nov!$AE$1</f>
+        <f>[4]Feb!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CH82" s="22">
-        <f>[5]Nov!$AE$1</f>
+        <f>[5]Feb!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CI82" s="22">
-        <f>[6]Nov!$AE$1</f>
+        <f>[6]Feb!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CJ82" s="22">
-        <f>[7]Nov!$AB$1</f>
+        <f>[7]Feb!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CK82" s="22"/>
@@ -35848,19 +35848,19 @@
       <c r="CP82" s="22"/>
       <c r="CQ82" s="22"/>
       <c r="CR82" s="22">
-        <f>[4]Dec!$AE$1</f>
+        <f>[4]Mar!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CS82" s="22">
-        <f>[5]Dec!$AE$1</f>
+        <f>[5]Mar!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CT82" s="22">
-        <f>[6]Dec!$AE$1</f>
+        <f>[6]Mar!$AE$1</f>
         <v>0</v>
       </c>
       <c r="CU82" s="22">
-        <f>[7]Dec!$AB$1</f>
+        <f>[7]Mar!$AB$1</f>
         <v>0</v>
       </c>
       <c r="CV82" s="22"/>
@@ -35874,19 +35874,19 @@
       <c r="DA82" s="22"/>
       <c r="DB82" s="22"/>
       <c r="DC82" s="22">
-        <f>[4]Jan!$AE$1</f>
+        <f>[4]Apr!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DD82" s="22">
-        <f>[5]Jan!$AE$1</f>
+        <f>[5]Apr!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DE82" s="22">
-        <f>[6]Jan!$AE$1</f>
+        <f>[6]Apr!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DF82" s="22">
-        <f>[7]Jan!$AB$1</f>
+        <f>[7]Apr!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DG82" s="22"/>
@@ -35900,19 +35900,19 @@
       <c r="DL82" s="22"/>
       <c r="DM82" s="22"/>
       <c r="DN82" s="22">
-        <f>[4]Feb!$AE$1</f>
+        <f>[4]May!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DO82" s="22">
-        <f>[5]Feb!$AE$1</f>
+        <f>[5]May!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DP82" s="22">
-        <f>[6]Feb!$AE$1</f>
+        <f>[6]May!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DQ82" s="22">
-        <f>[7]Feb!$AB$1</f>
+        <f>[7]May!$AB$1</f>
         <v>0</v>
       </c>
       <c r="DR82" s="22"/>
@@ -35926,19 +35926,19 @@
       <c r="DW82" s="22"/>
       <c r="DX82" s="22"/>
       <c r="DY82" s="22">
-        <f>[4]Mar!$AE$1</f>
+        <f>[4]Jun!$AE$1</f>
         <v>0</v>
       </c>
       <c r="DZ82" s="22">
-        <f>[5]Mar!$AE$1</f>
+        <f>[5]Jun!$AE$1</f>
         <v>0</v>
       </c>
       <c r="EA82" s="22">
-        <f>[6]Mar!$AE$1</f>
+        <f>[6]Jun!$AE$1</f>
         <v>0</v>
       </c>
       <c r="EB82" s="22">
-        <f>[7]Mar!$AB$1</f>
+        <f>[7]Jun!$AB$1</f>
         <v>0</v>
       </c>
       <c r="EC82" s="22"/>
@@ -35969,19 +35969,19 @@
       <c r="F83" s="22"/>
       <c r="G83" s="22"/>
       <c r="H83" s="22">
-        <f>[4]Apr!$AD$1</f>
+        <f>[4]Jul!$AD$1</f>
         <v>0</v>
       </c>
       <c r="I83" s="22">
-        <f>[5]Apr!$AD$1</f>
+        <f>[5]Jul!$AD$1</f>
         <v>0</v>
       </c>
       <c r="J83" s="22">
-        <f>[6]Apr!$AD$1</f>
+        <f>[6]Jul!$AD$1</f>
         <v>0</v>
       </c>
       <c r="K83" s="22">
-        <f>[7]Apr!$AA$1</f>
+        <f>[7]Jul!$AA$1</f>
         <v>0</v>
       </c>
       <c r="L83" s="22"/>
@@ -35994,19 +35994,19 @@
       <c r="Q83" s="22"/>
       <c r="R83" s="22"/>
       <c r="S83" s="22">
-        <f>[4]May!$AD$1</f>
+        <f>[4]Aug!$AD$1</f>
         <v>0</v>
       </c>
       <c r="T83" s="22">
-        <f>[5]May!$AD$1</f>
+        <f>[5]Aug!$AD$1</f>
         <v>0</v>
       </c>
       <c r="U83" s="22">
-        <f>[6]May!$AD$1</f>
+        <f>[6]Aug!$AD$1</f>
         <v>0</v>
       </c>
       <c r="V83" s="22">
-        <f>[7]May!$AA$1</f>
+        <f>[7]Aug!$AA$1</f>
         <v>0</v>
       </c>
       <c r="W83" s="22"/>
@@ -36020,19 +36020,19 @@
       <c r="AB83" s="22"/>
       <c r="AC83" s="22"/>
       <c r="AD83" s="22">
-        <f>[4]Jun!$AD$1</f>
+        <f>[4]Sep!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AE83" s="22">
-        <f>[5]Jun!$AD$1</f>
+        <f>[5]Sep!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AF83" s="22">
-        <f>[6]Jun!$AD$1</f>
+        <f>[6]Sep!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AG83" s="22">
-        <f>[7]Jun!$AA$1</f>
+        <f>[7]Sep!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AH83" s="22"/>
@@ -36046,19 +36046,19 @@
       <c r="AM83" s="22"/>
       <c r="AN83" s="22"/>
       <c r="AO83" s="22">
-        <f>[4]Jul!$AD$1</f>
+        <f>[4]Oct!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AP83" s="22">
-        <f>[5]Jul!$AD$1</f>
+        <f>[5]Oct!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AQ83" s="22">
-        <f>[6]Jul!$AD$1</f>
+        <f>[6]Oct!$AD$1</f>
         <v>0</v>
       </c>
       <c r="AR83" s="22">
-        <f>[7]Jul!$AA$1</f>
+        <f>[7]Oct!$AA$1</f>
         <v>0</v>
       </c>
       <c r="AS83" s="22"/>
@@ -36072,19 +36072,19 @@
       <c r="AX83" s="22"/>
       <c r="AY83" s="22"/>
       <c r="AZ83" s="22">
-        <f>[4]Aug!$AD$1</f>
+        <f>[4]Nov!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BA83" s="22">
-        <f>[5]Aug!$AD$1</f>
+        <f>[5]Nov!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BB83" s="22">
-        <f>[6]Aug!$AD$1</f>
+        <f>[6]Nov!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BC83" s="22">
-        <f>[7]Aug!$AA$1</f>
+        <f>[7]Nov!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BD83" s="22"/>
@@ -36098,19 +36098,19 @@
       <c r="BI83" s="22"/>
       <c r="BJ83" s="22"/>
       <c r="BK83" s="22">
-        <f>[4]Sep!$AD$1</f>
+        <f>[4]Dec!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BL83" s="22">
-        <f>[5]Sep!$AD$1</f>
+        <f>[5]Dec!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BM83" s="22">
-        <f>[6]Sep!$AD$1</f>
+        <f>[6]Dec!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BN83" s="22">
-        <f>[7]Sep!$AA$1</f>
+        <f>[7]Dec!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BO83" s="22"/>
@@ -36124,19 +36124,19 @@
       <c r="BT83" s="22"/>
       <c r="BU83" s="22"/>
       <c r="BV83" s="22">
-        <f>[4]Oct!$AD$1</f>
+        <f>[4]Jan!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BW83" s="22">
-        <f>[5]Oct!$AD$1</f>
+        <f>[5]Jan!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BX83" s="22">
-        <f>[6]Oct!$AD$1</f>
+        <f>[6]Jan!$AD$1</f>
         <v>0</v>
       </c>
       <c r="BY83" s="22">
-        <f>[7]Oct!$AA$1</f>
+        <f>[7]Jan!$AA$1</f>
         <v>0</v>
       </c>
       <c r="BZ83" s="22"/>
@@ -36150,19 +36150,19 @@
       <c r="CE83" s="22"/>
       <c r="CF83" s="22"/>
       <c r="CG83" s="22">
-        <f>[4]Nov!$AD$1</f>
+        <f>[4]Feb!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CH83" s="22">
-        <f>[5]Nov!$AD$1</f>
+        <f>[5]Feb!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CI83" s="22">
-        <f>[6]Nov!$AD$1</f>
+        <f>[6]Feb!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CJ83" s="22">
-        <f>[7]Nov!$AA$1</f>
+        <f>[7]Feb!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CK83" s="22"/>
@@ -36176,19 +36176,19 @@
       <c r="CP83" s="22"/>
       <c r="CQ83" s="22"/>
       <c r="CR83" s="22">
-        <f>[4]Dec!$AD$1</f>
+        <f>[4]Mar!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CS83" s="22">
-        <f>[5]Dec!$AD$1</f>
+        <f>[5]Mar!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CT83" s="22">
-        <f>[6]Dec!$AD$1</f>
+        <f>[6]Mar!$AD$1</f>
         <v>0</v>
       </c>
       <c r="CU83" s="22">
-        <f>[7]Dec!$AA$1</f>
+        <f>[7]Mar!$AA$1</f>
         <v>0</v>
       </c>
       <c r="CV83" s="22"/>
@@ -36202,19 +36202,19 @@
       <c r="DA83" s="22"/>
       <c r="DB83" s="22"/>
       <c r="DC83" s="22">
-        <f>[4]Jan!$AD$1</f>
+        <f>[4]Apr!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DD83" s="22">
-        <f>[5]Jan!$AD$1</f>
+        <f>[5]Apr!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DE83" s="22">
-        <f>[6]Jan!$AD$1</f>
+        <f>[6]Apr!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DF83" s="22">
-        <f>[7]Jan!$AA$1</f>
+        <f>[7]Apr!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DG83" s="22"/>
@@ -36228,19 +36228,19 @@
       <c r="DL83" s="22"/>
       <c r="DM83" s="22"/>
       <c r="DN83" s="22">
-        <f>[4]Feb!$AD$1</f>
+        <f>[4]May!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DO83" s="22">
-        <f>[5]Feb!$AD$1</f>
+        <f>[5]May!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DP83" s="22">
-        <f>[6]Feb!$AD$1</f>
+        <f>[6]May!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DQ83" s="22">
-        <f>[7]Feb!$AA$1</f>
+        <f>[7]May!$AA$1</f>
         <v>0</v>
       </c>
       <c r="DR83" s="22"/>
@@ -36254,19 +36254,19 @@
       <c r="DW83" s="22"/>
       <c r="DX83" s="22"/>
       <c r="DY83" s="22">
-        <f>[4]Mar!$AD$1</f>
+        <f>[4]Jun!$AD$1</f>
         <v>0</v>
       </c>
       <c r="DZ83" s="22">
-        <f>[5]Mar!$AD$1</f>
+        <f>[5]Jun!$AD$1</f>
         <v>0</v>
       </c>
       <c r="EA83" s="22">
-        <f>[6]Mar!$AD$1</f>
+        <f>[6]Jun!$AD$1</f>
         <v>0</v>
       </c>
       <c r="EB83" s="22">
-        <f>[7]Mar!$AA$1</f>
+        <f>[7]Jun!$AA$1</f>
         <v>0</v>
       </c>
       <c r="EC83" s="22"/>
@@ -36296,7 +36296,7 @@
       <c r="E84" s="21"/>
       <c r="F84" s="22"/>
       <c r="G84" s="22">
-        <f>[2]Apr!$AG$1</f>
+        <f>[2]Jul!$AG$1</f>
         <v>0</v>
       </c>
       <c r="H84" s="22"/>
@@ -36312,7 +36312,7 @@
       <c r="P84" s="21"/>
       <c r="Q84" s="22"/>
       <c r="R84" s="22">
-        <f>[2]May!$AG$1</f>
+        <f>[2]Aug!$AG$1</f>
         <v>0</v>
       </c>
       <c r="S84" s="22"/>
@@ -36329,7 +36329,7 @@
       <c r="AA84" s="21"/>
       <c r="AB84" s="22"/>
       <c r="AC84" s="22">
-        <f>[2]Jun!$AG$1</f>
+        <f>[2]Sep!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AD84" s="22"/>
@@ -36346,7 +36346,7 @@
       <c r="AL84" s="21"/>
       <c r="AM84" s="22"/>
       <c r="AN84" s="22">
-        <f>[2]Jul!$AG$1</f>
+        <f>[2]Oct!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AO84" s="22"/>
@@ -36363,7 +36363,7 @@
       <c r="AW84" s="21"/>
       <c r="AX84" s="22"/>
       <c r="AY84" s="22">
-        <f>[2]Aug!$AG$1</f>
+        <f>[2]Nov!$AG$1</f>
         <v>0</v>
       </c>
       <c r="AZ84" s="22"/>
@@ -36380,7 +36380,7 @@
       <c r="BH84" s="21"/>
       <c r="BI84" s="22"/>
       <c r="BJ84" s="22">
-        <f>[2]Sep!$AG$1</f>
+        <f>[2]Dec!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BK84" s="22"/>
@@ -36397,7 +36397,7 @@
       <c r="BS84" s="21"/>
       <c r="BT84" s="22"/>
       <c r="BU84" s="22">
-        <f>[2]Oct!$AG$1</f>
+        <f>[2]Jan!$AG$1</f>
         <v>0</v>
       </c>
       <c r="BV84" s="22"/>
@@ -36414,7 +36414,7 @@
       <c r="CD84" s="21"/>
       <c r="CE84" s="22"/>
       <c r="CF84" s="22">
-        <f>[2]Nov!$AG$1</f>
+        <f>[2]Feb!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CG84" s="22"/>
@@ -36431,7 +36431,7 @@
       <c r="CO84" s="21"/>
       <c r="CP84" s="22"/>
       <c r="CQ84" s="22">
-        <f>[2]Dec!$AG$1</f>
+        <f>[2]Mar!$AG$1</f>
         <v>0</v>
       </c>
       <c r="CR84" s="22"/>
@@ -36448,7 +36448,7 @@
       <c r="CZ84" s="21"/>
       <c r="DA84" s="22"/>
       <c r="DB84" s="22">
-        <f>[2]Jan!$AG$1</f>
+        <f>[2]Apr!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DC84" s="22"/>
@@ -36465,7 +36465,7 @@
       <c r="DK84" s="21"/>
       <c r="DL84" s="22"/>
       <c r="DM84" s="22">
-        <f>[2]Feb!$AG$1</f>
+        <f>[2]May!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DN84" s="22"/>
@@ -36482,7 +36482,7 @@
       <c r="DV84" s="21"/>
       <c r="DW84" s="22"/>
       <c r="DX84" s="22">
-        <f>[2]Mar!$AG$1</f>
+        <f>[2]Jun!$AG$1</f>
         <v>0</v>
       </c>
       <c r="DY84" s="22"/>
@@ -36516,7 +36516,7 @@
       <c r="E85" s="21"/>
       <c r="F85" s="22"/>
       <c r="G85" s="22">
-        <f>[2]Apr!$AH$1</f>
+        <f>[2]Jul!$AH$1</f>
         <v>0</v>
       </c>
       <c r="H85" s="22"/>
@@ -36532,7 +36532,7 @@
       <c r="P85" s="21"/>
       <c r="Q85" s="22"/>
       <c r="R85" s="22">
-        <f>[2]May!$AH$1</f>
+        <f>[2]Aug!$AH$1</f>
         <v>0</v>
       </c>
       <c r="S85" s="22"/>
@@ -36549,7 +36549,7 @@
       <c r="AA85" s="21"/>
       <c r="AB85" s="22"/>
       <c r="AC85" s="22">
-        <f>[2]Jun!$AH$1</f>
+        <f>[2]Sep!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AD85" s="22"/>
@@ -36566,7 +36566,7 @@
       <c r="AL85" s="21"/>
       <c r="AM85" s="22"/>
       <c r="AN85" s="22">
-        <f>[2]Jul!$AH$1</f>
+        <f>[2]Oct!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AO85" s="22"/>
@@ -36583,7 +36583,7 @@
       <c r="AW85" s="21"/>
       <c r="AX85" s="22"/>
       <c r="AY85" s="22">
-        <f>[2]Aug!$AH$1</f>
+        <f>[2]Nov!$AH$1</f>
         <v>0</v>
       </c>
       <c r="AZ85" s="22"/>
@@ -36600,7 +36600,7 @@
       <c r="BH85" s="21"/>
       <c r="BI85" s="22"/>
       <c r="BJ85" s="22">
-        <f>[2]Sep!$AH$1</f>
+        <f>[2]Dec!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BK85" s="22"/>
@@ -36617,7 +36617,7 @@
       <c r="BS85" s="21"/>
       <c r="BT85" s="22"/>
       <c r="BU85" s="22">
-        <f>[2]Oct!$AH$1</f>
+        <f>[2]Jan!$AH$1</f>
         <v>0</v>
       </c>
       <c r="BV85" s="22"/>
@@ -36634,7 +36634,7 @@
       <c r="CD85" s="21"/>
       <c r="CE85" s="22"/>
       <c r="CF85" s="22">
-        <f>[2]Nov!$AH$1</f>
+        <f>[2]Feb!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CG85" s="22"/>
@@ -36651,7 +36651,7 @@
       <c r="CO85" s="21"/>
       <c r="CP85" s="22"/>
       <c r="CQ85" s="22">
-        <f>[2]Dec!$AH$1</f>
+        <f>[2]Mar!$AH$1</f>
         <v>0</v>
       </c>
       <c r="CR85" s="22"/>
@@ -36668,7 +36668,7 @@
       <c r="CZ85" s="21"/>
       <c r="DA85" s="22"/>
       <c r="DB85" s="22">
-        <f>[2]Jan!$AH$1</f>
+        <f>[2]Apr!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DC85" s="22"/>
@@ -36685,7 +36685,7 @@
       <c r="DK85" s="21"/>
       <c r="DL85" s="22"/>
       <c r="DM85" s="22">
-        <f>[2]Feb!$AH$1</f>
+        <f>[2]May!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DN85" s="22"/>
@@ -36702,7 +36702,7 @@
       <c r="DV85" s="21"/>
       <c r="DW85" s="22"/>
       <c r="DX85" s="22">
-        <f>[2]Mar!$AH$1</f>
+        <f>[2]Jun!$AH$1</f>
         <v>0</v>
       </c>
       <c r="DY85" s="22"/>
@@ -37175,15 +37175,15 @@
       <c r="F88" s="22"/>
       <c r="G88" s="22"/>
       <c r="H88" s="22">
-        <f>-[4]Apr!$Q$1</f>
+        <f>-[4]Jul!$Q$1</f>
         <v>0</v>
       </c>
       <c r="I88" s="22">
-        <f>-[5]Apr!$Q$1</f>
+        <f>-[5]Jul!$Q$1</f>
         <v>0</v>
       </c>
       <c r="J88" s="22">
-        <f>-[6]Apr!$Q$1</f>
+        <f>-[6]Jul!$Q$1</f>
         <v>0</v>
       </c>
       <c r="K88" s="22"/>
@@ -37197,15 +37197,15 @@
       <c r="Q88" s="22"/>
       <c r="R88" s="22"/>
       <c r="S88" s="22">
-        <f>-[4]May!$Q$1</f>
+        <f>-[4]Aug!$Q$1</f>
         <v>0</v>
       </c>
       <c r="T88" s="22">
-        <f>-[5]May!$Q$1</f>
+        <f>-[5]Aug!$Q$1</f>
         <v>0</v>
       </c>
       <c r="U88" s="22">
-        <f>-[6]May!$Q$1</f>
+        <f>-[6]Aug!$Q$1</f>
         <v>0</v>
       </c>
       <c r="V88" s="22"/>
@@ -37220,15 +37220,15 @@
       <c r="AB88" s="22"/>
       <c r="AC88" s="22"/>
       <c r="AD88" s="22">
-        <f>-[4]Jun!$Q$1</f>
+        <f>-[4]Sep!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AE88" s="22">
-        <f>-[5]Jun!$Q$1</f>
+        <f>-[5]Sep!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AF88" s="22">
-        <f>-[6]Jun!$Q$1</f>
+        <f>-[6]Sep!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AG88" s="22"/>
@@ -37243,15 +37243,15 @@
       <c r="AM88" s="22"/>
       <c r="AN88" s="22"/>
       <c r="AO88" s="22">
-        <f>-[4]Jul!$Q$1</f>
+        <f>-[4]Oct!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AP88" s="22">
-        <f>-[5]Jul!$Q$1</f>
+        <f>-[5]Oct!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AQ88" s="22">
-        <f>-[6]Jul!$Q$1</f>
+        <f>-[6]Oct!$Q$1</f>
         <v>0</v>
       </c>
       <c r="AR88" s="22"/>
@@ -37266,15 +37266,15 @@
       <c r="AX88" s="22"/>
       <c r="AY88" s="22"/>
       <c r="AZ88" s="22">
-        <f>-[4]Aug!$Q$1</f>
+        <f>-[4]Nov!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BA88" s="22">
-        <f>-[5]Aug!$Q$1</f>
+        <f>-[5]Nov!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BB88" s="22">
-        <f>-[6]Aug!$Q$1</f>
+        <f>-[6]Nov!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BC88" s="22"/>
@@ -37289,15 +37289,15 @@
       <c r="BI88" s="22"/>
       <c r="BJ88" s="22"/>
       <c r="BK88" s="22">
-        <f>-[4]Sep!$Q$1</f>
+        <f>-[4]Dec!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BL88" s="22">
-        <f>-[5]Sep!$Q$1</f>
+        <f>-[5]Dec!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BM88" s="22">
-        <f>-[6]Sep!$Q$1</f>
+        <f>-[6]Dec!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BN88" s="22"/>
@@ -37312,15 +37312,15 @@
       <c r="BT88" s="22"/>
       <c r="BU88" s="22"/>
       <c r="BV88" s="22">
-        <f>-[4]Oct!$Q$1</f>
+        <f>-[4]Jan!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BW88" s="22">
-        <f>-[5]Oct!$Q$1</f>
+        <f>-[5]Jan!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BX88" s="22">
-        <f>-[6]Oct!$Q$1</f>
+        <f>-[6]Jan!$Q$1</f>
         <v>0</v>
       </c>
       <c r="BY88" s="22"/>
@@ -37335,15 +37335,15 @@
       <c r="CE88" s="22"/>
       <c r="CF88" s="22"/>
       <c r="CG88" s="22">
-        <f>-[4]Nov!$Q$1</f>
+        <f>-[4]Feb!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CH88" s="22">
-        <f>-[5]Nov!$Q$1</f>
+        <f>-[5]Feb!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CI88" s="22">
-        <f>-[6]Nov!$Q$1</f>
+        <f>-[6]Feb!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CJ88" s="22"/>
@@ -37358,15 +37358,15 @@
       <c r="CP88" s="22"/>
       <c r="CQ88" s="22"/>
       <c r="CR88" s="22">
-        <f>-[4]Dec!$Q$1</f>
+        <f>-[4]Mar!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CS88" s="22">
-        <f>-[5]Dec!$Q$1</f>
+        <f>-[5]Mar!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CT88" s="22">
-        <f>-[6]Dec!$Q$1</f>
+        <f>-[6]Mar!$Q$1</f>
         <v>0</v>
       </c>
       <c r="CU88" s="22"/>
@@ -37381,15 +37381,15 @@
       <c r="DA88" s="22"/>
       <c r="DB88" s="22"/>
       <c r="DC88" s="22">
-        <f>-[4]Jan!$Q$1</f>
+        <f>-[4]Apr!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DD88" s="22">
-        <f>-[5]Jan!$Q$1</f>
+        <f>-[5]Apr!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DE88" s="22">
-        <f>-[6]Jan!$Q$1</f>
+        <f>-[6]Apr!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DF88" s="22"/>
@@ -37404,15 +37404,15 @@
       <c r="DL88" s="22"/>
       <c r="DM88" s="22"/>
       <c r="DN88" s="22">
-        <f>-[4]Feb!$Q$1</f>
+        <f>-[4]May!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DO88" s="22">
-        <f>-[5]Feb!$Q$1</f>
+        <f>-[5]May!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DP88" s="22">
-        <f>-[6]Feb!$Q$1</f>
+        <f>-[6]May!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DQ88" s="22"/>
@@ -37427,15 +37427,15 @@
       <c r="DW88" s="22"/>
       <c r="DX88" s="22"/>
       <c r="DY88" s="22">
-        <f>-[4]Mar!$Q$1</f>
+        <f>-[4]Jun!$Q$1</f>
         <v>0</v>
       </c>
       <c r="DZ88" s="22">
-        <f>-[5]Mar!$Q$1</f>
+        <f>-[5]Jun!$Q$1</f>
         <v>0</v>
       </c>
       <c r="EA88" s="22">
-        <f>-[6]Mar!$Q$1</f>
+        <f>-[6]Jun!$Q$1</f>
         <v>0</v>
       </c>
       <c r="EB88" s="22"/>
@@ -37467,15 +37467,15 @@
       <c r="F89" s="22"/>
       <c r="G89" s="22"/>
       <c r="H89" s="22">
-        <f>[4]Apr!$AN$1</f>
+        <f>[4]Jul!$AN$1</f>
         <v>0</v>
       </c>
       <c r="I89" s="22">
-        <f>[5]Apr!$AN$1</f>
+        <f>[5]Jul!$AN$1</f>
         <v>0</v>
       </c>
       <c r="J89" s="22">
-        <f>[6]Apr!$AN$1</f>
+        <f>[6]Jul!$AN$1</f>
         <v>0</v>
       </c>
       <c r="K89" s="22"/>
@@ -37489,15 +37489,15 @@
       <c r="Q89" s="22"/>
       <c r="R89" s="22"/>
       <c r="S89" s="22">
-        <f>[4]May!$AN$1</f>
+        <f>[4]Aug!$AN$1</f>
         <v>0</v>
       </c>
       <c r="T89" s="22">
-        <f>[5]May!$AN$1</f>
+        <f>[5]Aug!$AN$1</f>
         <v>0</v>
       </c>
       <c r="U89" s="22">
-        <f>[6]May!$AN$1</f>
+        <f>[6]Aug!$AN$1</f>
         <v>0</v>
       </c>
       <c r="V89" s="22"/>
@@ -37512,15 +37512,15 @@
       <c r="AB89" s="22"/>
       <c r="AC89" s="22"/>
       <c r="AD89" s="22">
-        <f>[4]Jun!$AN$1</f>
+        <f>[4]Sep!$AN$1</f>
         <v>0</v>
       </c>
       <c r="AE89" s="22">
-        <f>[5]Jun!$AN$1</f>
+        <f>[5]Sep!$AN$1</f>
         <v>0</v>
       </c>
       <c r="AF89" s="22">
-        <f>[6]Jun!$AN$1</f>
+        <f>[6]Sep!$AN$1</f>
         <v>0</v>
       </c>
       <c r="AG89" s="22"/>
@@ -37535,15 +37535,15 @@
       <c r="AM89" s="22"/>
       <c r="AN89" s="22"/>
       <c r="AO89" s="22">
-        <f>[4]Jul!$AN$1</f>
+        <f>[4]Oct!$AN$1</f>
         <v>0</v>
       </c>
       <c r="AP89" s="22">
-        <f>[5]Jul!$AN$1</f>
+        <f>[5]Oct!$AN$1</f>
         <v>0</v>
       </c>
       <c r="AQ89" s="22">
-        <f>[6]Jul!$AN$1</f>
+        <f>[6]Oct!$AN$1</f>
         <v>0</v>
       </c>
       <c r="AR89" s="22"/>
@@ -37558,15 +37558,15 @@
       <c r="AX89" s="22"/>
       <c r="AY89" s="22"/>
       <c r="AZ89" s="22">
-        <f>[4]Aug!$AN$1</f>
+        <f>[4]Nov!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BA89" s="22">
-        <f>[5]Aug!$AN$1</f>
+        <f>[5]Nov!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BB89" s="22">
-        <f>[6]Aug!$AN$1</f>
+        <f>[6]Nov!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BC89" s="22"/>
@@ -37581,15 +37581,15 @@
       <c r="BI89" s="22"/>
       <c r="BJ89" s="22"/>
       <c r="BK89" s="22">
-        <f>[4]Sep!$AN$1</f>
+        <f>[4]Dec!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BL89" s="22">
-        <f>[5]Sep!$AN$1</f>
+        <f>[5]Dec!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BM89" s="22">
-        <f>[6]Sep!$AN$1</f>
+        <f>[6]Dec!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BN89" s="22"/>
@@ -37604,15 +37604,15 @@
       <c r="BT89" s="22"/>
       <c r="BU89" s="22"/>
       <c r="BV89" s="22">
-        <f>[4]Oct!$AN$1</f>
+        <f>[4]Jan!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BW89" s="22">
-        <f>[5]Oct!$AN$1</f>
+        <f>[5]Jan!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BX89" s="22">
-        <f>[6]Oct!$AN$1</f>
+        <f>[6]Jan!$AN$1</f>
         <v>0</v>
       </c>
       <c r="BY89" s="22"/>
@@ -37627,15 +37627,15 @@
       <c r="CE89" s="22"/>
       <c r="CF89" s="22"/>
       <c r="CG89" s="22">
-        <f>[4]Nov!$AN$1</f>
+        <f>[4]Feb!$AN$1</f>
         <v>0</v>
       </c>
       <c r="CH89" s="22">
-        <f>[5]Nov!$AN$1</f>
+        <f>[5]Feb!$AN$1</f>
         <v>0</v>
       </c>
       <c r="CI89" s="22">
-        <f>[6]Nov!$AN$1</f>
+        <f>[6]Feb!$AN$1</f>
         <v>0</v>
       </c>
       <c r="CJ89" s="22"/>
@@ -37650,15 +37650,15 @@
       <c r="CP89" s="22"/>
       <c r="CQ89" s="22"/>
       <c r="CR89" s="22">
-        <f>[4]Dec!$AN$1</f>
+        <f>[4]Mar!$AN$1</f>
         <v>0</v>
       </c>
       <c r="CS89" s="22">
-        <f>[5]Dec!$AN$1</f>
+        <f>[5]Mar!$AN$1</f>
         <v>0</v>
       </c>
       <c r="CT89" s="22">
-        <f>[6]Dec!$AN$1</f>
+        <f>[6]Mar!$AN$1</f>
         <v>0</v>
       </c>
       <c r="CU89" s="22"/>
@@ -37673,15 +37673,15 @@
       <c r="DA89" s="22"/>
       <c r="DB89" s="22"/>
       <c r="DC89" s="22">
-        <f>[4]Jan!$AN$1</f>
+        <f>[4]Apr!$AN$1</f>
         <v>0</v>
       </c>
       <c r="DD89" s="22">
-        <f>[5]Jan!$AN$1</f>
+        <f>[5]Apr!$AN$1</f>
         <v>0</v>
       </c>
       <c r="DE89" s="22">
-        <f>[6]Jan!$AN$1</f>
+        <f>[6]Apr!$AN$1</f>
         <v>0</v>
       </c>
       <c r="DF89" s="22"/>
@@ -37696,15 +37696,15 @@
       <c r="DL89" s="22"/>
       <c r="DM89" s="22"/>
       <c r="DN89" s="22">
-        <f>[4]Feb!$AN$1</f>
+        <f>[4]May!$AN$1</f>
         <v>0</v>
       </c>
       <c r="DO89" s="22">
-        <f>[5]Feb!$AN$1</f>
+        <f>[5]May!$AN$1</f>
         <v>0</v>
       </c>
       <c r="DP89" s="22">
-        <f>[6]Feb!$AN$1</f>
+        <f>[6]May!$AN$1</f>
         <v>0</v>
       </c>
       <c r="DQ89" s="22"/>
@@ -37719,15 +37719,15 @@
       <c r="DW89" s="22"/>
       <c r="DX89" s="22"/>
       <c r="DY89" s="22">
-        <f>[4]Mar!$AN$1</f>
+        <f>[4]Jun!$AN$1</f>
         <v>0</v>
       </c>
       <c r="DZ89" s="22">
-        <f>[5]Mar!$AN$1</f>
+        <f>[5]Jun!$AN$1</f>
         <v>0</v>
       </c>
       <c r="EA89" s="22">
-        <f>[6]Mar!$AN$1</f>
+        <f>[6]Jun!$AN$1</f>
         <v>0</v>
       </c>
       <c r="EB89" s="22"/>

--- a/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
@@ -16291,7 +16291,7 @@
       <c r="A2" s="253"/>
       <c r="B2" s="329">
         <f>DATE(YEAR(B4),MONTH(B4),1)-1</f>
-        <v>45657</v>
+        <v>45747</v>
       </c>
       <c r="C2" s="253"/>
       <c r="D2" s="634"/>
@@ -16313,7 +16313,7 @@
       <c r="A3" s="253"/>
       <c r="B3" s="330">
         <f>DATE(YEAR(B4),MONTH(B4),1)</f>
-        <v>45658</v>
+        <v>45748</v>
       </c>
       <c r="C3" s="253"/>
       <c r="D3" s="635" t="s">
@@ -16345,7 +16345,7 @@
       <c r="A4" s="253"/>
       <c r="B4" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)-1</f>
-        <v>45688</v>
+        <v>45777</v>
       </c>
       <c r="C4" s="253"/>
       <c r="D4" s="253"/>
@@ -16371,7 +16371,7 @@
       <c r="A5" s="253"/>
       <c r="B5" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)</f>
-        <v>45689</v>
+        <v>45778</v>
       </c>
       <c r="C5" s="253"/>
       <c r="D5" s="253" t="s">
@@ -16402,7 +16402,7 @@
       <c r="A6" s="253"/>
       <c r="B6" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)-1</f>
-        <v>45716</v>
+        <v>45808</v>
       </c>
       <c r="C6" s="253"/>
       <c r="D6" s="253" t="s">
@@ -16446,7 +16446,7 @@
       <c r="A7" s="253"/>
       <c r="B7" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)</f>
-        <v>45717</v>
+        <v>45809</v>
       </c>
       <c r="C7" s="253"/>
       <c r="D7" s="253" t="s">
@@ -16490,7 +16490,7 @@
       <c r="A8" s="253"/>
       <c r="B8" s="330">
         <f>DATE(YEAR(B10),MONTH(B10),1)-1</f>
-        <v>45747</v>
+        <v>45838</v>
       </c>
       <c r="C8" s="253"/>
       <c r="D8" s="253" t="s">
@@ -16519,7 +16519,7 @@
       <c r="A9" s="253"/>
       <c r="B9" s="330">
         <f>DATE(YEAR(B10),MONTH(B10),1)</f>
-        <v>45748</v>
+        <v>45839</v>
       </c>
       <c r="C9" s="253"/>
       <c r="D9" s="253"/>
@@ -16545,7 +16545,7 @@
       <c r="A10" s="253"/>
       <c r="B10" s="330">
         <f>DATE(YEAR(B12),MONTH(B12),1)-1</f>
-        <v>45777</v>
+        <v>45869</v>
       </c>
       <c r="C10" s="253"/>
       <c r="D10" s="637" t="s">
@@ -16577,7 +16577,7 @@
       <c r="A11" s="253"/>
       <c r="B11" s="330">
         <f>DATE(YEAR(B12),MONTH(B12),1)</f>
-        <v>45778</v>
+        <v>45870</v>
       </c>
       <c r="C11" s="253"/>
       <c r="D11" s="253" t="s">
@@ -16615,7 +16615,7 @@
       <c r="A12" s="253"/>
       <c r="B12" s="330">
         <f>DATE(YEAR(B14),MONTH(B14),1)-1</f>
-        <v>45808</v>
+        <v>45900</v>
       </c>
       <c r="C12" s="253"/>
       <c r="D12" s="253"/>
@@ -16637,7 +16637,7 @@
       <c r="A13" s="253"/>
       <c r="B13" s="330">
         <f>DATE(YEAR(B14),MONTH(B14),1)</f>
-        <v>45809</v>
+        <v>45901</v>
       </c>
       <c r="C13" s="253"/>
       <c r="D13" s="635" t="s">
@@ -16663,7 +16663,7 @@
       <c r="A14" s="253"/>
       <c r="B14" s="330">
         <f>DATE(YEAR(B16),MONTH(B16),1)-1</f>
-        <v>45838</v>
+        <v>45930</v>
       </c>
       <c r="C14" s="253"/>
       <c r="D14" s="253"/>
@@ -16691,7 +16691,7 @@
       <c r="A15" s="253"/>
       <c r="B15" s="330">
         <f>DATE(YEAR(B16),MONTH(B16),1)</f>
-        <v>45839</v>
+        <v>45931</v>
       </c>
       <c r="C15" s="253"/>
       <c r="D15" s="637" t="s">
@@ -16717,7 +16717,7 @@
       <c r="A16" s="253"/>
       <c r="B16" s="330">
         <f>DATE(YEAR(B18),MONTH(B18),1)-1</f>
-        <v>45869</v>
+        <v>45961</v>
       </c>
       <c r="C16" s="253"/>
       <c r="D16" s="637" t="s">
@@ -16749,7 +16749,7 @@
       <c r="A17" s="253"/>
       <c r="B17" s="330">
         <f>DATE(YEAR(B18),MONTH(B18),1)</f>
-        <v>45870</v>
+        <v>45962</v>
       </c>
       <c r="C17" s="253"/>
       <c r="D17" s="637" t="s">
@@ -16781,7 +16781,7 @@
       <c r="A18" s="253"/>
       <c r="B18" s="330">
         <f>DATE(YEAR(B20),MONTH(B20),1)-1</f>
-        <v>45900</v>
+        <v>45991</v>
       </c>
       <c r="C18" s="253"/>
       <c r="D18" s="637" t="s">
@@ -16807,7 +16807,7 @@
       <c r="A19" s="253"/>
       <c r="B19" s="330">
         <f>DATE(YEAR(B20),MONTH(B20),1)</f>
-        <v>45901</v>
+        <v>45992</v>
       </c>
       <c r="C19" s="253"/>
       <c r="D19" s="637" t="s">
@@ -16843,7 +16843,7 @@
       <c r="A20" s="253"/>
       <c r="B20" s="330">
         <f>DATE(YEAR(B22),MONTH(B22),1)-1</f>
-        <v>45930</v>
+        <v>46022</v>
       </c>
       <c r="C20" s="253"/>
       <c r="D20" s="253"/>
@@ -16865,7 +16865,7 @@
       <c r="A21" s="253"/>
       <c r="B21" s="330">
         <f>DATE(YEAR(B22),MONTH(B22),1)</f>
-        <v>45931</v>
+        <v>46023</v>
       </c>
       <c r="C21" s="253"/>
       <c r="D21" s="9" t="s">
@@ -16898,7 +16898,7 @@
       <c r="A22" s="253"/>
       <c r="B22" s="330">
         <f>DATE(YEAR(B24),MONTH(B24),1)-1</f>
-        <v>45961</v>
+        <v>46053</v>
       </c>
       <c r="C22" s="253"/>
       <c r="D22" s="253"/>
@@ -16920,7 +16920,7 @@
       <c r="A23" s="253"/>
       <c r="B23" s="330">
         <f>DATE(YEAR(B24),MONTH(B24),1)</f>
-        <v>45962</v>
+        <v>46054</v>
       </c>
       <c r="C23" s="253"/>
       <c r="F23" s="293"/>
@@ -16929,7 +16929,7 @@
       <c r="A24" s="253"/>
       <c r="B24" s="330">
         <f>DATE(YEAR(B26),MONTH(B26),1)-1</f>
-        <v>45991</v>
+        <v>46081</v>
       </c>
       <c r="C24" s="253"/>
     </row>
@@ -16937,7 +16937,7 @@
       <c r="A25" s="253"/>
       <c r="B25" s="330">
         <f>DATE(YEAR(B26),MONTH(B26),1)</f>
-        <v>45992</v>
+        <v>46082</v>
       </c>
       <c r="C25" s="253"/>
       <c r="F25" s="267"/>
@@ -16947,7 +16947,7 @@
       <c r="A26" s="253"/>
       <c r="B26" s="330">
         <f>DATE(YEAR(B28),MONTH(B28),1)-1</f>
-        <v>46022</v>
+        <v>46112</v>
       </c>
       <c r="C26" s="253"/>
       <c r="G26" s="256"/>
@@ -16956,7 +16956,7 @@
       <c r="A27" s="253"/>
       <c r="B27" s="330">
         <f>DATE(YEAR(B28),MONTH(B28),1)</f>
-        <v>46023</v>
+        <v>46113</v>
       </c>
       <c r="C27" s="253"/>
       <c r="G27" s="256"/>
@@ -16965,7 +16965,7 @@
       <c r="A28" s="253"/>
       <c r="B28" s="330">
         <f>DATE(YEAR(B30),MONTH(B30),1)-1</f>
-        <v>46053</v>
+        <v>46142</v>
       </c>
       <c r="C28" s="253"/>
     </row>
@@ -16973,7 +16973,7 @@
       <c r="A29" s="253"/>
       <c r="B29" s="330">
         <f>DATE(YEAR(B30),MONTH(B30),1)</f>
-        <v>46054</v>
+        <v>46143</v>
       </c>
       <c r="C29" s="253"/>
     </row>
@@ -16981,7 +16981,7 @@
       <c r="A30" s="253"/>
       <c r="B30" s="330">
         <f>DATE(YEAR(B32),MONTH(B32),1)-1</f>
-        <v>46081</v>
+        <v>46173</v>
       </c>
       <c r="C30" s="253"/>
     </row>
@@ -16989,7 +16989,7 @@
       <c r="A31" s="253"/>
       <c r="B31" s="330">
         <f>DATE(YEAR(B32),MONTH(B32),1)</f>
-        <v>46082</v>
+        <v>46174</v>
       </c>
       <c r="C31" s="253"/>
     </row>
@@ -16997,7 +16997,7 @@
       <c r="A32" s="253"/>
       <c r="B32" s="331">
         <f>F21</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="C32" s="253"/>
     </row>
@@ -17005,7 +17005,7 @@
       <c r="A33" s="253"/>
       <c r="B33" s="330">
         <f>DATE(YEAR(B34),MONTH(B34),1)</f>
-        <v>46113</v>
+        <v>46204</v>
       </c>
       <c r="C33" s="253"/>
     </row>
@@ -17013,7 +17013,7 @@
       <c r="A34" s="253"/>
       <c r="B34" s="330">
         <f>DATE(IF(MONTH(B32)&lt;11,YEAR(B32),YEAR(B32)+1),IF(MONTH(B32)&lt;11,MONTH(B32)+2,IF(MONTH(B32)=11,1,2)),1)-1</f>
-        <v>46142</v>
+        <v>46234</v>
       </c>
       <c r="C34" s="253"/>
     </row>
@@ -17021,7 +17021,7 @@
       <c r="A35" s="253"/>
       <c r="B35" s="330">
         <f>DATE(YEAR(B36),MONTH(B36),1)</f>
-        <v>46143</v>
+        <v>46235</v>
       </c>
       <c r="C35" s="253"/>
     </row>
@@ -17029,7 +17029,7 @@
       <c r="A36" s="253"/>
       <c r="B36" s="330">
         <f>DATE(IF(MONTH(B34)&lt;11,YEAR(B34),YEAR(B34)+1),IF(MONTH(B34)&lt;11,MONTH(B34)+2,IF(MONTH(B34)=11,1,2)),1)-1</f>
-        <v>46173</v>
+        <v>46265</v>
       </c>
       <c r="C36" s="253"/>
     </row>
@@ -17037,7 +17037,7 @@
       <c r="A37" s="253"/>
       <c r="B37" s="330">
         <f>DATE(YEAR(B38),MONTH(B38),1)</f>
-        <v>46174</v>
+        <v>46266</v>
       </c>
       <c r="C37" s="253"/>
     </row>
@@ -17045,7 +17045,7 @@
       <c r="A38" s="253"/>
       <c r="B38" s="330">
         <f>DATE(IF(MONTH(B36)&lt;11,YEAR(B36),YEAR(B36)+1),IF(MONTH(B36)&lt;11,MONTH(B36)+2,IF(MONTH(B36)=11,1,2)),1)-1</f>
-        <v>46203</v>
+        <v>46295</v>
       </c>
       <c r="C38" s="253"/>
     </row>
@@ -17053,7 +17053,7 @@
       <c r="A39" s="253"/>
       <c r="B39" s="330">
         <f>DATE(YEAR(B40),MONTH(B40),1)</f>
-        <v>46204</v>
+        <v>46296</v>
       </c>
       <c r="C39" s="253"/>
     </row>
@@ -17061,7 +17061,7 @@
       <c r="A40" s="253"/>
       <c r="B40" s="330">
         <f>DATE(IF(MONTH(B38)&lt;11,YEAR(B38),YEAR(B38)+1),IF(MONTH(B38)&lt;11,MONTH(B38)+2,IF(MONTH(B38)=11,1,2)),1)-1</f>
-        <v>46234</v>
+        <v>46326</v>
       </c>
       <c r="C40" s="253"/>
     </row>
@@ -17069,7 +17069,7 @@
       <c r="A41" s="253"/>
       <c r="B41" s="330">
         <f>DATE(YEAR(B42),MONTH(B42),1)</f>
-        <v>46235</v>
+        <v>46327</v>
       </c>
       <c r="C41" s="253"/>
     </row>
@@ -17077,7 +17077,7 @@
       <c r="A42" s="253"/>
       <c r="B42" s="330">
         <f>DATE(IF(MONTH(B40)&lt;11,YEAR(B40),YEAR(B40)+1),IF(MONTH(B40)&lt;11,MONTH(B40)+2,IF(MONTH(B40)=11,1,2)),1)-1</f>
-        <v>46265</v>
+        <v>46356</v>
       </c>
       <c r="C42" s="253"/>
     </row>
@@ -17085,7 +17085,7 @@
       <c r="A43" s="253"/>
       <c r="B43" s="330">
         <f>DATE(YEAR(B44),MONTH(B44),1)</f>
-        <v>46266</v>
+        <v>46357</v>
       </c>
       <c r="C43" s="253"/>
     </row>
@@ -17093,7 +17093,7 @@
       <c r="A44" s="253"/>
       <c r="B44" s="330">
         <f>DATE(IF(MONTH(B42)&lt;11,YEAR(B42),YEAR(B42)+1),IF(MONTH(B42)&lt;11,MONTH(B42)+2,IF(MONTH(B42)=11,1,2)),1)-1</f>
-        <v>46295</v>
+        <v>46387</v>
       </c>
       <c r="C44" s="253"/>
     </row>
@@ -17101,7 +17101,7 @@
       <c r="A45" s="253"/>
       <c r="B45" s="330">
         <f>DATE(YEAR(B46),MONTH(B46),1)</f>
-        <v>46296</v>
+        <v>46388</v>
       </c>
       <c r="C45" s="253"/>
     </row>
@@ -17109,7 +17109,7 @@
       <c r="A46" s="253"/>
       <c r="B46" s="330">
         <f>DATE(IF(MONTH(B44)&lt;11,YEAR(B44),YEAR(B44)+1),IF(MONTH(B44)&lt;11,MONTH(B44)+2,IF(MONTH(B44)=11,1,2)),1)-1</f>
-        <v>46326</v>
+        <v>46418</v>
       </c>
       <c r="C46" s="253"/>
     </row>
@@ -17117,7 +17117,7 @@
       <c r="A47" s="253"/>
       <c r="B47" s="330">
         <f>DATE(YEAR(B48),MONTH(B48),1)</f>
-        <v>46327</v>
+        <v>46419</v>
       </c>
       <c r="C47" s="253"/>
     </row>
@@ -17125,7 +17125,7 @@
       <c r="A48" s="253"/>
       <c r="B48" s="330">
         <f>DATE(IF(MONTH(B46)&lt;11,YEAR(B46),YEAR(B46)+1),IF(MONTH(B46)&lt;11,MONTH(B46)+2,IF(MONTH(B46)=11,1,2)),1)-1</f>
-        <v>46356</v>
+        <v>46446</v>
       </c>
       <c r="C48" s="253"/>
     </row>
@@ -17133,7 +17133,7 @@
       <c r="A49" s="253"/>
       <c r="B49" s="330">
         <f>DATE(YEAR(B50),MONTH(B50),1)</f>
-        <v>46357</v>
+        <v>46447</v>
       </c>
       <c r="C49" s="253"/>
     </row>
@@ -17141,7 +17141,7 @@
       <c r="A50" s="253"/>
       <c r="B50" s="330">
         <f>DATE(IF(MONTH(B48)&lt;11,YEAR(B48),YEAR(B48)+1),IF(MONTH(B48)&lt;11,MONTH(B48)+2,IF(MONTH(B48)=11,1,2)),1)-1</f>
-        <v>46387</v>
+        <v>46477</v>
       </c>
       <c r="C50" s="253"/>
     </row>
@@ -17149,7 +17149,7 @@
       <c r="A51" s="253"/>
       <c r="B51" s="330">
         <f>DATE(YEAR(B52),MONTH(B52),1)</f>
-        <v>46388</v>
+        <v>46478</v>
       </c>
       <c r="C51" s="253"/>
     </row>
@@ -17157,7 +17157,7 @@
       <c r="A52" s="253"/>
       <c r="B52" s="330">
         <f>DATE(IF(MONTH(B50)&lt;11,YEAR(B50),YEAR(B50)+1),IF(MONTH(B50)&lt;11,MONTH(B50)+2,IF(MONTH(B50)=11,1,2)),1)-1</f>
-        <v>46418</v>
+        <v>46507</v>
       </c>
       <c r="C52" s="253"/>
     </row>
@@ -17165,7 +17165,7 @@
       <c r="A53" s="253"/>
       <c r="B53" s="330">
         <f>DATE(YEAR(B54),MONTH(B54),1)</f>
-        <v>46419</v>
+        <v>46508</v>
       </c>
       <c r="C53" s="253"/>
     </row>
@@ -17173,7 +17173,7 @@
       <c r="A54" s="253"/>
       <c r="B54" s="330">
         <f>DATE(IF(MONTH(B52)&lt;11,YEAR(B52),YEAR(B52)+1),IF(MONTH(B52)&lt;11,MONTH(B52)+2,IF(MONTH(B52)=11,1,2)),1)-1</f>
-        <v>46446</v>
+        <v>46538</v>
       </c>
       <c r="C54" s="253"/>
     </row>
@@ -17181,7 +17181,7 @@
       <c r="A55" s="253"/>
       <c r="B55" s="330">
         <f>DATE(YEAR(B56),MONTH(B56),1)</f>
-        <v>46447</v>
+        <v>46539</v>
       </c>
       <c r="C55" s="253"/>
     </row>
@@ -17189,7 +17189,7 @@
       <c r="A56" s="253"/>
       <c r="B56" s="332">
         <f>DATE(IF(MONTH(B54)&lt;11,YEAR(B54),YEAR(B54)+1),IF(MONTH(B54)&lt;11,MONTH(B54)+2,IF(MONTH(B54)=11,1,2)),1)-1</f>
-        <v>46477</v>
+        <v>46568</v>
       </c>
       <c r="C56" s="253"/>
     </row>

--- a/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
@@ -12979,7 +12979,7 @@
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="11">
-        <f>E15</f>
+        <f>IF(COUNT(E43:E47,E49:E76,E80:E85)=0,0,E15)</f>
         <v>0</v>
       </c>
       <c r="F48" s="3"/>
@@ -16422,16 +16422,16 @@
       </c>
       <c r="J6" s="185"/>
       <c r="K6" s="185">
-        <f>YEAR(L6)</f>
+        <f>YEAR(L6)-IF(MONTH(L6)&lt;4,1,0)</f>
         <v>2025</v>
       </c>
       <c r="L6" s="638">
         <f>B9</f>
-        <v>45748</v>
+        <v>45839</v>
       </c>
       <c r="M6" s="639"/>
       <c r="N6" s="638">
-        <f>B32</f>
+        <f>MIN(IF(DATE(YEAR(L6),3,31)&gt;=L6,DATE(YEAR(L6),3,31),DATE(YEAR(L6)+1,3,31)),F21)</f>
         <v>46112</v>
       </c>
       <c r="O6" s="641"/>
@@ -16466,17 +16466,17 @@
       </c>
       <c r="J7" s="185"/>
       <c r="K7" s="185">
-        <f>YEAR(L7)</f>
+        <f>YEAR(L7)-IF(MONTH(L7)&lt;4,1,0)</f>
         <v>2026</v>
       </c>
       <c r="L7" s="638">
-        <f>B33</f>
+        <f>N6+1</f>
         <v>46113</v>
       </c>
       <c r="M7" s="639"/>
       <c r="N7" s="638">
-        <f>B56</f>
-        <v>46477</v>
+        <f>F21</f>
+        <v>46203</v>
       </c>
       <c r="O7" s="641"/>
       <c r="P7" s="310">
@@ -16505,15 +16505,23 @@
         <v>14</v>
       </c>
       <c r="H8" s="253"/>
-      <c r="I8" s="253"/>
+      <c r="I8" s="185" t="inlineStr">
+        <is>
+          <t>Corporation Tax main rate</t>
+        </is>
+      </c>
       <c r="J8" s="253"/>
       <c r="K8" s="253"/>
       <c r="L8" s="253"/>
       <c r="M8" s="253"/>
       <c r="N8" s="253"/>
       <c r="O8" s="253"/>
-      <c r="P8" s="255"/>
-      <c r="Q8" s="255"/>
+      <c r="P8" s="310">
+        <v>25</v>
+      </c>
+      <c r="Q8" s="255" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="253"/>
@@ -16527,7 +16535,11 @@
       <c r="F9" s="253"/>
       <c r="G9" s="255"/>
       <c r="H9" s="253"/>
-      <c r="I9" s="253"/>
+      <c r="I9" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief fraction</t>
+        </is>
+      </c>
       <c r="J9" s="253"/>
       <c r="K9" s="253"/>
       <c r="L9" s="262" t="s">
@@ -16538,7 +16550,9 @@
         <v>521</v>
       </c>
       <c r="O9" s="263"/>
-      <c r="P9" s="264"/>
+      <c r="P9" s="262">
+        <v>0.015</v>
+      </c>
       <c r="Q9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16623,14 +16637,20 @@
       <c r="F12" s="253"/>
       <c r="G12" s="255"/>
       <c r="H12" s="253"/>
-      <c r="I12" s="253"/>
+      <c r="I12" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief lower limit</t>
+        </is>
+      </c>
       <c r="J12" s="253"/>
       <c r="K12" s="253"/>
       <c r="L12" s="253"/>
       <c r="M12" s="265"/>
       <c r="N12" s="255"/>
       <c r="O12" s="253"/>
-      <c r="P12" s="255"/>
+      <c r="P12" s="262">
+        <v>50000</v>
+      </c>
       <c r="Q12" s="255"/>
     </row>
     <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16649,14 +16669,20 @@
         <v>268</v>
       </c>
       <c r="H13" s="253"/>
-      <c r="I13" s="253"/>
+      <c r="I13" s="185" t="inlineStr">
+        <is>
+          <t>Marginal relief upper limit</t>
+        </is>
+      </c>
       <c r="J13" s="253"/>
       <c r="K13" s="253"/>
       <c r="L13" s="253"/>
       <c r="M13" s="253"/>
       <c r="N13" s="253"/>
       <c r="O13" s="253"/>
-      <c r="P13" s="253"/>
+      <c r="P13" s="262">
+        <v>250000</v>
+      </c>
       <c r="Q13" s="253"/>
     </row>
     <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -44960,22 +44986,28 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>Admin!P6</f>
+        <f>IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
       <c r="I33" s="187">
+        <f>J33-L33</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="167">
         <f>F33*G33/100</f>
         <v>0</v>
       </c>
-      <c r="J33" s="167"/>
       <c r="K33" s="161"/>
-      <c r="L33" s="38"/>
+      <c r="L33" s="38">
+        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="184">
-        <f>D34-C34+1</f>
-        <v>365</v>
+        <f>MAX(0,D34-C34+1)</f>
+        <v>0</v>
       </c>
       <c r="B34" s="182" t="s">
         <v>14</v>
@@ -44997,22 +45029,28 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>Admin!P7</f>
+        <f>IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
       <c r="I34" s="187">
+        <f>J34-L34</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="167">
         <f>F34*G34/100</f>
         <v>0</v>
       </c>
-      <c r="J34" s="167"/>
       <c r="K34" s="161"/>
-      <c r="L34" s="38"/>
+      <c r="L34" s="38">
+        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="35" spans="1:12" s="40" customFormat="1" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A35" s="184">
         <f>D34-C33+1</f>
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="B35" s="157"/>
       <c r="C35" s="420" t="s">
@@ -52778,7 +52816,7 @@
         <v>150</v>
       </c>
       <c r="AJ126" s="535">
-        <f>CorporationTax!I33</f>
+        <f>CorporationTax!J33</f>
         <v>0</v>
       </c>
       <c r="AK126" s="535"/>
@@ -52843,12 +52881,15 @@
       <c r="B128" s="209">
         <v>53</v>
       </c>
-      <c r="C128" s="483"/>
-      <c r="D128" s="483"/>
-      <c r="E128" s="483"/>
-      <c r="F128" s="483"/>
-      <c r="G128" s="483"/>
-      <c r="H128" s="483"/>
+      <c r="C128" s="545" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!E34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="D128" s="546"/>
+      <c r="E128" s="546"/>
+      <c r="F128" s="546"/>
+      <c r="G128" s="546"/>
+      <c r="H128" s="547"/>
       <c r="I128" s="198"/>
       <c r="J128" s="198"/>
       <c r="K128" s="198"/>
@@ -52858,13 +52899,16 @@
       <c r="M128" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="N128" s="483"/>
-      <c r="O128" s="483"/>
-      <c r="P128" s="483"/>
-      <c r="Q128" s="483"/>
-      <c r="R128" s="483"/>
-      <c r="S128" s="483"/>
-      <c r="T128" s="483"/>
+      <c r="N128" s="522" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!F34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="O128" s="468"/>
+      <c r="P128" s="468"/>
+      <c r="Q128" s="468"/>
+      <c r="R128" s="468"/>
+      <c r="S128" s="468"/>
+      <c r="T128" s="534"/>
       <c r="U128" s="198"/>
       <c r="V128" s="198"/>
       <c r="W128" s="198"/>
@@ -52873,8 +52917,11 @@
         <v>55</v>
       </c>
       <c r="Z128" s="351"/>
-      <c r="AA128" s="483"/>
-      <c r="AB128" s="483"/>
+      <c r="AA128" s="548" t="str">
+        <f>IF(CorporationTax!A34&gt;0,CorporationTax!G34," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
+      <c r="AB128" s="549"/>
       <c r="AC128" s="198"/>
       <c r="AD128" s="198"/>
       <c r="AE128" s="198"/>
@@ -52886,13 +52933,16 @@
       <c r="AI128" s="212" t="s">
         <v>150</v>
       </c>
-      <c r="AJ128" s="535"/>
-      <c r="AK128" s="468"/>
-      <c r="AL128" s="468"/>
-      <c r="AM128" s="468"/>
-      <c r="AN128" s="468"/>
-      <c r="AO128" s="468"/>
-      <c r="AP128" s="468"/>
+      <c r="AJ128" s="535">
+        <f>CorporationTax!J34</f>
+        <v>0</v>
+      </c>
+      <c r="AK128" s="535"/>
+      <c r="AL128" s="535"/>
+      <c r="AM128" s="535"/>
+      <c r="AN128" s="535"/>
+      <c r="AO128" s="535"/>
+      <c r="AP128" s="535"/>
       <c r="AQ128" s="224" t="s">
         <v>391</v>
       </c>
@@ -53130,11 +53180,14 @@
         <v>150</v>
       </c>
       <c r="X133" s="225"/>
-      <c r="Y133" s="514"/>
-      <c r="Z133" s="514"/>
-      <c r="AA133" s="514"/>
-      <c r="AB133" s="514"/>
-      <c r="AC133" s="514"/>
+      <c r="Y133" s="535">
+        <f>CorporationTax!L33+CorporationTax!L34</f>
+        <v>0</v>
+      </c>
+      <c r="Z133" s="535"/>
+      <c r="AA133" s="535"/>
+      <c r="AB133" s="535"/>
+      <c r="AC133" s="535"/>
       <c r="AD133" s="225"/>
       <c r="AE133" s="224" t="s">
         <v>391</v>
@@ -53232,11 +53285,14 @@
         <v>150</v>
       </c>
       <c r="X135" s="225"/>
-      <c r="Y135" s="514"/>
-      <c r="Z135" s="514"/>
-      <c r="AA135" s="514"/>
-      <c r="AB135" s="514"/>
-      <c r="AC135" s="514"/>
+      <c r="Y135" s="535">
+        <f>AJ131-Y133</f>
+        <v>0</v>
+      </c>
+      <c r="Z135" s="535"/>
+      <c r="AA135" s="535"/>
+      <c r="AB135" s="535"/>
+      <c r="AC135" s="535"/>
       <c r="AD135" s="225"/>
       <c r="AE135" s="224" t="s">
         <v>391</v>
@@ -53331,7 +53387,7 @@
         <v>66</v>
       </c>
       <c r="W137" s="543" t="str">
-        <f>IF(AJ131&gt;0,AJ131*100/AJ110," ")</f>
+        <f>IF(Y135&gt;0,Y135*100/AJ110," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="X137" s="544"/>
@@ -53753,7 +53809,7 @@
         <v>150</v>
       </c>
       <c r="AJ145" s="535">
-        <f>AJ131</f>
+        <f>Y135</f>
         <v>0</v>
       </c>
       <c r="AK145" s="468"/>

--- a/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
@@ -16594,18 +16594,10 @@
         <v>45870</v>
       </c>
       <c r="C11" s="253"/>
-      <c r="D11" s="253" t="s">
-        <v>501</v>
-      </c>
-      <c r="E11" s="262">
-        <v>12000</v>
-      </c>
-      <c r="F11" s="253" t="s">
-        <v>502</v>
-      </c>
-      <c r="G11" s="262">
-        <v>3000</v>
-      </c>
+      <c r="D11" s="253"/>
+      <c r="E11" s="262"/>
+      <c r="F11" s="253"/>
+      <c r="G11" s="262"/>
       <c r="H11" s="253"/>
       <c r="I11" s="253"/>
       <c r="J11" s="253"/>
@@ -41121,7 +41113,7 @@
       </c>
       <c r="D3" s="281">
         <f>Admin!B32</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="E3" s="67"/>
       <c r="H3" s="70"/>
@@ -41155,7 +41147,7 @@
       <c r="D5" s="81"/>
       <c r="E5" s="368">
         <f>D3</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="F5" s="369"/>
       <c r="H5" s="70"/>
@@ -42231,7 +42223,7 @@
       </c>
       <c r="D2" s="285">
         <f>'PubP&amp;L'!D3</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.15">
@@ -43150,7 +43142,7 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A11" s="286">
         <f>'PubP&amp;L'!D3</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="B11" s="71">
         <f t="shared" ref="B11:G11" si="0">B8+B9-B10</f>
@@ -43569,7 +43561,7 @@
       <c r="E22" s="351"/>
       <c r="F22" s="416">
         <f>PubBalSht!D2</f>
-        <v>46112</v>
+        <v>46203</v>
       </c>
       <c r="G22" s="416"/>
       <c r="H22" s="389"/>
@@ -44441,7 +44433,7 @@
       <c r="D5" s="433"/>
       <c r="E5" s="434">
         <f>Admin!L6</f>
-        <v>45748</v>
+        <v>45839</v>
       </c>
       <c r="F5" s="392"/>
       <c r="G5" s="176" t="s">
@@ -44449,7 +44441,7 @@
       </c>
       <c r="H5" s="434">
         <f>Admin!N7</f>
-        <v>46477</v>
+        <v>46203</v>
       </c>
       <c r="I5" s="435"/>
       <c r="J5" s="161"/>
@@ -44964,7 +44956,7 @@
     <row r="33" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="184">
         <f>D33-C33+1</f>
-        <v>365</v>
+        <v>274</v>
       </c>
       <c r="B33" s="182" t="s">
         <v>14</v>
@@ -45007,7 +44999,7 @@
     <row r="34" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A34" s="184">
         <f>MAX(0,D34-C34+1)</f>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="B34" s="182" t="s">
         <v>14</v>
@@ -48191,7 +48183,7 @@
       <c r="A33" s="198"/>
       <c r="B33" s="576">
         <f>Admin!L6</f>
-        <v>45748</v>
+        <v>45839</v>
       </c>
       <c r="C33" s="577"/>
       <c r="D33" s="578"/>
@@ -48205,7 +48197,7 @@
       <c r="L33" s="198"/>
       <c r="M33" s="576">
         <f>Admin!N7</f>
-        <v>46477</v>
+        <v>46203</v>
       </c>
       <c r="N33" s="577"/>
       <c r="O33" s="578"/>

--- a/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
@@ -55397,7 +55397,7 @@
         <v>150</v>
       </c>
       <c r="AA177" s="522" t="str">
-        <f>IF((CorporationTax!H15+CorporationTax!H17)&gt;0,CorporationTax!H15+CorporationTax!H17," ")</f>
+        <f>IF((CorporationTax!I15+CorporationTax!I17)&gt;0,CorporationTax!I15+CorporationTax!I17," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB177" s="522"/>
@@ -55415,7 +55415,7 @@
         <v>150</v>
       </c>
       <c r="AL177" s="522" t="str">
-        <f>IF(CorporationTax!H18&lt;&gt;0,CorporationTax!H18," ")</f>
+        <f>IF(CorporationTax!I18&lt;&gt;0,CorporationTax!I18," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AM177" s="522"/>
@@ -55507,7 +55507,7 @@
         <v>150</v>
       </c>
       <c r="AA179" s="522" t="str">
-        <f>IF(CorporationTax!H16&gt;0,CorporationTax!H16," ")</f>
+        <f>IF(CorporationTax!I16&gt;0,CorporationTax!I16," ")</f>
         <v xml:space="preserve"> </v>
       </c>
       <c r="AB179" s="522"/>

--- a/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="624">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="626">
   <si>
     <t>Depreciation</t>
   </si>
@@ -2159,6 +2159,12 @@
   </si>
   <si>
     <t>(Small profits rate)</t>
+  </si>
+  <si>
+    <t>Copyright (C) 2006-2026 DIY Accounting Limited</t>
+  </si>
+  <si>
+    <t>Licensed under the PolyForm Internal Use License 1.0.0 with an additional grant for accountants. Free to use, source available: https://spreadsheets.diyaccounting.co.uk</t>
   </si>
 </sst>
 </file>
@@ -11957,7 +11963,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R86"/>
+  <dimension ref="A1:R89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="11" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="0.83203125" style="6" customWidth="1"/>
@@ -13448,6 +13454,16 @@
       <c r="F86" s="3"/>
       <c r="G86" s="3"/>
       <c r="H86" s="3"/>
+    </row>
+    <row r="88">
+      <c r="B88" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="s">
+        <v>625</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="19">

--- a/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
+++ b/packages/GB Accounts Company 2026-06-30 (Jun26) Excel 2007/Financialaccounts.xlsx
@@ -12112,9 +12112,13 @@
       </c>
       <c r="M6" s="348"/>
       <c r="N6" s="170"/>
-      <c r="O6" s="151"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
+      <c r="O6" s="338" t="inlineStr">
+        <is>
+          <t>Franked investment income</t>
+        </is>
+      </c>
+      <c r="P6" s="339"/>
+      <c r="Q6" s="11"/>
       <c r="R6" s="3"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.15">
@@ -13466,7 +13470,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="20">
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="G10:K10"/>
     <mergeCell ref="E5:H5"/>
@@ -13485,6 +13489,7 @@
     <mergeCell ref="E4:H4"/>
     <mergeCell ref="O2:Q2"/>
     <mergeCell ref="O5:P5"/>
+    <mergeCell ref="O6:P6"/>
     <mergeCell ref="J6:K6"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -16259,7 +16264,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:Q57"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="1.5" style="256" customWidth="1"/>
@@ -16383,7 +16388,7 @@
       <c r="P4" s="253"/>
       <c r="Q4" s="253"/>
     </row>
-    <row r="5" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="253"/>
       <c r="B5" s="330">
         <f>DATE(YEAR(B6),MONTH(B6),1)</f>
@@ -16413,8 +16418,28 @@
         <v>623</v>
       </c>
       <c r="Q5" s="255"/>
-    </row>
-    <row r="6" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R5" s="253" t="inlineStr">
+        <is>
+          <t>(Main rate %)</t>
+        </is>
+      </c>
+      <c r="S5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief fraction)</t>
+        </is>
+      </c>
+      <c r="T5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief lower limit)</t>
+        </is>
+      </c>
+      <c r="U5" s="253" t="inlineStr">
+        <is>
+          <t>(Relief upper limit)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="253"/>
       <c r="B6" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)-1</f>
@@ -16457,8 +16482,20 @@
       <c r="Q6" s="255" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="R6" s="310">
+        <v>25</v>
+      </c>
+      <c r="S6" s="262">
+        <v>0.015</v>
+      </c>
+      <c r="T6" s="262">
+        <v>50000</v>
+      </c>
+      <c r="U6" s="262">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="253"/>
       <c r="B7" s="330">
         <f>DATE(YEAR(B8),MONTH(B8),1)</f>
@@ -16500,6 +16537,18 @@
       </c>
       <c r="Q7" s="255" t="s">
         <v>268</v>
+      </c>
+      <c r="R7" s="310">
+        <v>25</v>
+      </c>
+      <c r="S7" s="262">
+        <v>0.015</v>
+      </c>
+      <c r="T7" s="262">
+        <v>50000</v>
+      </c>
+      <c r="U7" s="262">
+        <v>250000</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16521,23 +16570,15 @@
         <v>14</v>
       </c>
       <c r="H8" s="253"/>
-      <c r="I8" s="185" t="inlineStr">
-        <is>
-          <t>Corporation Tax main rate</t>
-        </is>
-      </c>
+      <c r="I8" s="185"/>
       <c r="J8" s="253"/>
       <c r="K8" s="253"/>
       <c r="L8" s="253"/>
       <c r="M8" s="253"/>
       <c r="N8" s="253"/>
       <c r="O8" s="253"/>
-      <c r="P8" s="310">
-        <v>25</v>
-      </c>
-      <c r="Q8" s="255" t="s">
-        <v>268</v>
-      </c>
+      <c r="P8" s="310"/>
+      <c r="Q8" s="255"/>
     </row>
     <row r="9" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="253"/>
@@ -16551,11 +16592,7 @@
       <c r="F9" s="253"/>
       <c r="G9" s="255"/>
       <c r="H9" s="253"/>
-      <c r="I9" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief fraction</t>
-        </is>
-      </c>
+      <c r="I9" s="185"/>
       <c r="J9" s="253"/>
       <c r="K9" s="253"/>
       <c r="L9" s="262" t="s">
@@ -16566,9 +16603,7 @@
         <v>521</v>
       </c>
       <c r="O9" s="263"/>
-      <c r="P9" s="262">
-        <v>0.015</v>
-      </c>
+      <c r="P9" s="262"/>
       <c r="Q9" s="255"/>
     </row>
     <row r="10" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16645,20 +16680,14 @@
       <c r="F12" s="253"/>
       <c r="G12" s="255"/>
       <c r="H12" s="253"/>
-      <c r="I12" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief lower limit</t>
-        </is>
-      </c>
+      <c r="I12" s="185"/>
       <c r="J12" s="253"/>
       <c r="K12" s="253"/>
       <c r="L12" s="253"/>
       <c r="M12" s="265"/>
       <c r="N12" s="255"/>
       <c r="O12" s="253"/>
-      <c r="P12" s="262">
-        <v>50000</v>
-      </c>
+      <c r="P12" s="262"/>
       <c r="Q12" s="255"/>
     </row>
     <row r="13" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -16677,20 +16706,14 @@
         <v>268</v>
       </c>
       <c r="H13" s="253"/>
-      <c r="I13" s="185" t="inlineStr">
-        <is>
-          <t>Marginal relief upper limit</t>
-        </is>
-      </c>
+      <c r="I13" s="185"/>
       <c r="J13" s="253"/>
       <c r="K13" s="253"/>
       <c r="L13" s="253"/>
       <c r="M13" s="253"/>
       <c r="N13" s="253"/>
       <c r="O13" s="253"/>
-      <c r="P13" s="262">
-        <v>250000</v>
-      </c>
+      <c r="P13" s="262"/>
       <c r="Q13" s="253"/>
     </row>
     <row r="14" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
@@ -44899,7 +44922,11 @@
     </row>
     <row r="29" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A29" s="159"/>
-      <c r="B29" s="39"/>
+      <c r="B29" s="306" t="inlineStr">
+        <is>
+          <t>Add franked investment income (exempt distributions received)</t>
+        </is>
+      </c>
       <c r="C29" s="39"/>
       <c r="D29" s="39"/>
       <c r="E29" s="157"/>
@@ -44908,12 +44935,19 @@
       <c r="H29" s="162"/>
       <c r="I29" s="161"/>
       <c r="J29" s="161"/>
-      <c r="K29" s="176"/>
+      <c r="K29" s="252">
+        <f>OpenAccounts!Q6</f>
+        <v>0</v>
+      </c>
       <c r="L29" s="39"/>
     </row>
     <row r="30" spans="1:12" s="40" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A30" s="158"/>
-      <c r="B30" s="39"/>
+      <c r="B30" s="306" t="inlineStr">
+        <is>
+          <t>Augmented profits, which the marginal relief limits are tested against</t>
+        </is>
+      </c>
       <c r="C30" s="39"/>
       <c r="D30" s="39"/>
       <c r="E30" s="177"/>
@@ -44922,7 +44956,10 @@
       <c r="H30" s="162"/>
       <c r="I30" s="161"/>
       <c r="J30" s="161"/>
-      <c r="K30" s="161"/>
+      <c r="K30" s="252">
+        <f>K28+K29</f>
+        <v>0</v>
+      </c>
       <c r="L30" s="39"/>
     </row>
     <row r="31" spans="1:12" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -44994,7 +45031,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="441">
-        <f>IF(F33&lt;=Admin!$P$12*A33/A35,Admin!P6,Admin!$P$8)</f>
+        <f>IF(K30*A33/A35&lt;=Admin!$T$6*A33/A35/(1+Admin!$P$14),Admin!P6,Admin!$R$6)</f>
         <v>19</v>
       </c>
       <c r="H33" s="442"/>
@@ -45008,7 +45045,7 @@
       </c>
       <c r="K33" s="161"/>
       <c r="L33" s="38">
-        <f>IF(AND(F33&gt;Admin!$P$12*A33/A35,F33&lt;Admin!$P$13*A33/A35),(Admin!$P$13*A33/A35-F33)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A33/A35&gt;Admin!$T$6*A33/A35/(1+Admin!$P$14),K30*A33/A35&lt;Admin!$U$6*A33/A35/(1+Admin!$P$14)),(Admin!$U$6*A33/A35/(1+Admin!$P$14)-K30*A33/A35)*F33/(K30*A33/A35)*Admin!$S$6,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -45037,7 +45074,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="441">
-        <f>IF(F34&lt;=Admin!$P$12*A34/A35,Admin!P7,Admin!$P$8)</f>
+        <f>IF(K30*A34/A35&lt;=Admin!$T$7*A34/A35/(1+Admin!$P$14),Admin!P7,Admin!$R$7)</f>
         <v>19</v>
       </c>
       <c r="H34" s="442"/>
@@ -45051,7 +45088,7 @@
       </c>
       <c r="K34" s="161"/>
       <c r="L34" s="38">
-        <f>IF(AND(F34&gt;Admin!$P$12*A34/A35,F34&lt;Admin!$P$13*A34/A35),(Admin!$P$13*A34/A35-F34)*Admin!$P$9,0)</f>
+        <f>IF(AND(K30*A34/A35&gt;Admin!$T$7*A34/A35/(1+Admin!$P$14),K30*A34/A35&lt;Admin!$U$7*A34/A35/(1+Admin!$P$14)),(Admin!$U$7*A34/A35/(1+Admin!$P$14)-K30*A34/A35)*F34/(K30*A34/A35)*Admin!$S$7,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -52198,7 +52235,10 @@
       <c r="Y114" s="210" t="s">
         <v>150</v>
       </c>
-      <c r="Z114" s="514"/>
+      <c r="Z114" s="514">
+        <f>CorporationTax!K29</f>
+        <v>0</v>
+      </c>
       <c r="AA114" s="514"/>
       <c r="AB114" s="514"/>
       <c r="AC114" s="514"/>
@@ -52397,7 +52437,10 @@
         <v>40</v>
       </c>
       <c r="X118" s="553"/>
-      <c r="Y118" s="560"/>
+      <c r="Y118" s="560">
+        <f>Admin!$P$14</f>
+        <v>0</v>
+      </c>
       <c r="Z118" s="561"/>
       <c r="AA118" s="562"/>
       <c r="AB118" s="198"/>
@@ -52495,7 +52538,10 @@
         <v>41</v>
       </c>
       <c r="X120" s="553"/>
-      <c r="Y120" s="560"/>
+      <c r="Y120" s="560" t="str">
+        <f>IF(CorporationTax!A34&gt;0,Admin!$P$14," ")</f>
+        <v xml:space="preserve"> </v>
+      </c>
       <c r="Z120" s="561"/>
       <c r="AA120" s="562"/>
       <c r="AB120" s="198"/>
